--- a/docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx
+++ b/docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx
@@ -17290,7 +17290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" style="135" min="1" max="1"/>
@@ -17781,7 +17781,7 @@
       </c>
       <c r="J10" s="177" t="inlineStr">
         <is>
-          <t>深度2+及主题池；COMBAT/ELITE/Boss护卫</t>
+          <t>停止现行刷新，原点位/池由fat_zombie03接替</t>
         </is>
       </c>
       <c r="K10" s="177" t="inlineStr">
@@ -17791,12 +17791,12 @@
       </c>
       <c r="L10" s="180" t="inlineStr">
         <is>
-          <t>[已实装]</t>
+          <t>[已退役]</t>
         </is>
       </c>
       <c r="M10" s="177" t="inlineStr">
         <is>
-          <t>正式3D基础模板</t>
+          <t>弃用；旧档兼容保留</t>
         </is>
       </c>
       <c r="N10" s="177" t="inlineStr">
@@ -17806,7 +17806,7 @@
       </c>
       <c r="O10" s="177" t="inlineStr">
         <is>
-          <t>正式数值以Enemy3D.PROFILES为基线；旧2D基线仅用于倍率换算</t>
+          <t>2026-10-03用户裁定退役；普通怪身份由胖子僵尸03替换。原数值留作历史，未实装壳甲精英设计保留。</t>
         </is>
       </c>
     </row>
@@ -18152,6 +18152,73 @@
       <c r="O15" t="inlineStr">
         <is>
           <t>2026-09-23 由业主指示登记为新怪，先不考虑调用。HP/速度/伤害/攻击范围/冷却全部待定：按《字段字典》「怪物与Boss·正式3D数值」要求，这些列必须是 Enemy3D.PROFILES 的正式 3D 基线、不得混用旧 2D 基线，而本怪尚未进入 PROFILES ⇒ 刻意留「待定」而不编造数值。补数时机：接入玩法并写入 Enemy3D.PROFILES 时一并回填。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="54" customHeight="1" s="135">
+      <c r="A16" s="177" t="inlineStr">
+        <is>
+          <t>monster_fat_zombie03</t>
+        </is>
+      </c>
+      <c r="B16" s="177" t="inlineStr">
+        <is>
+          <t>胖子僵尸</t>
+        </is>
+      </c>
+      <c r="C16" s="177" t="inlineStr">
+        <is>
+          <t>fat_zombie03</t>
+        </is>
+      </c>
+      <c r="D16" s="177" t="n">
+        <v>232</v>
+      </c>
+      <c r="E16" s="177" t="n">
+        <v>0.857142857</v>
+      </c>
+      <c r="F16" s="177" t="n">
+        <v>19</v>
+      </c>
+      <c r="G16" s="177" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H16" s="177" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I16" s="177" t="inlineStr">
+        <is>
+          <t>厚血慢速；张臂抱扑拍合；1.2秒前摇/1.3秒收势；轻击上半身反应</t>
+        </is>
+      </c>
+      <c r="J16" s="177" t="inlineStr">
+        <is>
+          <t>远征01纵列/桥心盒；原壳甲默认随机池和锈炉/深渊主题池</t>
+        </is>
+      </c>
+      <c r="K16" s="177" t="inlineStr">
+        <is>
+          <t>通用楼层掉落表；killed一次结算</t>
+        </is>
+      </c>
+      <c r="L16" s="180" t="inlineStr">
+        <is>
+          <t>[已实装]</t>
+        </is>
+      </c>
+      <c r="M16" s="177" t="inlineStr">
+        <is>
+          <t>正式独立怪物，12态/13动画绑定</t>
+        </is>
+      </c>
+      <c r="N16" s="177" t="inlineStr">
+        <is>
+          <t>src/enemy3d/Enemy3D.gd；src/map/MonsterInjector.gd；docs/v0.1/design/胖子僵尸03运行配置.md</t>
+        </is>
+      </c>
+      <c r="O16" s="177" t="inlineStr">
+        <is>
+          <t>D/E为PROFILES源基线；实际第一层生命696、追击0.60m/s、巡逻0.30m/s；内容调用ID=fat_zombie03；资产编号03；已接替壳甲卫兵投放</t>
         </is>
       </c>
     </row>

--- a/docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx
+++ b/docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx
@@ -1,16 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="武器" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命运卡" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物与Boss" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="精英怪" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掉落物品" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段字典" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="基地商店" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="总览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="武器" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="命运卡" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="怪物与Boss" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="精英怪" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="掉落物品" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="字段字典" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="基地商店" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Boss002技能设计" sheetId="9" r:id="rId11"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -18,8 +19,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="28">
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="36">
     <font>
       <name val="Carlito"/>
       <sz val="11"/>
@@ -176,8 +182,50 @@
       <color rgb="FF12333A"/>
       <sz val="11"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF172232"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF172232"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF172232"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF172232"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Microsoft YaHei"/>
+    </font>
   </fonts>
-  <fills count="18">
+  <fills count="26">
     <fill>
       <patternFill/>
     </fill>
@@ -264,8 +312,40 @@
         <fgColor rgb="FF0C6670"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23324A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F4F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23324A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F4F8"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="19">
+  <borders count="21">
     <border/>
     <border>
       <left style="thin">
@@ -459,11 +539,13 @@
         <color rgb="FFB7D1D4"/>
       </bottom>
     </border>
+    <border/>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="182">
+  <cellXfs count="202">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -888,6 +970,58 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="19" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="21" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="29" fillId="21" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="22" borderId="20" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="22" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="33" fillId="22" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="22" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="22" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="24" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="24" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="25" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="33" fillId="25" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="33" fillId="25" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -17290,7 +17424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" style="135" min="1" max="1"/>
@@ -18220,6 +18354,53 @@
         <is>
           <t>D/E为PROFILES源基线；实际第一层生命696、追击0.60m/s、巡逻0.30m/s；内容调用ID=fat_zombie03；资产编号03；已接替壳甲卫兵投放</t>
         </is>
+      </c>
+    </row>
+    <row r="17" ht="120" customHeight="1">
+      <c xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="A17" t="str" s="177">
+        <v>boss_monitor002</v>
+      </c>
+      <c xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="B17" t="str" s="177">
+        <v>MONITOR.EXE 显示器</v>
+      </c>
+      <c xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="C17" t="str" s="177">
+        <v>boss</v>
+      </c>
+      <c xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="D17" t="n" s="177">
+        <v>5200</v>
+      </c>
+      <c xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="E17" t="n" s="177">
+        <v>1.204</v>
+      </c>
+      <c xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="F17" t="n" s="177">
+        <v>24</v>
+      </c>
+      <c xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="G17" t="n" s="177">
+        <v>6</v>
+      </c>
+      <c xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="H17" t="n" s="177">
+        <v>0.65</v>
+      </c>
+      <c xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="I17" t="str" s="177">
+        <v>键盘24 / 数据线20 / 旋转砸地36 / 接地电流每0.8s12；HP66%/33%三阶段</v>
+      </c>
+      <c xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="J17" t="str" s="177">
+        <v>远征01 f00_boss；显式内容ID调用</v>
+      </c>
+      <c xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="K17" t="str" s="177">
+        <v>Enemy3D Boss结算与既有房间奖励</v>
+      </c>
+      <c xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="L17" t="str" s="180">
+        <v>用户动作要求；技能设计r1</v>
+      </c>
+      <c xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="M17" t="str" s="177">
+        <v>active</v>
+      </c>
+      <c xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="N17" t="str" s="177">
+        <v>BossContentCatalog / MonitorBossCombat；Boss002技能设计分页</v>
+      </c>
+      <c xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="O17" t="str" s="177">
+        <v>16 Blender剪辑，十二态；伤害8%韧性击晕4.8s；通电暴击可打断；单帧黄色闪形；独立资产ENM-BOSS-MONITOR002-3D</v>
       </c>
     </row>
   </sheetData>
@@ -26566,4 +26747,641 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="32" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="32" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="32" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="21" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="42" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="42" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="195"/>
+      <c r="B1" s="195"/>
+      <c r="C1" s="195"/>
+      <c r="D1" s="195"/>
+      <c r="E1" s="195"/>
+      <c r="F1" s="195"/>
+      <c r="G1" s="195"/>
+      <c r="H1" s="195"/>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="196" t="str">
+        <v>Boss002 显示器技能设计</v>
+      </c>
+      <c r="B2" s="195"/>
+      <c r="C2" s="195"/>
+      <c r="D2" s="195"/>
+      <c r="E2" s="195"/>
+      <c r="F2" s="195"/>
+      <c r="G2" s="195"/>
+      <c r="H2" s="195"/>
+    </row>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="195"/>
+      <c r="B3" s="195"/>
+      <c r="C3" s="195"/>
+      <c r="D3" s="195"/>
+      <c r="E3" s="195"/>
+      <c r="F3" s="195"/>
+      <c r="G3" s="195"/>
+      <c r="H3" s="195"/>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="195" t="str">
+        <v>内容ID</v>
+      </c>
+      <c r="B4" s="195" t="str">
+        <v>boss_monitor002</v>
+      </c>
+      <c r="C4" s="195"/>
+      <c r="D4" s="195"/>
+      <c r="E4" s="195"/>
+      <c r="F4" s="195" t="str">
+        <v>生命</v>
+      </c>
+      <c r="G4" s="195" t="n">
+        <v>5200</v>
+      </c>
+      <c r="H4" s="195"/>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="195" t="str">
+        <v>AssetID</v>
+      </c>
+      <c r="B5" s="195" t="str">
+        <v>ENM-BOSS-MONITOR002-3D</v>
+      </c>
+      <c r="C5" s="195"/>
+      <c r="D5" s="195"/>
+      <c r="E5" s="195"/>
+      <c r="F5" s="195" t="str">
+        <v>移动m/s</v>
+      </c>
+      <c r="G5" s="195" t="n">
+        <v>1.204</v>
+      </c>
+      <c r="H5" s="195"/>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="195"/>
+      <c r="B6" s="195"/>
+      <c r="C6" s="195"/>
+      <c r="D6" s="195"/>
+      <c r="E6" s="195"/>
+      <c r="F6" s="195"/>
+      <c r="G6" s="195"/>
+      <c r="H6" s="195"/>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="195"/>
+      <c r="B7" s="195"/>
+      <c r="C7" s="195"/>
+      <c r="D7" s="195"/>
+      <c r="E7" s="195"/>
+      <c r="F7" s="195"/>
+      <c r="G7" s="195"/>
+      <c r="H7" s="195"/>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="198" t="str">
+        <v>技能ID</v>
+      </c>
+      <c r="B8" s="198" t="str">
+        <v>名称</v>
+      </c>
+      <c r="C8" s="198" t="str">
+        <v>动作</v>
+      </c>
+      <c r="D8" s="198" t="str">
+        <v>前摇秒</v>
+      </c>
+      <c r="E8" s="198" t="str">
+        <v>生效秒</v>
+      </c>
+      <c r="F8" s="198" t="str">
+        <v>总时长秒</v>
+      </c>
+      <c r="G8" s="198" t="str">
+        <v>范围与伤害</v>
+      </c>
+      <c r="H8" s="198" t="str">
+        <v>打断与特效</v>
+      </c>
+    </row>
+    <row r="9" ht="64" customHeight="1">
+      <c r="A9" s="199" t="str">
+        <v>monitor_keyboard</v>
+      </c>
+      <c r="B9" s="199" t="str">
+        <v>键盘拍地</v>
+      </c>
+      <c r="C9" s="199" t="str">
+        <v>melee_keyboard</v>
+      </c>
+      <c r="D9" s="200" t="n">
+        <v>1.066667</v>
+      </c>
+      <c r="E9" s="200" t="n">
+        <v>1.066667</v>
+      </c>
+      <c r="F9" s="201" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G9" s="199" t="str">
+        <v>前方3.2m，半径1.65m；24</v>
+      </c>
+      <c r="H9" s="199" t="str">
+        <v>单次命中；蓝/玫红；黄闪1帧</v>
+      </c>
+    </row>
+    <row r="10" ht="64" customHeight="1">
+      <c r="A10" s="199" t="str">
+        <v>monitor_cable</v>
+      </c>
+      <c r="B10" s="199" t="str">
+        <v>数据线甩击</v>
+      </c>
+      <c r="C10" s="199" t="str">
+        <v>melee_cable</v>
+      </c>
+      <c r="D10" s="200" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E10" s="200" t="str">
+        <v>0.8–0.967</v>
+      </c>
+      <c r="F10" s="201" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" s="199" t="str">
+        <v>160°弧，半径6m；20</v>
+      </c>
+      <c r="H10" s="199" t="str">
+        <v>螺旋前摇；平滑弧带；每目标1次</v>
+      </c>
+    </row>
+    <row r="11" ht="64" customHeight="1">
+      <c r="A11" s="199" t="str">
+        <v>monitor_spin_slam</v>
+      </c>
+      <c r="B11" s="199" t="str">
+        <v>旋转砸地</v>
+      </c>
+      <c r="C11" s="199" t="str">
+        <v>heavy_spin_slam</v>
+      </c>
+      <c r="D11" s="200" t="n">
+        <v>2.133333</v>
+      </c>
+      <c r="E11" s="200" t="n">
+        <v>2.133333</v>
+      </c>
+      <c r="F11" s="201" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G11" s="199" t="str">
+        <v>前方1.4m，半径5.2m；36</v>
+      </c>
+      <c r="H11" s="199" t="str">
+        <v>3圈屏幕旋转；后仰停顿；黄闪1帧</v>
+      </c>
+    </row>
+    <row r="12" ht="64" customHeight="1">
+      <c r="A12" s="199" t="str">
+        <v>monitor_ground_current</v>
+      </c>
+      <c r="B12" s="199" t="str">
+        <v>接地电流</v>
+      </c>
+      <c r="C12" s="199" t="str">
+        <v>special四段</v>
+      </c>
+      <c r="D12" s="199" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E12" s="199" t="str">
+        <v>每0.8秒脉冲</v>
+      </c>
+      <c r="F12" s="199" t="str">
+        <v>5.1 / 5.9 / 6.7</v>
+      </c>
+      <c r="G12" s="199" t="str">
+        <v>线尖接地点半径7m；每次12</v>
+      </c>
+      <c r="H12" s="199" t="str">
+        <v>通电2.4/3.2/4s；暴击可打断；冷却10s</v>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="195"/>
+      <c r="B13" s="195"/>
+      <c r="C13" s="195"/>
+      <c r="D13" s="195"/>
+      <c r="E13" s="195"/>
+      <c r="F13" s="195"/>
+      <c r="G13" s="195"/>
+      <c r="H13" s="195"/>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="195"/>
+      <c r="B14" s="195"/>
+      <c r="C14" s="195"/>
+      <c r="D14" s="195"/>
+      <c r="E14" s="195"/>
+      <c r="F14" s="195"/>
+      <c r="G14" s="195"/>
+      <c r="H14" s="195"/>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="198" t="str">
+        <v>阶段</v>
+      </c>
+      <c r="B15" s="198" t="str">
+        <v>HP阈值</v>
+      </c>
+      <c r="C15" s="198" t="str">
+        <v>技能序列</v>
+      </c>
+      <c r="D15" s="198"/>
+      <c r="E15" s="198"/>
+      <c r="F15" s="198"/>
+      <c r="G15" s="198"/>
+      <c r="H15" s="198"/>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="195" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" s="195" t="str">
+        <v>&gt;66%</v>
+      </c>
+      <c r="C16" s="195" t="str">
+        <v>键盘、数据线、键盘、重击</v>
+      </c>
+      <c r="D16" s="195"/>
+      <c r="E16" s="195"/>
+      <c r="F16" s="195"/>
+      <c r="G16" s="195"/>
+      <c r="H16" s="195"/>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="195" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" s="195" t="str">
+        <v>≤66%</v>
+      </c>
+      <c r="C17" s="195" t="str">
+        <v>数据线、插线、键盘、重击</v>
+      </c>
+      <c r="D17" s="195"/>
+      <c r="E17" s="195"/>
+      <c r="F17" s="195"/>
+      <c r="G17" s="195"/>
+      <c r="H17" s="195"/>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="195" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" s="195" t="str">
+        <v>≤33%</v>
+      </c>
+      <c r="C18" s="195" t="str">
+        <v>重击、插线、数据线、重击、插线</v>
+      </c>
+      <c r="D18" s="195"/>
+      <c r="E18" s="195"/>
+      <c r="F18" s="195"/>
+      <c r="G18" s="195"/>
+      <c r="H18" s="195"/>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="195"/>
+      <c r="B19" s="195"/>
+      <c r="C19" s="195"/>
+      <c r="D19" s="195"/>
+      <c r="E19" s="195"/>
+      <c r="F19" s="195"/>
+      <c r="G19" s="195"/>
+      <c r="H19" s="195"/>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="198" t="str">
+        <v>状态ID</v>
+      </c>
+      <c r="B20" s="198" t="str">
+        <v>表现动作</v>
+      </c>
+      <c r="C20" s="198"/>
+      <c r="D20" s="198"/>
+      <c r="E20" s="198"/>
+      <c r="F20" s="198"/>
+      <c r="G20" s="198" t="str">
+        <v>规则</v>
+      </c>
+      <c r="H20" s="198"/>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="195" t="str">
+        <v>dormant</v>
+      </c>
+      <c r="B21" s="195" t="str">
+        <v>idle</v>
+      </c>
+      <c r="C21" s="195"/>
+      <c r="D21" s="195"/>
+      <c r="E21" s="195"/>
+      <c r="F21" s="195"/>
+      <c r="G21" s="195" t="str">
+        <v>Enemy3D状态与真实进度单向采样</v>
+      </c>
+      <c r="H21" s="195"/>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="195" t="str">
+        <v>idle</v>
+      </c>
+      <c r="B22" s="195" t="str">
+        <v>idle</v>
+      </c>
+      <c r="C22" s="195"/>
+      <c r="D22" s="195"/>
+      <c r="E22" s="195"/>
+      <c r="F22" s="195"/>
+      <c r="G22" s="195" t="str">
+        <v>Enemy3D状态与真实进度单向采样</v>
+      </c>
+      <c r="H22" s="195"/>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="195" t="str">
+        <v>patrol</v>
+      </c>
+      <c r="B23" s="195" t="str">
+        <v>move</v>
+      </c>
+      <c r="C23" s="195"/>
+      <c r="D23" s="195"/>
+      <c r="E23" s="195"/>
+      <c r="F23" s="195"/>
+      <c r="G23" s="195" t="str">
+        <v>Enemy3D状态与真实进度单向采样</v>
+      </c>
+      <c r="H23" s="195"/>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="195" t="str">
+        <v>alert</v>
+      </c>
+      <c r="B24" s="195" t="str">
+        <v>idle</v>
+      </c>
+      <c r="C24" s="195"/>
+      <c r="D24" s="195"/>
+      <c r="E24" s="195"/>
+      <c r="F24" s="195"/>
+      <c r="G24" s="195" t="str">
+        <v>Enemy3D状态与真实进度单向采样</v>
+      </c>
+      <c r="H24" s="195"/>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="195" t="str">
+        <v>chase</v>
+      </c>
+      <c r="B25" s="195" t="str">
+        <v>move / turn_left/right</v>
+      </c>
+      <c r="C25" s="195"/>
+      <c r="D25" s="195"/>
+      <c r="E25" s="195"/>
+      <c r="F25" s="195"/>
+      <c r="G25" s="195" t="str">
+        <v>Enemy3D状态与真实进度单向采样</v>
+      </c>
+      <c r="H25" s="195"/>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="195" t="str">
+        <v>search</v>
+      </c>
+      <c r="B26" s="195" t="str">
+        <v>move</v>
+      </c>
+      <c r="C26" s="195"/>
+      <c r="D26" s="195"/>
+      <c r="E26" s="195"/>
+      <c r="F26" s="195"/>
+      <c r="G26" s="195" t="str">
+        <v>Enemy3D状态与真实进度单向采样</v>
+      </c>
+      <c r="H26" s="195"/>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="195" t="str">
+        <v>return</v>
+      </c>
+      <c r="B27" s="195" t="str">
+        <v>move</v>
+      </c>
+      <c r="C27" s="195"/>
+      <c r="D27" s="195"/>
+      <c r="E27" s="195"/>
+      <c r="F27" s="195"/>
+      <c r="G27" s="195" t="str">
+        <v>Enemy3D状态与真实进度单向采样</v>
+      </c>
+      <c r="H27" s="195"/>
+    </row>
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="195" t="str">
+        <v>telegraph</v>
+      </c>
+      <c r="B28" s="195" t="str">
+        <v>技能剪辑前摇</v>
+      </c>
+      <c r="C28" s="195"/>
+      <c r="D28" s="195"/>
+      <c r="E28" s="195"/>
+      <c r="F28" s="195"/>
+      <c r="G28" s="195" t="str">
+        <v>Enemy3D状态与真实进度单向采样</v>
+      </c>
+      <c r="H28" s="195"/>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="A29" s="195" t="str">
+        <v>attack</v>
+      </c>
+      <c r="B29" s="195" t="str">
+        <v>技能剪辑生效段 / special_channel</v>
+      </c>
+      <c r="C29" s="195"/>
+      <c r="D29" s="195"/>
+      <c r="E29" s="195"/>
+      <c r="F29" s="195"/>
+      <c r="G29" s="195" t="str">
+        <v>Enemy3D状态与真实进度单向采样</v>
+      </c>
+      <c r="H29" s="195"/>
+    </row>
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="195" t="str">
+        <v>recovery</v>
+      </c>
+      <c r="B30" s="195" t="str">
+        <v>技能剪辑恢复段 / special_recover</v>
+      </c>
+      <c r="C30" s="195"/>
+      <c r="D30" s="195"/>
+      <c r="E30" s="195"/>
+      <c r="F30" s="195"/>
+      <c r="G30" s="195" t="str">
+        <v>Enemy3D状态与真实进度单向采样</v>
+      </c>
+      <c r="H30" s="195"/>
+    </row>
+    <row r="31" ht="26" customHeight="1">
+      <c r="A31" s="195" t="str">
+        <v>stagger</v>
+      </c>
+      <c r="B31" s="195" t="str">
+        <v>hurt / stun_enter→stun_loop→stun_exit</v>
+      </c>
+      <c r="C31" s="195"/>
+      <c r="D31" s="195"/>
+      <c r="E31" s="195"/>
+      <c r="F31" s="195"/>
+      <c r="G31" s="195" t="str">
+        <v>韧性8%：坐下1.4s、坐地2.4s、起身1s</v>
+      </c>
+      <c r="H31" s="195"/>
+    </row>
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="195" t="str">
+        <v>dead</v>
+      </c>
+      <c r="B32" s="195" t="str">
+        <v>dead</v>
+      </c>
+      <c r="C32" s="195"/>
+      <c r="D32" s="195"/>
+      <c r="E32" s="195"/>
+      <c r="F32" s="195"/>
+      <c r="G32" s="195" t="str">
+        <v>死亡2s后回收；根不压扁</v>
+      </c>
+      <c r="H32" s="195"/>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="A33" s="195"/>
+      <c r="B33" s="195"/>
+      <c r="C33" s="195"/>
+      <c r="D33" s="195"/>
+      <c r="E33" s="195"/>
+      <c r="F33" s="195"/>
+      <c r="G33" s="195"/>
+      <c r="H33" s="195"/>
+    </row>
+    <row r="34" ht="40" customHeight="1">
+      <c r="A34" s="195" t="str">
+        <v>规则</v>
+      </c>
+      <c r="B34" s="195" t="str">
+        <v>同层且无遮挡；命中不重复；坐地再受击不重播；读档取消危险技能</v>
+      </c>
+      <c r="C34" s="195"/>
+      <c r="D34" s="195"/>
+      <c r="E34" s="195"/>
+      <c r="F34" s="195"/>
+      <c r="G34" s="195"/>
+      <c r="H34" s="195"/>
+    </row>
+    <row r="35" ht="26" customHeight="1">
+      <c r="A35" s="195"/>
+      <c r="B35" s="195"/>
+      <c r="C35" s="195"/>
+      <c r="D35" s="195"/>
+      <c r="E35" s="195"/>
+      <c r="F35" s="195"/>
+      <c r="G35" s="195"/>
+      <c r="H35" s="195"/>
+    </row>
+    <row r="36" ht="40" customHeight="1">
+      <c r="A36" s="195" t="str">
+        <v>设计主源</v>
+      </c>
+      <c r="B36" s="195" t="str">
+        <v>docs/v0.1/design/Boss002显示器技能设计.md</v>
+      </c>
+      <c r="C36" s="195"/>
+      <c r="D36" s="195"/>
+      <c r="E36" s="195"/>
+      <c r="F36" s="195"/>
+      <c r="G36" s="195"/>
+      <c r="H36" s="195"/>
+    </row>
+    <row r="37" ht="40" customHeight="1">
+      <c r="A37" s="195" t="str">
+        <v>实现源</v>
+      </c>
+      <c r="B37" s="195" t="str">
+        <v>src/enemy3d/MonitorBossCombat.gd</v>
+      </c>
+      <c r="C37" s="195"/>
+      <c r="D37" s="195"/>
+      <c r="E37" s="195"/>
+      <c r="F37" s="195"/>
+      <c r="G37" s="195"/>
+      <c r="H37" s="195"/>
+    </row>
+  </sheetData>
+  <mergeCells>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="C15:H15"/>
+    <mergeCell ref="C16:H16"/>
+    <mergeCell ref="C17:H17"/>
+    <mergeCell ref="C18:H18"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="B21:F21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="B34:H34"/>
+    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="B37:H37"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx
+++ b/docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
     <sheet name="总览" sheetId="1" state="visible" r:id="rId1"/>
@@ -11,7 +11,7 @@
     <sheet name="掉落物品" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="字段字典" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="基地商店" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Boss002技能设计" sheetId="9" r:id="rId11"/>
+    <sheet name="Boss002技能设计" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -19,11 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
-    <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
   <fonts count="36">
     <font>
@@ -183,46 +181,46 @@
       <sz val="11"/>
     </font>
     <font>
+      <name val="Carlito"/>
       <sz val="11"/>
-      <name val="Carlito"/>
     </font>
     <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="FF172232"/>
       <sz val="11"/>
-      <color rgb="FF172232"/>
-      <name val="Microsoft YaHei"/>
     </font>
     <font>
-      <b/>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="FF172232"/>
       <sz val="16"/>
-      <color rgb="FF172232"/>
-      <name val="Microsoft YaHei"/>
     </font>
     <font>
-      <b/>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Microsoft YaHei"/>
     </font>
     <font>
+      <name val="Carlito"/>
       <sz val="11"/>
-      <name val="Carlito"/>
     </font>
     <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="FF172232"/>
       <sz val="11"/>
-      <color rgb="FF172232"/>
-      <name val="Microsoft YaHei"/>
     </font>
     <font>
-      <b/>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="FF172232"/>
       <sz val="16"/>
-      <color rgb="FF172232"/>
-      <name val="Microsoft YaHei"/>
     </font>
     <font>
-      <b/>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Microsoft YaHei"/>
     </font>
   </fonts>
   <fills count="26">
@@ -313,7 +311,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -329,7 +327,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -543,9 +541,9 @@
     <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="22" borderId="20"/>
   </cellStyleXfs>
-  <cellXfs count="202">
+  <cellXfs count="215">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -970,56 +968,89 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="19" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="20" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="21" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="29" fillId="21" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="29" fillId="21" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="29" fillId="21" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="22" borderId="20" xfId="0"/>
-    <xf numFmtId="0" fontId="33" fillId="22" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="33" fillId="22" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="22" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="22" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="22" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="22" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="22" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="22" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="22" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="24" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="24" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="24" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="24" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="25" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="25" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="33" fillId="25" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="33" fillId="25" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="33" fillId="25" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="33" fillId="25" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="25" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="33" fillId="25" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1308,25 +1339,46 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="135">
-      <c r="A1" s="23" t="inlineStr">
+      <c r="A1" s="202" t="inlineStr">
         <is>
           <t>ShellStorm2 游戏内容数据库 v0.1</t>
         </is>
       </c>
+      <c r="B1" s="203" t="n"/>
+      <c r="C1" s="203" t="n"/>
+      <c r="D1" s="203" t="n"/>
+      <c r="E1" s="203" t="n"/>
+      <c r="F1" s="203" t="n"/>
+      <c r="G1" s="203" t="n"/>
+      <c r="H1" s="203" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1" s="135">
-      <c r="A2" s="173" t="inlineStr">
+      <c r="A2" s="204" t="inlineStr">
         <is>
           <t>设计、内容与实现状态的中央索引｜最后校对：2026-08-27｜正式入口：TowerDescent3D.tscn</t>
         </is>
       </c>
+      <c r="B2" s="203" t="n"/>
+      <c r="C2" s="203" t="n"/>
+      <c r="D2" s="203" t="n"/>
+      <c r="E2" s="203" t="n"/>
+      <c r="F2" s="203" t="n"/>
+      <c r="G2" s="203" t="n"/>
+      <c r="H2" s="203" t="n"/>
     </row>
     <row r="3" ht="30" customHeight="1" s="135">
-      <c r="A3" s="25" t="inlineStr">
+      <c r="A3" s="205" t="inlineStr">
         <is>
           <t>绿色字体=已实装；蓝色字体=用户设计；橙色字体=Codex补充。条目存在不等于全部表现与数值已通过最终QA。</t>
         </is>
       </c>
+      <c r="B3" s="203" t="n"/>
+      <c r="C3" s="203" t="n"/>
+      <c r="D3" s="203" t="n"/>
+      <c r="E3" s="203" t="n"/>
+      <c r="F3" s="203" t="n"/>
+      <c r="G3" s="203" t="n"/>
+      <c r="H3" s="203" t="n"/>
     </row>
     <row r="5" ht="34" customHeight="1" s="135">
       <c r="A5" s="12" t="inlineStr">
@@ -1545,11 +1597,18 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="30" t="inlineStr">
+      <c r="A12" s="206" t="inlineStr">
         <is>
           <t>七大系统与文档定位</t>
         </is>
       </c>
+      <c r="B12" s="203" t="n"/>
+      <c r="C12" s="203" t="n"/>
+      <c r="D12" s="203" t="n"/>
+      <c r="E12" s="203" t="n"/>
+      <c r="F12" s="203" t="n"/>
+      <c r="G12" s="203" t="n"/>
+      <c r="H12" s="203" t="n"/>
     </row>
     <row r="13" ht="34" customHeight="1" s="135">
       <c r="A13" s="12" t="inlineStr">
@@ -1874,11 +1933,18 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="33" t="inlineStr">
+      <c r="A22" s="207" t="inlineStr">
         <is>
           <t>发布前检查：稳定ID唯一｜78张卡名唯一｜22大+56小｜36/21/21作用域｜正/逆各50%｜逆位整卡倒置｜旧存档不重投｜实现状态真实</t>
         </is>
       </c>
+      <c r="B22" s="203" t="n"/>
+      <c r="C22" s="203" t="n"/>
+      <c r="D22" s="203" t="n"/>
+      <c r="E22" s="203" t="n"/>
+      <c r="F22" s="203" t="n"/>
+      <c r="G22" s="203" t="n"/>
+      <c r="H22" s="203" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1929,25 +1995,82 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="135">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="208" t="inlineStr">
         <is>
           <t>ShellStorm2 游戏内容数据库｜武器</t>
         </is>
       </c>
+      <c r="B1" s="203" t="n"/>
+      <c r="C1" s="203" t="n"/>
+      <c r="D1" s="203" t="n"/>
+      <c r="E1" s="203" t="n"/>
+      <c r="F1" s="203" t="n"/>
+      <c r="G1" s="203" t="n"/>
+      <c r="H1" s="203" t="n"/>
+      <c r="I1" s="203" t="n"/>
+      <c r="J1" s="203" t="n"/>
+      <c r="K1" s="203" t="n"/>
+      <c r="L1" s="203" t="n"/>
+      <c r="M1" s="203" t="n"/>
+      <c r="N1" s="203" t="n"/>
+      <c r="O1" s="203" t="n"/>
+      <c r="P1" s="203" t="n"/>
+      <c r="Q1" s="203" t="n"/>
+      <c r="R1" s="203" t="n"/>
+      <c r="S1" s="203" t="n"/>
+      <c r="T1" s="203" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1" s="135">
-      <c r="A2" s="174" t="inlineStr">
+      <c r="A2" s="209" t="inlineStr">
         <is>
           <t>正式注册：7远程枪身、2大型近战武器、8子弹、6配件。独立WeaponInstance与普通武器8命运槽已实装；近战四态/三段/命中闭环已验收，逐条最终美术与专属音频继续QA。</t>
         </is>
       </c>
+      <c r="B2" s="203" t="n"/>
+      <c r="C2" s="203" t="n"/>
+      <c r="D2" s="203" t="n"/>
+      <c r="E2" s="203" t="n"/>
+      <c r="F2" s="203" t="n"/>
+      <c r="G2" s="203" t="n"/>
+      <c r="H2" s="203" t="n"/>
+      <c r="I2" s="203" t="n"/>
+      <c r="J2" s="203" t="n"/>
+      <c r="K2" s="203" t="n"/>
+      <c r="L2" s="203" t="n"/>
+      <c r="M2" s="203" t="n"/>
+      <c r="N2" s="203" t="n"/>
+      <c r="O2" s="203" t="n"/>
+      <c r="P2" s="203" t="n"/>
+      <c r="Q2" s="203" t="n"/>
+      <c r="R2" s="203" t="n"/>
+      <c r="S2" s="203" t="n"/>
+      <c r="T2" s="203" t="n"/>
     </row>
     <row r="3" ht="30" customHeight="1" s="135">
-      <c r="A3" s="174" t="inlineStr">
+      <c r="A3" s="209" t="inlineStr">
         <is>
           <t>字体颜色：绿色=已实装；蓝色=用户设计；橙色=Codex补充。实现状态需结合事实源判断。</t>
         </is>
       </c>
+      <c r="B3" s="203" t="n"/>
+      <c r="C3" s="203" t="n"/>
+      <c r="D3" s="203" t="n"/>
+      <c r="E3" s="203" t="n"/>
+      <c r="F3" s="203" t="n"/>
+      <c r="G3" s="203" t="n"/>
+      <c r="H3" s="203" t="n"/>
+      <c r="I3" s="203" t="n"/>
+      <c r="J3" s="203" t="n"/>
+      <c r="K3" s="203" t="n"/>
+      <c r="L3" s="203" t="n"/>
+      <c r="M3" s="203" t="n"/>
+      <c r="N3" s="203" t="n"/>
+      <c r="O3" s="203" t="n"/>
+      <c r="P3" s="203" t="n"/>
+      <c r="Q3" s="203" t="n"/>
+      <c r="R3" s="203" t="n"/>
+      <c r="S3" s="203" t="n"/>
+      <c r="T3" s="203" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1" s="135">
       <c r="A4" s="176" t="inlineStr">
@@ -2541,12 +2664,12 @@
       </c>
       <c r="G9" s="177" t="inlineStr">
         <is>
-          <t>damage=5；spread=-0.05</t>
+          <t>damage=15；spread=-0.05</t>
         </is>
       </c>
       <c r="H9" s="177" t="inlineStr">
         <is>
-          <t>装配后提供damage=5；spread=-0.05；修饰方向：crit、accuracy</t>
+          <t>装配后提供damage=15；spread=-0.05；修饰方向：crit、accuracy</t>
         </is>
       </c>
       <c r="I9" s="177" t="inlineStr">
@@ -3631,17 +3754,17 @@
       </c>
       <c r="G19" s="177" t="inlineStr">
         <is>
-          <t>bullet_count=1；charge_time=1.2；damage=30；fire_rate=1.5；magazine_size=4；reload_time=3；spread=0.05</t>
+          <t>bullet_count=1；charge_time=1.2；damage=880；fire_rate=1.5；magazine_size=4；reload_time=3；spread=0.05；explosion_damage_scale=0.630631（中心范围伤害560）</t>
         </is>
       </c>
       <c r="H19" s="177" t="inlineStr">
         <is>
-          <t>蓄力时间越长伤害越高，超蓄力后弹体变大并附带穿透。左键装备为当前主武器。</t>
+          <t>蓄力时间越长伤害越高；命中时产生范围爆炸（中心560）；超蓄力后弹体变大。左键装备为当前主武器。</t>
         </is>
       </c>
       <c r="I19" s="177" t="inlineStr">
         <is>
-          <t>标签：charge、蓄力、high_damage</t>
+          <t>标签：charge、蓄力、high_damage、explosive</t>
         </is>
       </c>
       <c r="J19" s="177" t="inlineStr">
@@ -3747,7 +3870,7 @@
       </c>
       <c r="G20" s="177" t="inlineStr">
         <is>
-          <t>bullet_count=1；damage=38；fire_rate=0.8；magazine_size=3；reload_time=4；spread=0.1</t>
+          <t>bullet_count=1；damage=250；fire_rate=1；magazine_size=3；reload_time=4；spread=0.1；explosion_damage_scale=0.697675（中心范围伤害180）</t>
         </is>
       </c>
       <c r="H20" s="177" t="inlineStr">
@@ -3979,7 +4102,7 @@
       </c>
       <c r="G22" s="177" t="inlineStr">
         <is>
-          <t>bullet_count=1；damage=18；fire_rate=3.5；magazine_size=12；reload_time=1.5；spread=0.03</t>
+          <t>bullet_count=1；damage=25；fire_rate=3.5；magazine_size=12；reload_time=1.5；spread=0.03</t>
         </is>
       </c>
       <c r="H22" s="177" t="inlineStr">
@@ -4095,7 +4218,7 @@
       </c>
       <c r="G23" s="177" t="inlineStr">
         <is>
-          <t>bullet_count=1；damage=22；fire_rate=6；magazine_size=30；reload_time=2.2；spread=0.07</t>
+          <t>bullet_count=1；damage=60；fire_rate=6；magazine_size=30；reload_time=2.2；spread=0.07</t>
         </is>
       </c>
       <c r="H23" s="177" t="inlineStr">
@@ -4211,7 +4334,7 @@
       </c>
       <c r="G24" s="177" t="inlineStr">
         <is>
-          <t>bullet_count=5；damage=12；fire_rate=1.2；magazine_size=6；reload_time=3；spread=0.35</t>
+          <t>bullet_count=5；damage=45；fire_rate=1.2；magazine_size=6；reload_time=3；spread=0.35</t>
         </is>
       </c>
       <c r="H24" s="177" t="inlineStr">
@@ -4327,7 +4450,7 @@
       </c>
       <c r="G25" s="177" t="inlineStr">
         <is>
-          <t>bullet_count=1；damage=55；fire_rate=1；magazine_size=5；reload_time=3.5；spread=0.01</t>
+          <t>bullet_count=1；damage=380；fire_rate=1；magazine_size=5；reload_time=3.5；spread=0.01</t>
         </is>
       </c>
       <c r="H25" s="177" t="inlineStr">
@@ -4805,25 +4928,121 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" s="135">
-      <c r="A1" s="59" t="inlineStr">
+      <c r="A1" s="210" t="inlineStr">
         <is>
           <t>ShellStorm2 游戏内容数据库｜命运塔罗</t>
         </is>
       </c>
+      <c r="B1" s="203" t="n"/>
+      <c r="C1" s="203" t="n"/>
+      <c r="D1" s="203" t="n"/>
+      <c r="E1" s="203" t="n"/>
+      <c r="F1" s="203" t="n"/>
+      <c r="G1" s="203" t="n"/>
+      <c r="H1" s="203" t="n"/>
+      <c r="I1" s="203" t="n"/>
+      <c r="J1" s="203" t="n"/>
+      <c r="K1" s="203" t="n"/>
+      <c r="L1" s="203" t="n"/>
+      <c r="M1" s="203" t="n"/>
+      <c r="N1" s="203" t="n"/>
+      <c r="O1" s="203" t="n"/>
+      <c r="P1" s="203" t="n"/>
+      <c r="Q1" s="203" t="n"/>
+      <c r="R1" s="203" t="n"/>
+      <c r="S1" s="203" t="n"/>
+      <c r="T1" s="203" t="n"/>
+      <c r="U1" s="203" t="n"/>
+      <c r="V1" s="203" t="n"/>
+      <c r="W1" s="203" t="n"/>
+      <c r="X1" s="203" t="n"/>
+      <c r="Y1" s="203" t="n"/>
+      <c r="Z1" s="203" t="n"/>
+      <c r="AA1" s="203" t="n"/>
+      <c r="AB1" s="203" t="n"/>
+      <c r="AC1" s="203" t="n"/>
+      <c r="AD1" s="203" t="n"/>
+      <c r="AE1" s="203" t="n"/>
+      <c r="AF1" s="203" t="n"/>
+      <c r="AG1" s="203" t="n"/>
     </row>
     <row r="2" ht="34" customHeight="1" s="135">
-      <c r="A2" s="62" t="inlineStr">
+      <c r="A2" s="211" t="inlineStr">
         <is>
           <t>78张完整牌组：48张现有卡已接入塔罗名称、正/逆位效果快照、50%/50%方位与代码翻牌；新增30张须完成独立玩法执行器后再进入正式池。</t>
         </is>
       </c>
+      <c r="B2" s="203" t="n"/>
+      <c r="C2" s="203" t="n"/>
+      <c r="D2" s="203" t="n"/>
+      <c r="E2" s="203" t="n"/>
+      <c r="F2" s="203" t="n"/>
+      <c r="G2" s="203" t="n"/>
+      <c r="H2" s="203" t="n"/>
+      <c r="I2" s="203" t="n"/>
+      <c r="J2" s="203" t="n"/>
+      <c r="K2" s="203" t="n"/>
+      <c r="L2" s="203" t="n"/>
+      <c r="M2" s="203" t="n"/>
+      <c r="N2" s="203" t="n"/>
+      <c r="O2" s="203" t="n"/>
+      <c r="P2" s="203" t="n"/>
+      <c r="Q2" s="203" t="n"/>
+      <c r="R2" s="203" t="n"/>
+      <c r="S2" s="203" t="n"/>
+      <c r="T2" s="203" t="n"/>
+      <c r="U2" s="203" t="n"/>
+      <c r="V2" s="203" t="n"/>
+      <c r="W2" s="203" t="n"/>
+      <c r="X2" s="203" t="n"/>
+      <c r="Y2" s="203" t="n"/>
+      <c r="Z2" s="203" t="n"/>
+      <c r="AA2" s="203" t="n"/>
+      <c r="AB2" s="203" t="n"/>
+      <c r="AC2" s="203" t="n"/>
+      <c r="AD2" s="203" t="n"/>
+      <c r="AE2" s="203" t="n"/>
+      <c r="AF2" s="203" t="n"/>
+      <c r="AG2" s="203" t="n"/>
     </row>
     <row r="3" ht="34" customHeight="1" s="135">
-      <c r="A3" s="62" t="inlineStr">
+      <c r="A3" s="211" t="inlineStr">
         <is>
           <t>每张卡先抽身份，再以50%/50%独立抽正位或逆位；同名、同稳定ID、同收藏条目。逆位只倒置图案/框体，名称、说明、数值和目标文字始终正向。</t>
         </is>
       </c>
+      <c r="B3" s="203" t="n"/>
+      <c r="C3" s="203" t="n"/>
+      <c r="D3" s="203" t="n"/>
+      <c r="E3" s="203" t="n"/>
+      <c r="F3" s="203" t="n"/>
+      <c r="G3" s="203" t="n"/>
+      <c r="H3" s="203" t="n"/>
+      <c r="I3" s="203" t="n"/>
+      <c r="J3" s="203" t="n"/>
+      <c r="K3" s="203" t="n"/>
+      <c r="L3" s="203" t="n"/>
+      <c r="M3" s="203" t="n"/>
+      <c r="N3" s="203" t="n"/>
+      <c r="O3" s="203" t="n"/>
+      <c r="P3" s="203" t="n"/>
+      <c r="Q3" s="203" t="n"/>
+      <c r="R3" s="203" t="n"/>
+      <c r="S3" s="203" t="n"/>
+      <c r="T3" s="203" t="n"/>
+      <c r="U3" s="203" t="n"/>
+      <c r="V3" s="203" t="n"/>
+      <c r="W3" s="203" t="n"/>
+      <c r="X3" s="203" t="n"/>
+      <c r="Y3" s="203" t="n"/>
+      <c r="Z3" s="203" t="n"/>
+      <c r="AA3" s="203" t="n"/>
+      <c r="AB3" s="203" t="n"/>
+      <c r="AC3" s="203" t="n"/>
+      <c r="AD3" s="203" t="n"/>
+      <c r="AE3" s="203" t="n"/>
+      <c r="AF3" s="203" t="n"/>
+      <c r="AG3" s="203" t="n"/>
     </row>
     <row r="4" ht="42" customHeight="1" s="135">
       <c r="A4" s="68" t="inlineStr">
@@ -17445,25 +17664,67 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="135">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="208" t="inlineStr">
         <is>
           <t>ShellStorm2 游戏内容数据库｜怪物与 Boss</t>
         </is>
       </c>
+      <c r="B1" s="203" t="n"/>
+      <c r="C1" s="203" t="n"/>
+      <c r="D1" s="203" t="n"/>
+      <c r="E1" s="203" t="n"/>
+      <c r="F1" s="203" t="n"/>
+      <c r="G1" s="203" t="n"/>
+      <c r="H1" s="203" t="n"/>
+      <c r="I1" s="203" t="n"/>
+      <c r="J1" s="203" t="n"/>
+      <c r="K1" s="203" t="n"/>
+      <c r="L1" s="203" t="n"/>
+      <c r="M1" s="203" t="n"/>
+      <c r="N1" s="203" t="n"/>
+      <c r="O1" s="203" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1" s="135">
-      <c r="A2" s="174" t="inlineStr">
+      <c r="A2" s="209" t="inlineStr">
         <is>
           <t>数值采用Enemy3D.PROFILES正式3D基线；MonsterInjector旧2D基线仅换算楼层/主题倍率，不再作为玩家可见生命值。</t>
         </is>
       </c>
+      <c r="B2" s="203" t="n"/>
+      <c r="C2" s="203" t="n"/>
+      <c r="D2" s="203" t="n"/>
+      <c r="E2" s="203" t="n"/>
+      <c r="F2" s="203" t="n"/>
+      <c r="G2" s="203" t="n"/>
+      <c r="H2" s="203" t="n"/>
+      <c r="I2" s="203" t="n"/>
+      <c r="J2" s="203" t="n"/>
+      <c r="K2" s="203" t="n"/>
+      <c r="L2" s="203" t="n"/>
+      <c r="M2" s="203" t="n"/>
+      <c r="N2" s="203" t="n"/>
+      <c r="O2" s="203" t="n"/>
     </row>
     <row r="3" ht="30" customHeight="1" s="135">
-      <c r="A3" s="174" t="inlineStr">
+      <c r="A3" s="209" t="inlineStr">
         <is>
           <t>字体颜色：绿色=已实装；蓝色=用户设计；橙色=Codex补充。实现状态需结合事实源判断。</t>
         </is>
       </c>
+      <c r="B3" s="203" t="n"/>
+      <c r="C3" s="203" t="n"/>
+      <c r="D3" s="203" t="n"/>
+      <c r="E3" s="203" t="n"/>
+      <c r="F3" s="203" t="n"/>
+      <c r="G3" s="203" t="n"/>
+      <c r="H3" s="203" t="n"/>
+      <c r="I3" s="203" t="n"/>
+      <c r="J3" s="203" t="n"/>
+      <c r="K3" s="203" t="n"/>
+      <c r="L3" s="203" t="n"/>
+      <c r="M3" s="203" t="n"/>
+      <c r="N3" s="203" t="n"/>
+      <c r="O3" s="203" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1" s="135">
       <c r="A4" s="176" t="inlineStr">
@@ -18356,51 +18617,71 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="120" customHeight="1">
-      <c xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="A17" t="str" s="177">
-        <v>boss_monitor002</v>
-      </c>
-      <c xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="B17" t="str" s="177">
-        <v>MONITOR.EXE 显示器</v>
-      </c>
-      <c xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="C17" t="str" s="177">
-        <v>boss</v>
-      </c>
-      <c xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="D17" t="n" s="177">
+    <row r="17" ht="120" customHeight="1" s="135">
+      <c r="A17" s="177" t="inlineStr">
+        <is>
+          <t>boss_monitor002</t>
+        </is>
+      </c>
+      <c r="B17" s="177" t="inlineStr">
+        <is>
+          <t>MONITOR.EXE 显示器</t>
+        </is>
+      </c>
+      <c r="C17" s="177" t="inlineStr">
+        <is>
+          <t>boss</t>
+        </is>
+      </c>
+      <c r="D17" s="177" t="n">
         <v>5200</v>
       </c>
-      <c xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="E17" s="177" t="n">
+      <c r="E17" s="177" t="n">
         <v>3.612</v>
       </c>
-      <c xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="F17" t="n" s="177">
+      <c r="F17" s="177" t="n">
         <v>24</v>
       </c>
-      <c xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="G17" t="n" s="177">
+      <c r="G17" s="177" t="n">
         <v>6</v>
       </c>
-      <c xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="H17" t="n" s="177">
+      <c r="H17" s="177" t="n">
         <v>0.65</v>
       </c>
-      <c xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="I17" t="str" s="177">
-        <v>键盘24 / 数据线20 / 旋转砸地36 / 接地电流每0.8s12；HP66%/33%三阶段</v>
-      </c>
-      <c xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="J17" t="str" s="177">
-        <v>远征01 f00_boss；显式内容ID调用</v>
-      </c>
-      <c xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="K17" t="str" s="177">
-        <v>Enemy3D Boss结算与既有房间奖励</v>
-      </c>
-      <c xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="L17" s="180" t="str">
-        <v>用户10米激活要求；技能设计r4</v>
-      </c>
-      <c xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="M17" t="str" s="177">
-        <v>active</v>
-      </c>
-      <c xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="N17" t="str" s="177">
-        <v>BossContentCatalog / MonitorBossCombat；Boss002技能设计分页</v>
-      </c>
-      <c xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="O17" s="177" t="str">
-        <v>17 Blender剪辑；首次activate6.4s（非伤害技能），四技能/十二态；伤害8%韧性击晕4.8s；通电暴击可打断；独立资产ENM-BOSS-MONITOR002-3D；首次10米触发，出场播完后战斗；显示器Boss由正式触发盒生成于房间中心（局部X/Z=0），初始面向南方（世界+Z）。移动速度由1.204提高至3.612米/秒（3倍；内容speed=123.84）。10米激活及6.4秒出场规则保持。</v>
+      <c r="I17" s="177" t="inlineStr">
+        <is>
+          <t>键盘24 / 数据线20 / 旋转砸地36 / 接地电流每0.8s12；HP66%/33%三阶段</t>
+        </is>
+      </c>
+      <c r="J17" s="177" t="inlineStr">
+        <is>
+          <t>远征01 f00_boss；显式内容ID调用</t>
+        </is>
+      </c>
+      <c r="K17" s="177" t="inlineStr">
+        <is>
+          <t>Enemy3D Boss结算与既有房间奖励</t>
+        </is>
+      </c>
+      <c r="L17" s="180" t="inlineStr">
+        <is>
+          <t>用户10米激活要求；技能设计r4</t>
+        </is>
+      </c>
+      <c r="M17" s="177" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="N17" s="177" t="inlineStr">
+        <is>
+          <t>BossContentCatalog / MonitorBossCombat；Boss002技能设计分页</t>
+        </is>
+      </c>
+      <c r="O17" s="177" t="inlineStr">
+        <is>
+          <t>17 Blender剪辑；首次activate6.4s（非伤害技能），四技能/十二态；伤害8%韧性击晕4.8s；通电暴击可打断；独立资产ENM-BOSS-MONITOR002-3D；首次10米触发，出场播完后战斗；显示器Boss由正式触发盒生成于房间中心（局部X/Z=0），初始面向南方（世界+Z）。移动速度由1.204提高至3.612米/秒（3倍；内容speed=123.84）。10米激活及6.4秒出场规则保持。</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -18445,25 +18726,67 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="135">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="208" t="inlineStr">
         <is>
           <t>ShellStorm2 游戏内容数据库｜12只唯一精英</t>
         </is>
       </c>
+      <c r="B1" s="203" t="n"/>
+      <c r="C1" s="203" t="n"/>
+      <c r="D1" s="203" t="n"/>
+      <c r="E1" s="203" t="n"/>
+      <c r="F1" s="203" t="n"/>
+      <c r="G1" s="203" t="n"/>
+      <c r="H1" s="203" t="n"/>
+      <c r="I1" s="203" t="n"/>
+      <c r="J1" s="203" t="n"/>
+      <c r="K1" s="203" t="n"/>
+      <c r="L1" s="203" t="n"/>
+      <c r="M1" s="203" t="n"/>
+      <c r="N1" s="203" t="n"/>
+      <c r="O1" s="203" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1" s="135">
-      <c r="A2" s="174" t="inlineStr">
+      <c r="A2" s="209" t="inlineStr">
         <is>
           <t>名册固定12只并保持稳定ID。2026-08-27：首只背枪的裂口爬虫已完成独立资产、唯一投放和跨局成长闭环；其余11只保留设计与行为雏形但未投放。</t>
         </is>
       </c>
+      <c r="B2" s="203" t="n"/>
+      <c r="C2" s="203" t="n"/>
+      <c r="D2" s="203" t="n"/>
+      <c r="E2" s="203" t="n"/>
+      <c r="F2" s="203" t="n"/>
+      <c r="G2" s="203" t="n"/>
+      <c r="H2" s="203" t="n"/>
+      <c r="I2" s="203" t="n"/>
+      <c r="J2" s="203" t="n"/>
+      <c r="K2" s="203" t="n"/>
+      <c r="L2" s="203" t="n"/>
+      <c r="M2" s="203" t="n"/>
+      <c r="N2" s="203" t="n"/>
+      <c r="O2" s="203" t="n"/>
     </row>
     <row r="3" ht="30" customHeight="1" s="135">
-      <c r="A3" s="174" t="inlineStr">
+      <c r="A3" s="209" t="inlineStr">
         <is>
           <t>字体颜色：绿色=已实装；蓝色=用户设计；橙色=Codex补充。实现状态需结合事实源判断。</t>
         </is>
       </c>
+      <c r="B3" s="203" t="n"/>
+      <c r="C3" s="203" t="n"/>
+      <c r="D3" s="203" t="n"/>
+      <c r="E3" s="203" t="n"/>
+      <c r="F3" s="203" t="n"/>
+      <c r="G3" s="203" t="n"/>
+      <c r="H3" s="203" t="n"/>
+      <c r="I3" s="203" t="n"/>
+      <c r="J3" s="203" t="n"/>
+      <c r="K3" s="203" t="n"/>
+      <c r="L3" s="203" t="n"/>
+      <c r="M3" s="203" t="n"/>
+      <c r="N3" s="203" t="n"/>
+      <c r="O3" s="203" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1" s="135">
       <c r="A4" s="176" t="inlineStr">
@@ -19516,25 +19839,67 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="135">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="208" t="inlineStr">
         <is>
           <t>ShellStorm2 游戏内容数据库｜掉落物品</t>
         </is>
       </c>
+      <c r="B1" s="203" t="n"/>
+      <c r="C1" s="203" t="n"/>
+      <c r="D1" s="203" t="n"/>
+      <c r="E1" s="203" t="n"/>
+      <c r="F1" s="203" t="n"/>
+      <c r="G1" s="203" t="n"/>
+      <c r="H1" s="203" t="n"/>
+      <c r="I1" s="203" t="n"/>
+      <c r="J1" s="203" t="n"/>
+      <c r="K1" s="203" t="n"/>
+      <c r="L1" s="203" t="n"/>
+      <c r="M1" s="203" t="n"/>
+      <c r="N1" s="203" t="n"/>
+      <c r="O1" s="203" t="n"/>
     </row>
     <row r="2" ht="31.5" customHeight="1" s="135">
-      <c r="A2" s="174" t="inlineStr">
+      <c r="A2" s="209" t="inlineStr">
         <is>
           <t>导入ItemRegistry当前44条正式记录与1条设计契约条目（Boss下行专用钥匙），共45条；大型电池、电芯包和三档手电模块均使用正式运行ID。价格0不自动代表免费，进度物不进入普通商店。</t>
         </is>
       </c>
+      <c r="B2" s="203" t="n"/>
+      <c r="C2" s="203" t="n"/>
+      <c r="D2" s="203" t="n"/>
+      <c r="E2" s="203" t="n"/>
+      <c r="F2" s="203" t="n"/>
+      <c r="G2" s="203" t="n"/>
+      <c r="H2" s="203" t="n"/>
+      <c r="I2" s="203" t="n"/>
+      <c r="J2" s="203" t="n"/>
+      <c r="K2" s="203" t="n"/>
+      <c r="L2" s="203" t="n"/>
+      <c r="M2" s="203" t="n"/>
+      <c r="N2" s="203" t="n"/>
+      <c r="O2" s="203" t="n"/>
     </row>
     <row r="3" ht="30" customHeight="1" s="135">
-      <c r="A3" s="174" t="inlineStr">
+      <c r="A3" s="209" t="inlineStr">
         <is>
           <t>字体颜色：绿色=已实装；蓝色=用户设计；橙色=Codex补充。实现状态需结合事实源判断。</t>
         </is>
       </c>
+      <c r="B3" s="203" t="n"/>
+      <c r="C3" s="203" t="n"/>
+      <c r="D3" s="203" t="n"/>
+      <c r="E3" s="203" t="n"/>
+      <c r="F3" s="203" t="n"/>
+      <c r="G3" s="203" t="n"/>
+      <c r="H3" s="203" t="n"/>
+      <c r="I3" s="203" t="n"/>
+      <c r="J3" s="203" t="n"/>
+      <c r="K3" s="203" t="n"/>
+      <c r="L3" s="203" t="n"/>
+      <c r="M3" s="203" t="n"/>
+      <c r="N3" s="203" t="n"/>
+      <c r="O3" s="203" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1" s="135">
       <c r="A4" s="176" t="inlineStr">
@@ -23504,25 +23869,46 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="135">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="208" t="inlineStr">
         <is>
           <t>ShellStorm2 游戏内容数据库｜字段字典</t>
         </is>
       </c>
+      <c r="B1" s="203" t="n"/>
+      <c r="C1" s="203" t="n"/>
+      <c r="D1" s="203" t="n"/>
+      <c r="E1" s="203" t="n"/>
+      <c r="F1" s="203" t="n"/>
+      <c r="G1" s="203" t="n"/>
+      <c r="H1" s="203" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1" s="135">
-      <c r="A2" s="174" t="inlineStr">
+      <c r="A2" s="209" t="inlineStr">
         <is>
           <t>字段字典内容调整至人的共同契约。新增命运塔罗的阿尔卡那、花色、正/逆位概率、参数快照与翻牌字段。</t>
         </is>
       </c>
+      <c r="B2" s="203" t="n"/>
+      <c r="C2" s="203" t="n"/>
+      <c r="D2" s="203" t="n"/>
+      <c r="E2" s="203" t="n"/>
+      <c r="F2" s="203" t="n"/>
+      <c r="G2" s="203" t="n"/>
+      <c r="H2" s="203" t="n"/>
     </row>
     <row r="3" ht="30" customHeight="1" s="135">
-      <c r="A3" s="174" t="inlineStr">
+      <c r="A3" s="209" t="inlineStr">
         <is>
           <t>字体颜色：绿色=已实装；蓝色=用户设计；橙色=Codex补充。实现状态需结合事实源判断。</t>
         </is>
       </c>
+      <c r="B3" s="203" t="n"/>
+      <c r="C3" s="203" t="n"/>
+      <c r="D3" s="203" t="n"/>
+      <c r="E3" s="203" t="n"/>
+      <c r="F3" s="203" t="n"/>
+      <c r="G3" s="203" t="n"/>
+      <c r="H3" s="203" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1" s="135">
       <c r="A4" s="176" t="inlineStr">
@@ -26047,11 +26433,28 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" s="135">
-      <c r="A1" s="157" t="inlineStr">
+      <c r="A1" s="212" t="inlineStr">
         <is>
           <t>基地自动贩卖机｜固定货物清单 v0.1</t>
         </is>
       </c>
+      <c r="B1" s="203" t="n"/>
+      <c r="C1" s="203" t="n"/>
+      <c r="D1" s="203" t="n"/>
+      <c r="E1" s="203" t="n"/>
+      <c r="F1" s="203" t="n"/>
+      <c r="G1" s="203" t="n"/>
+      <c r="H1" s="203" t="n"/>
+      <c r="I1" s="203" t="n"/>
+      <c r="J1" s="203" t="n"/>
+      <c r="K1" s="203" t="n"/>
+      <c r="L1" s="203" t="n"/>
+      <c r="M1" s="203" t="n"/>
+      <c r="N1" s="203" t="n"/>
+      <c r="O1" s="203" t="n"/>
+      <c r="P1" s="203" t="n"/>
+      <c r="Q1" s="203" t="n"/>
+      <c r="R1" s="203" t="n"/>
     </row>
     <row r="2" ht="31.5" customHeight="1" s="135">
       <c r="A2" s="161" t="inlineStr">
@@ -26751,635 +27154,824 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="32" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="32" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="32" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="14" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="21" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="42" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="42" hidden="0" customWidth="1"/>
+    <col width="32" customWidth="1" style="135" min="1" max="1"/>
+    <col width="32" customWidth="1" style="135" min="2" max="2"/>
+    <col width="32" customWidth="1" style="135" min="3" max="3"/>
+    <col width="14" customWidth="1" style="135" min="4" max="4"/>
+    <col width="18" customWidth="1" style="135" min="5" max="5"/>
+    <col width="21" customWidth="1" style="135" min="6" max="6"/>
+    <col width="42" customWidth="1" style="135" min="7" max="7"/>
+    <col width="42" customWidth="1" style="135" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="195"/>
-      <c r="B1" s="195"/>
-      <c r="C1" s="195"/>
-      <c r="D1" s="195"/>
-      <c r="E1" s="195"/>
-      <c r="F1" s="195"/>
-      <c r="G1" s="195"/>
-      <c r="H1" s="195"/>
-    </row>
-    <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="196" t="str">
-        <v>Boss002 显示器技能设计</v>
-      </c>
-      <c r="B2" s="195"/>
-      <c r="C2" s="195"/>
-      <c r="D2" s="195"/>
-      <c r="E2" s="195"/>
-      <c r="F2" s="195"/>
-      <c r="G2" s="195"/>
-      <c r="H2" s="195"/>
-    </row>
-    <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="195"/>
-      <c r="B3" s="195"/>
-      <c r="C3" s="195"/>
-      <c r="D3" s="195"/>
-      <c r="E3" s="195"/>
-      <c r="F3" s="195"/>
-      <c r="G3" s="195"/>
-      <c r="H3" s="195"/>
-    </row>
-    <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="195" t="str">
-        <v>内容ID</v>
-      </c>
-      <c r="B4" s="195" t="str">
-        <v>boss_monitor002</v>
-      </c>
-      <c r="C4" s="195"/>
-      <c r="D4" s="195"/>
-      <c r="E4" s="195"/>
-      <c r="F4" s="195" t="str">
-        <v>生命</v>
+    <row r="1" ht="26" customHeight="1" s="135">
+      <c r="A1" s="195" t="n"/>
+      <c r="B1" s="195" t="n"/>
+      <c r="C1" s="195" t="n"/>
+      <c r="D1" s="195" t="n"/>
+      <c r="E1" s="195" t="n"/>
+      <c r="F1" s="195" t="n"/>
+      <c r="G1" s="195" t="n"/>
+      <c r="H1" s="195" t="n"/>
+    </row>
+    <row r="2" ht="26" customHeight="1" s="135">
+      <c r="A2" s="196" t="inlineStr">
+        <is>
+          <t>Boss002 显示器技能设计</t>
+        </is>
+      </c>
+      <c r="B2" s="203" t="n"/>
+      <c r="C2" s="203" t="n"/>
+      <c r="D2" s="203" t="n"/>
+      <c r="E2" s="203" t="n"/>
+      <c r="F2" s="203" t="n"/>
+      <c r="G2" s="203" t="n"/>
+      <c r="H2" s="203" t="n"/>
+    </row>
+    <row r="3" ht="26" customHeight="1" s="135">
+      <c r="A3" s="195" t="n"/>
+      <c r="B3" s="195" t="n"/>
+      <c r="C3" s="195" t="n"/>
+      <c r="D3" s="195" t="n"/>
+      <c r="E3" s="195" t="n"/>
+      <c r="F3" s="195" t="n"/>
+      <c r="G3" s="195" t="n"/>
+      <c r="H3" s="195" t="n"/>
+    </row>
+    <row r="4" ht="26" customHeight="1" s="135">
+      <c r="A4" s="195" t="inlineStr">
+        <is>
+          <t>内容ID</t>
+        </is>
+      </c>
+      <c r="B4" s="195" t="inlineStr">
+        <is>
+          <t>boss_monitor002</t>
+        </is>
+      </c>
+      <c r="C4" s="195" t="n"/>
+      <c r="D4" s="195" t="n"/>
+      <c r="E4" s="195" t="n"/>
+      <c r="F4" s="195" t="inlineStr">
+        <is>
+          <t>生命</t>
+        </is>
       </c>
       <c r="G4" s="195" t="n">
         <v>5200</v>
       </c>
-      <c r="H4" s="195"/>
-    </row>
-    <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="195" t="str">
-        <v>AssetID</v>
-      </c>
-      <c r="B5" s="195" t="str">
-        <v>ENM-BOSS-MONITOR002-3D</v>
-      </c>
-      <c r="C5" s="195"/>
-      <c r="D5" s="195"/>
-      <c r="E5" s="195"/>
-      <c r="F5" s="195" t="str">
-        <v>移动m/s</v>
+      <c r="H4" s="195" t="n"/>
+    </row>
+    <row r="5" ht="26" customHeight="1" s="135">
+      <c r="A5" s="195" t="inlineStr">
+        <is>
+          <t>AssetID</t>
+        </is>
+      </c>
+      <c r="B5" s="195" t="inlineStr">
+        <is>
+          <t>ENM-BOSS-MONITOR002-3D</t>
+        </is>
+      </c>
+      <c r="C5" s="195" t="n"/>
+      <c r="D5" s="195" t="n"/>
+      <c r="E5" s="195" t="n"/>
+      <c r="F5" s="195" t="inlineStr">
+        <is>
+          <t>移动m/s</t>
+        </is>
       </c>
       <c r="G5" s="195" t="n">
         <v>1.204</v>
       </c>
-      <c r="H5" s="195"/>
-    </row>
-    <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="195"/>
-      <c r="B6" s="195"/>
-      <c r="C6" s="195"/>
-      <c r="D6" s="195"/>
-      <c r="E6" s="195"/>
-      <c r="F6" s="195"/>
-      <c r="G6" s="195"/>
-      <c r="H6" s="195"/>
-    </row>
-    <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="195"/>
-      <c r="B7" s="195"/>
-      <c r="C7" s="195"/>
-      <c r="D7" s="195"/>
-      <c r="E7" s="195"/>
-      <c r="F7" s="195"/>
-      <c r="G7" s="195"/>
-      <c r="H7" s="195"/>
-    </row>
-    <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="198" t="str">
-        <v>技能ID</v>
-      </c>
-      <c r="B8" s="198" t="str">
-        <v>名称</v>
-      </c>
-      <c r="C8" s="198" t="str">
-        <v>动作</v>
-      </c>
-      <c r="D8" s="198" t="str">
-        <v>前摇秒</v>
-      </c>
-      <c r="E8" s="198" t="str">
-        <v>生效秒</v>
-      </c>
-      <c r="F8" s="198" t="str">
-        <v>总时长秒</v>
-      </c>
-      <c r="G8" s="198" t="str">
-        <v>范围与伤害</v>
-      </c>
-      <c r="H8" s="198" t="str">
-        <v>打断与特效</v>
-      </c>
-    </row>
-    <row r="9" ht="64" customHeight="1">
-      <c r="A9" s="199" t="str">
-        <v>monitor_keyboard</v>
-      </c>
-      <c r="B9" s="199" t="str">
-        <v>键盘拍地</v>
-      </c>
-      <c r="C9" s="199" t="str">
-        <v>melee_keyboard</v>
-      </c>
-      <c r="D9" s="200" t="n">
+      <c r="H5" s="195" t="n"/>
+    </row>
+    <row r="6" ht="26" customHeight="1" s="135">
+      <c r="A6" s="195" t="n"/>
+      <c r="B6" s="195" t="n"/>
+      <c r="C6" s="195" t="n"/>
+      <c r="D6" s="195" t="n"/>
+      <c r="E6" s="195" t="n"/>
+      <c r="F6" s="195" t="n"/>
+      <c r="G6" s="195" t="n"/>
+      <c r="H6" s="195" t="n"/>
+    </row>
+    <row r="7" ht="26" customHeight="1" s="135">
+      <c r="A7" s="195" t="n"/>
+      <c r="B7" s="195" t="n"/>
+      <c r="C7" s="195" t="n"/>
+      <c r="D7" s="195" t="n"/>
+      <c r="E7" s="195" t="n"/>
+      <c r="F7" s="195" t="n"/>
+      <c r="G7" s="195" t="n"/>
+      <c r="H7" s="195" t="n"/>
+    </row>
+    <row r="8" ht="26" customHeight="1" s="135">
+      <c r="A8" s="198" t="inlineStr">
+        <is>
+          <t>技能ID</t>
+        </is>
+      </c>
+      <c r="B8" s="198" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C8" s="198" t="inlineStr">
+        <is>
+          <t>动作</t>
+        </is>
+      </c>
+      <c r="D8" s="198" t="inlineStr">
+        <is>
+          <t>前摇秒</t>
+        </is>
+      </c>
+      <c r="E8" s="198" t="inlineStr">
+        <is>
+          <t>生效秒</t>
+        </is>
+      </c>
+      <c r="F8" s="198" t="inlineStr">
+        <is>
+          <t>总时长秒</t>
+        </is>
+      </c>
+      <c r="G8" s="198" t="inlineStr">
+        <is>
+          <t>范围与伤害</t>
+        </is>
+      </c>
+      <c r="H8" s="198" t="inlineStr">
+        <is>
+          <t>打断与特效</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="64" customHeight="1" s="135">
+      <c r="A9" s="199" t="inlineStr">
+        <is>
+          <t>monitor_keyboard</t>
+        </is>
+      </c>
+      <c r="B9" s="199" t="inlineStr">
+        <is>
+          <t>键盘拍地</t>
+        </is>
+      </c>
+      <c r="C9" s="199" t="inlineStr">
+        <is>
+          <t>melee_keyboard</t>
+        </is>
+      </c>
+      <c r="D9" s="213" t="n">
         <v>1.066667</v>
       </c>
-      <c r="E9" s="200" t="n">
+      <c r="E9" s="213" t="n">
         <v>1.066667</v>
       </c>
-      <c r="F9" s="201" t="n">
+      <c r="F9" s="214" t="n">
         <v>1.8</v>
       </c>
-      <c r="G9" s="199" t="str">
-        <v>前方3.2m，半径1.65m；24</v>
-      </c>
-      <c r="H9" s="199" t="str">
-        <v>单次命中；蓝/玫红；黄闪1帧</v>
-      </c>
-    </row>
-    <row r="10" ht="64" customHeight="1">
-      <c r="A10" s="199" t="str">
-        <v>monitor_cable</v>
-      </c>
-      <c r="B10" s="199" t="str">
-        <v>数据线甩击</v>
-      </c>
-      <c r="C10" s="199" t="str">
-        <v>melee_cable</v>
-      </c>
-      <c r="D10" s="200" t="n">
+      <c r="G9" s="199" t="inlineStr">
+        <is>
+          <t>前方3.2m，半径1.65m；24</t>
+        </is>
+      </c>
+      <c r="H9" s="199" t="inlineStr">
+        <is>
+          <t>单次命中；蓝/玫红；黄闪1帧</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="64" customHeight="1" s="135">
+      <c r="A10" s="199" t="inlineStr">
+        <is>
+          <t>monitor_cable</t>
+        </is>
+      </c>
+      <c r="B10" s="199" t="inlineStr">
+        <is>
+          <t>数据线甩击</t>
+        </is>
+      </c>
+      <c r="C10" s="199" t="inlineStr">
+        <is>
+          <t>melee_cable</t>
+        </is>
+      </c>
+      <c r="D10" s="213" t="n">
         <v>0.8</v>
       </c>
-      <c r="E10" s="200" t="str">
-        <v>0.8–0.967</v>
-      </c>
-      <c r="F10" s="201" t="n">
+      <c r="E10" s="213" t="inlineStr">
+        <is>
+          <t>0.8–0.967</t>
+        </is>
+      </c>
+      <c r="F10" s="214" t="n">
         <v>2</v>
       </c>
-      <c r="G10" s="199" t="str">
-        <v>160°弧，半径6m；20</v>
-      </c>
-      <c r="H10" s="199" t="str">
-        <v>螺旋前摇；平滑弧带；每目标1次</v>
-      </c>
-    </row>
-    <row r="11" ht="64" customHeight="1">
-      <c r="A11" s="199" t="str">
-        <v>monitor_spin_slam</v>
-      </c>
-      <c r="B11" s="199" t="str">
-        <v>旋转砸地</v>
-      </c>
-      <c r="C11" s="199" t="str">
-        <v>heavy_spin_slam</v>
-      </c>
-      <c r="D11" s="200" t="n">
+      <c r="G10" s="199" t="inlineStr">
+        <is>
+          <t>160°弧，半径6m；20</t>
+        </is>
+      </c>
+      <c r="H10" s="199" t="inlineStr">
+        <is>
+          <t>螺旋前摇；平滑弧带；每目标1次</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="64" customHeight="1" s="135">
+      <c r="A11" s="199" t="inlineStr">
+        <is>
+          <t>monitor_spin_slam</t>
+        </is>
+      </c>
+      <c r="B11" s="199" t="inlineStr">
+        <is>
+          <t>旋转砸地</t>
+        </is>
+      </c>
+      <c r="C11" s="199" t="inlineStr">
+        <is>
+          <t>heavy_spin_slam</t>
+        </is>
+      </c>
+      <c r="D11" s="213" t="n">
         <v>2.133333</v>
       </c>
-      <c r="E11" s="200" t="n">
+      <c r="E11" s="213" t="n">
         <v>2.133333</v>
       </c>
-      <c r="F11" s="201" t="n">
+      <c r="F11" s="214" t="n">
         <v>3.2</v>
       </c>
-      <c r="G11" s="199" t="str">
-        <v>前方1.4m，半径5.2m；36</v>
-      </c>
-      <c r="H11" s="199" t="str">
-        <v>3圈屏幕旋转；后仰停顿；黄闪1帧</v>
-      </c>
-    </row>
-    <row r="12" ht="64" customHeight="1">
-      <c r="A12" s="199" t="str">
-        <v>monitor_ground_current</v>
-      </c>
-      <c r="B12" s="199" t="str">
-        <v>接地电流</v>
-      </c>
-      <c r="C12" s="199" t="str">
-        <v>special四段</v>
+      <c r="G11" s="199" t="inlineStr">
+        <is>
+          <t>前方1.4m，半径5.2m；36</t>
+        </is>
+      </c>
+      <c r="H11" s="199" t="inlineStr">
+        <is>
+          <t>3圈屏幕旋转；后仰停顿；黄闪1帧</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="64" customHeight="1" s="135">
+      <c r="A12" s="199" t="inlineStr">
+        <is>
+          <t>monitor_ground_current</t>
+        </is>
+      </c>
+      <c r="B12" s="199" t="inlineStr">
+        <is>
+          <t>接地电流</t>
+        </is>
+      </c>
+      <c r="C12" s="199" t="inlineStr">
+        <is>
+          <t>special四段</t>
+        </is>
       </c>
       <c r="D12" s="199" t="n">
         <v>1.8</v>
       </c>
-      <c r="E12" s="199" t="str">
-        <v>每0.8秒脉冲</v>
-      </c>
-      <c r="F12" s="199" t="str">
-        <v>5.1 / 5.9 / 6.7</v>
-      </c>
-      <c r="G12" s="199" t="str">
-        <v>线尖接地点半径7m；每次12</v>
-      </c>
-      <c r="H12" s="199" t="str">
-        <v>通电2.4/3.2/4s；暴击可打断；冷却10s</v>
-      </c>
-    </row>
-    <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="195"/>
-      <c r="B13" s="195"/>
-      <c r="C13" s="195"/>
-      <c r="D13" s="195"/>
-      <c r="E13" s="195"/>
-      <c r="F13" s="195"/>
-      <c r="G13" s="195"/>
-      <c r="H13" s="195"/>
-    </row>
-    <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="195"/>
-      <c r="B14" s="195"/>
-      <c r="C14" s="195"/>
-      <c r="D14" s="195"/>
-      <c r="E14" s="195"/>
-      <c r="F14" s="195"/>
-      <c r="G14" s="195"/>
-      <c r="H14" s="195"/>
-    </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="198" t="str">
-        <v>阶段</v>
-      </c>
-      <c r="B15" s="198" t="str">
-        <v>HP阈值</v>
-      </c>
-      <c r="C15" s="198" t="str">
-        <v>技能序列</v>
-      </c>
-      <c r="D15" s="198"/>
-      <c r="E15" s="198"/>
-      <c r="F15" s="198"/>
-      <c r="G15" s="198"/>
-      <c r="H15" s="198"/>
-    </row>
-    <row r="16" ht="26" customHeight="1">
+      <c r="E12" s="199" t="inlineStr">
+        <is>
+          <t>每0.8秒脉冲</t>
+        </is>
+      </c>
+      <c r="F12" s="199" t="inlineStr">
+        <is>
+          <t>5.1 / 5.9 / 6.7</t>
+        </is>
+      </c>
+      <c r="G12" s="199" t="inlineStr">
+        <is>
+          <t>线尖接地点半径7m；每次12</t>
+        </is>
+      </c>
+      <c r="H12" s="199" t="inlineStr">
+        <is>
+          <t>通电2.4/3.2/4s；暴击可打断；冷却10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1" s="135">
+      <c r="A13" s="195" t="n"/>
+      <c r="B13" s="195" t="n"/>
+      <c r="C13" s="195" t="n"/>
+      <c r="D13" s="195" t="n"/>
+      <c r="E13" s="195" t="n"/>
+      <c r="F13" s="195" t="n"/>
+      <c r="G13" s="195" t="n"/>
+      <c r="H13" s="195" t="n"/>
+    </row>
+    <row r="14" ht="26" customHeight="1" s="135">
+      <c r="A14" s="195" t="n"/>
+      <c r="B14" s="195" t="n"/>
+      <c r="C14" s="195" t="n"/>
+      <c r="D14" s="195" t="n"/>
+      <c r="E14" s="195" t="n"/>
+      <c r="F14" s="195" t="n"/>
+      <c r="G14" s="195" t="n"/>
+      <c r="H14" s="195" t="n"/>
+    </row>
+    <row r="15" ht="26" customHeight="1" s="135">
+      <c r="A15" s="198" t="inlineStr">
+        <is>
+          <t>阶段</t>
+        </is>
+      </c>
+      <c r="B15" s="198" t="inlineStr">
+        <is>
+          <t>HP阈值</t>
+        </is>
+      </c>
+      <c r="C15" s="198" t="inlineStr">
+        <is>
+          <t>技能序列</t>
+        </is>
+      </c>
+      <c r="D15" s="203" t="n"/>
+      <c r="E15" s="203" t="n"/>
+      <c r="F15" s="203" t="n"/>
+      <c r="G15" s="203" t="n"/>
+      <c r="H15" s="203" t="n"/>
+    </row>
+    <row r="16" ht="26" customHeight="1" s="135">
       <c r="A16" s="195" t="n">
         <v>1</v>
       </c>
-      <c r="B16" s="195" t="str">
-        <v>&gt;66%</v>
-      </c>
-      <c r="C16" s="195" t="str">
-        <v>键盘、数据线、键盘、重击</v>
-      </c>
-      <c r="D16" s="195"/>
-      <c r="E16" s="195"/>
-      <c r="F16" s="195"/>
-      <c r="G16" s="195"/>
-      <c r="H16" s="195"/>
-    </row>
-    <row r="17" ht="26" customHeight="1">
+      <c r="B16" s="195" t="inlineStr">
+        <is>
+          <t>&gt;66%</t>
+        </is>
+      </c>
+      <c r="C16" s="195" t="inlineStr">
+        <is>
+          <t>键盘、数据线、键盘、重击</t>
+        </is>
+      </c>
+      <c r="D16" s="203" t="n"/>
+      <c r="E16" s="203" t="n"/>
+      <c r="F16" s="203" t="n"/>
+      <c r="G16" s="203" t="n"/>
+      <c r="H16" s="203" t="n"/>
+    </row>
+    <row r="17" ht="26" customHeight="1" s="135">
       <c r="A17" s="195" t="n">
         <v>2</v>
       </c>
-      <c r="B17" s="195" t="str">
-        <v>≤66%</v>
-      </c>
-      <c r="C17" s="195" t="str">
-        <v>数据线、插线、键盘、重击</v>
-      </c>
-      <c r="D17" s="195"/>
-      <c r="E17" s="195"/>
-      <c r="F17" s="195"/>
-      <c r="G17" s="195"/>
-      <c r="H17" s="195"/>
-    </row>
-    <row r="18" ht="26" customHeight="1">
+      <c r="B17" s="195" t="inlineStr">
+        <is>
+          <t>≤66%</t>
+        </is>
+      </c>
+      <c r="C17" s="195" t="inlineStr">
+        <is>
+          <t>数据线、插线、键盘、重击</t>
+        </is>
+      </c>
+      <c r="D17" s="203" t="n"/>
+      <c r="E17" s="203" t="n"/>
+      <c r="F17" s="203" t="n"/>
+      <c r="G17" s="203" t="n"/>
+      <c r="H17" s="203" t="n"/>
+    </row>
+    <row r="18" ht="26" customHeight="1" s="135">
       <c r="A18" s="195" t="n">
         <v>3</v>
       </c>
-      <c r="B18" s="195" t="str">
-        <v>≤33%</v>
-      </c>
-      <c r="C18" s="195" t="str">
-        <v>重击、插线、数据线、重击、插线</v>
-      </c>
-      <c r="D18" s="195"/>
-      <c r="E18" s="195"/>
-      <c r="F18" s="195"/>
-      <c r="G18" s="195"/>
-      <c r="H18" s="195"/>
-    </row>
-    <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="195"/>
-      <c r="B19" s="195"/>
-      <c r="C19" s="195"/>
-      <c r="D19" s="195"/>
-      <c r="E19" s="195"/>
-      <c r="F19" s="195"/>
-      <c r="G19" s="195"/>
-      <c r="H19" s="195"/>
-    </row>
-    <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="198" t="str">
-        <v>状态ID</v>
-      </c>
-      <c r="B20" s="198" t="str">
-        <v>表现动作</v>
-      </c>
-      <c r="C20" s="198"/>
-      <c r="D20" s="198"/>
-      <c r="E20" s="198"/>
-      <c r="F20" s="198"/>
-      <c r="G20" s="198" t="str">
-        <v>规则</v>
-      </c>
-      <c r="H20" s="198"/>
-    </row>
-    <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="195" t="str">
-        <v>dormant</v>
-      </c>
-      <c xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="B21" s="195" t="str">
-        <v>未激活：activate第0帧；已出场：idle</v>
-      </c>
-      <c r="C21" s="195"/>
-      <c r="D21" s="195"/>
-      <c r="E21" s="195"/>
-      <c r="F21" s="195"/>
-      <c r="G21" s="195" t="str">
-        <v>Enemy3D状态与真实进度单向采样</v>
-      </c>
-      <c r="H21" s="195"/>
-    </row>
-    <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="195" t="str">
-        <v>idle</v>
-      </c>
-      <c r="B22" s="195" t="str">
-        <v>idle</v>
-      </c>
-      <c r="C22" s="195"/>
-      <c r="D22" s="195"/>
-      <c r="E22" s="195"/>
-      <c r="F22" s="195"/>
-      <c r="G22" s="195" t="str">
-        <v>Enemy3D状态与真实进度单向采样</v>
-      </c>
-      <c r="H22" s="195"/>
-    </row>
-    <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="195" t="str">
-        <v>patrol</v>
-      </c>
-      <c r="B23" s="195" t="str">
-        <v>move</v>
-      </c>
-      <c r="C23" s="195"/>
-      <c r="D23" s="195"/>
-      <c r="E23" s="195"/>
-      <c r="F23" s="195"/>
-      <c r="G23" s="195" t="str">
-        <v>Enemy3D状态与真实进度单向采样</v>
-      </c>
-      <c r="H23" s="195"/>
-    </row>
-    <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="195" t="str">
-        <v>alert</v>
-      </c>
-      <c xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="B24" s="195" t="str">
-        <v>存活玩家≤10米首次触发activate6.4s，结束后战斗</v>
-      </c>
-      <c r="C24" s="195"/>
-      <c r="D24" s="195"/>
-      <c r="E24" s="195"/>
-      <c r="F24" s="195"/>
-      <c r="G24" s="195" t="str">
-        <v>Enemy3D状态与真实进度单向采样</v>
-      </c>
-      <c r="H24" s="195"/>
-    </row>
-    <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="195" t="str">
-        <v>chase</v>
-      </c>
-      <c r="B25" s="195" t="str">
-        <v>move / turn_left/right</v>
-      </c>
-      <c r="C25" s="195"/>
-      <c r="D25" s="195"/>
-      <c r="E25" s="195"/>
-      <c r="F25" s="195"/>
-      <c r="G25" s="195" t="str">
-        <v>Enemy3D状态与真实进度单向采样</v>
-      </c>
-      <c r="H25" s="195"/>
-    </row>
-    <row r="26" ht="26" customHeight="1">
-      <c r="A26" s="195" t="str">
-        <v>search</v>
-      </c>
-      <c r="B26" s="195" t="str">
-        <v>move</v>
-      </c>
-      <c r="C26" s="195"/>
-      <c r="D26" s="195"/>
-      <c r="E26" s="195"/>
-      <c r="F26" s="195"/>
-      <c r="G26" s="195" t="str">
-        <v>Enemy3D状态与真实进度单向采样</v>
-      </c>
-      <c r="H26" s="195"/>
-    </row>
-    <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="195" t="str">
-        <v>return</v>
-      </c>
-      <c r="B27" s="195" t="str">
-        <v>move</v>
-      </c>
-      <c r="C27" s="195"/>
-      <c r="D27" s="195"/>
-      <c r="E27" s="195"/>
-      <c r="F27" s="195"/>
-      <c r="G27" s="195" t="str">
-        <v>Enemy3D状态与真实进度单向采样</v>
-      </c>
-      <c r="H27" s="195"/>
-    </row>
-    <row r="28" ht="26" customHeight="1">
-      <c r="A28" s="195" t="str">
-        <v>telegraph</v>
-      </c>
-      <c r="B28" s="195" t="str">
-        <v>技能剪辑前摇</v>
-      </c>
-      <c r="C28" s="195"/>
-      <c r="D28" s="195"/>
-      <c r="E28" s="195"/>
-      <c r="F28" s="195"/>
-      <c r="G28" s="195" t="str">
-        <v>Enemy3D状态与真实进度单向采样</v>
-      </c>
-      <c r="H28" s="195"/>
-    </row>
-    <row r="29" ht="26" customHeight="1">
-      <c r="A29" s="195" t="str">
-        <v>attack</v>
-      </c>
-      <c r="B29" s="195" t="str">
-        <v>技能剪辑生效段 / special_channel</v>
-      </c>
-      <c r="C29" s="195"/>
-      <c r="D29" s="195"/>
-      <c r="E29" s="195"/>
-      <c r="F29" s="195"/>
-      <c r="G29" s="195" t="str">
-        <v>Enemy3D状态与真实进度单向采样</v>
-      </c>
-      <c r="H29" s="195"/>
-    </row>
-    <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="195" t="str">
-        <v>recovery</v>
-      </c>
-      <c r="B30" s="195" t="str">
-        <v>技能剪辑恢复段 / special_recover</v>
-      </c>
-      <c r="C30" s="195"/>
-      <c r="D30" s="195"/>
-      <c r="E30" s="195"/>
-      <c r="F30" s="195"/>
-      <c r="G30" s="195" t="str">
-        <v>Enemy3D状态与真实进度单向采样</v>
-      </c>
-      <c r="H30" s="195"/>
-    </row>
-    <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="195" t="str">
-        <v>stagger</v>
-      </c>
-      <c r="B31" s="195" t="str">
-        <v>hurt / stun_enter→stun_loop→stun_exit</v>
-      </c>
-      <c r="C31" s="195"/>
-      <c r="D31" s="195"/>
-      <c r="E31" s="195"/>
-      <c r="F31" s="195"/>
-      <c r="G31" s="195" t="str">
-        <v>韧性8%：坐下1.4s、坐地2.4s、起身1s</v>
-      </c>
-      <c r="H31" s="195"/>
-    </row>
-    <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="195" t="str">
-        <v>dead</v>
-      </c>
-      <c r="B32" s="195" t="str">
-        <v>dead</v>
-      </c>
-      <c r="C32" s="195"/>
-      <c r="D32" s="195"/>
-      <c r="E32" s="195"/>
-      <c r="F32" s="195"/>
-      <c r="G32" s="195" t="str">
-        <v>死亡2s后回收；根不压扁</v>
-      </c>
-      <c r="H32" s="195"/>
-    </row>
-    <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="195"/>
-      <c r="B33" s="195"/>
-      <c r="C33" s="195"/>
-      <c r="D33" s="195"/>
-      <c r="E33" s="195"/>
-      <c r="F33" s="195"/>
-      <c r="G33" s="195"/>
-      <c r="H33" s="195"/>
-    </row>
-    <row r="34" ht="40" customHeight="1">
-      <c r="A34" s="195" t="str">
-        <v>规则</v>
-      </c>
-      <c xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="B34" s="195" t="str">
-        <v>10米外黑屏静止；触发后离开范围继续播完；started/进度/完成标记随实例保存；休眠暂停，旧档兼容。</v>
-      </c>
-      <c r="C34" s="195"/>
-      <c r="D34" s="195"/>
-      <c r="E34" s="195"/>
-      <c r="F34" s="195"/>
-      <c r="G34" s="195"/>
-      <c r="H34" s="195"/>
-    </row>
-    <row r="35" ht="26" customHeight="1">
-      <c r="A35" s="195"/>
-      <c r="B35" s="195"/>
-      <c r="C35" s="195"/>
-      <c r="D35" s="195"/>
-      <c r="E35" s="195"/>
-      <c r="F35" s="195"/>
-      <c r="G35" s="195"/>
-      <c r="H35" s="195"/>
-    </row>
-    <row r="36" ht="40" customHeight="1">
-      <c r="A36" s="195" t="str">
-        <v>设计主源</v>
-      </c>
-      <c xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="B36" s="195" t="str">
-        <v>docs/v0.1/design/Boss002显示器技能设计.md（r4）；动画设计r28</v>
-      </c>
-      <c r="C36" s="195"/>
-      <c r="D36" s="195"/>
-      <c r="E36" s="195"/>
-      <c r="F36" s="195"/>
-      <c r="G36" s="195"/>
-      <c r="H36" s="195"/>
-    </row>
-    <row r="37" ht="40" customHeight="1">
-      <c r="A37" s="195" t="str">
-        <v>实现源</v>
-      </c>
-      <c r="B37" s="195" t="str">
-        <v>src/enemy3d/MonitorBossCombat.gd</v>
-      </c>
-      <c r="C37" s="195"/>
-      <c r="D37" s="195"/>
-      <c r="E37" s="195"/>
-      <c r="F37" s="195"/>
-      <c r="G37" s="195"/>
-      <c r="H37" s="195"/>
+      <c r="B18" s="195" t="inlineStr">
+        <is>
+          <t>≤33%</t>
+        </is>
+      </c>
+      <c r="C18" s="195" t="inlineStr">
+        <is>
+          <t>重击、插线、数据线、重击、插线</t>
+        </is>
+      </c>
+      <c r="D18" s="203" t="n"/>
+      <c r="E18" s="203" t="n"/>
+      <c r="F18" s="203" t="n"/>
+      <c r="G18" s="203" t="n"/>
+      <c r="H18" s="203" t="n"/>
+    </row>
+    <row r="19" ht="26" customHeight="1" s="135">
+      <c r="A19" s="195" t="n"/>
+      <c r="B19" s="195" t="n"/>
+      <c r="C19" s="195" t="n"/>
+      <c r="D19" s="195" t="n"/>
+      <c r="E19" s="195" t="n"/>
+      <c r="F19" s="195" t="n"/>
+      <c r="G19" s="195" t="n"/>
+      <c r="H19" s="195" t="n"/>
+    </row>
+    <row r="20" ht="26" customHeight="1" s="135">
+      <c r="A20" s="198" t="inlineStr">
+        <is>
+          <t>状态ID</t>
+        </is>
+      </c>
+      <c r="B20" s="198" t="inlineStr">
+        <is>
+          <t>表现动作</t>
+        </is>
+      </c>
+      <c r="C20" s="203" t="n"/>
+      <c r="D20" s="203" t="n"/>
+      <c r="E20" s="203" t="n"/>
+      <c r="F20" s="203" t="n"/>
+      <c r="G20" s="198" t="inlineStr">
+        <is>
+          <t>规则</t>
+        </is>
+      </c>
+      <c r="H20" s="203" t="n"/>
+    </row>
+    <row r="21" ht="26" customHeight="1" s="135">
+      <c r="A21" s="195" t="inlineStr">
+        <is>
+          <t>dormant</t>
+        </is>
+      </c>
+      <c r="B21" s="195" t="inlineStr">
+        <is>
+          <t>未激活：activate第0帧；已出场：idle</t>
+        </is>
+      </c>
+      <c r="C21" s="203" t="n"/>
+      <c r="D21" s="203" t="n"/>
+      <c r="E21" s="203" t="n"/>
+      <c r="F21" s="203" t="n"/>
+      <c r="G21" s="195" t="inlineStr">
+        <is>
+          <t>Enemy3D状态与真实进度单向采样</t>
+        </is>
+      </c>
+      <c r="H21" s="203" t="n"/>
+    </row>
+    <row r="22" ht="26" customHeight="1" s="135">
+      <c r="A22" s="195" t="inlineStr">
+        <is>
+          <t>idle</t>
+        </is>
+      </c>
+      <c r="B22" s="195" t="inlineStr">
+        <is>
+          <t>idle</t>
+        </is>
+      </c>
+      <c r="C22" s="203" t="n"/>
+      <c r="D22" s="203" t="n"/>
+      <c r="E22" s="203" t="n"/>
+      <c r="F22" s="203" t="n"/>
+      <c r="G22" s="195" t="inlineStr">
+        <is>
+          <t>Enemy3D状态与真实进度单向采样</t>
+        </is>
+      </c>
+      <c r="H22" s="203" t="n"/>
+    </row>
+    <row r="23" ht="26" customHeight="1" s="135">
+      <c r="A23" s="195" t="inlineStr">
+        <is>
+          <t>patrol</t>
+        </is>
+      </c>
+      <c r="B23" s="195" t="inlineStr">
+        <is>
+          <t>move</t>
+        </is>
+      </c>
+      <c r="C23" s="203" t="n"/>
+      <c r="D23" s="203" t="n"/>
+      <c r="E23" s="203" t="n"/>
+      <c r="F23" s="203" t="n"/>
+      <c r="G23" s="195" t="inlineStr">
+        <is>
+          <t>Enemy3D状态与真实进度单向采样</t>
+        </is>
+      </c>
+      <c r="H23" s="203" t="n"/>
+    </row>
+    <row r="24" ht="26" customHeight="1" s="135">
+      <c r="A24" s="195" t="inlineStr">
+        <is>
+          <t>alert</t>
+        </is>
+      </c>
+      <c r="B24" s="195" t="inlineStr">
+        <is>
+          <t>存活玩家≤10米首次触发activate6.4s，结束后战斗</t>
+        </is>
+      </c>
+      <c r="C24" s="203" t="n"/>
+      <c r="D24" s="203" t="n"/>
+      <c r="E24" s="203" t="n"/>
+      <c r="F24" s="203" t="n"/>
+      <c r="G24" s="195" t="inlineStr">
+        <is>
+          <t>Enemy3D状态与真实进度单向采样</t>
+        </is>
+      </c>
+      <c r="H24" s="203" t="n"/>
+    </row>
+    <row r="25" ht="26" customHeight="1" s="135">
+      <c r="A25" s="195" t="inlineStr">
+        <is>
+          <t>chase</t>
+        </is>
+      </c>
+      <c r="B25" s="195" t="inlineStr">
+        <is>
+          <t>move / turn_left/right</t>
+        </is>
+      </c>
+      <c r="C25" s="203" t="n"/>
+      <c r="D25" s="203" t="n"/>
+      <c r="E25" s="203" t="n"/>
+      <c r="F25" s="203" t="n"/>
+      <c r="G25" s="195" t="inlineStr">
+        <is>
+          <t>Enemy3D状态与真实进度单向采样</t>
+        </is>
+      </c>
+      <c r="H25" s="203" t="n"/>
+    </row>
+    <row r="26" ht="26" customHeight="1" s="135">
+      <c r="A26" s="195" t="inlineStr">
+        <is>
+          <t>search</t>
+        </is>
+      </c>
+      <c r="B26" s="195" t="inlineStr">
+        <is>
+          <t>move</t>
+        </is>
+      </c>
+      <c r="C26" s="203" t="n"/>
+      <c r="D26" s="203" t="n"/>
+      <c r="E26" s="203" t="n"/>
+      <c r="F26" s="203" t="n"/>
+      <c r="G26" s="195" t="inlineStr">
+        <is>
+          <t>Enemy3D状态与真实进度单向采样</t>
+        </is>
+      </c>
+      <c r="H26" s="203" t="n"/>
+    </row>
+    <row r="27" ht="26" customHeight="1" s="135">
+      <c r="A27" s="195" t="inlineStr">
+        <is>
+          <t>return</t>
+        </is>
+      </c>
+      <c r="B27" s="195" t="inlineStr">
+        <is>
+          <t>move</t>
+        </is>
+      </c>
+      <c r="C27" s="203" t="n"/>
+      <c r="D27" s="203" t="n"/>
+      <c r="E27" s="203" t="n"/>
+      <c r="F27" s="203" t="n"/>
+      <c r="G27" s="195" t="inlineStr">
+        <is>
+          <t>Enemy3D状态与真实进度单向采样</t>
+        </is>
+      </c>
+      <c r="H27" s="203" t="n"/>
+    </row>
+    <row r="28" ht="26" customHeight="1" s="135">
+      <c r="A28" s="195" t="inlineStr">
+        <is>
+          <t>telegraph</t>
+        </is>
+      </c>
+      <c r="B28" s="195" t="inlineStr">
+        <is>
+          <t>技能剪辑前摇</t>
+        </is>
+      </c>
+      <c r="C28" s="203" t="n"/>
+      <c r="D28" s="203" t="n"/>
+      <c r="E28" s="203" t="n"/>
+      <c r="F28" s="203" t="n"/>
+      <c r="G28" s="195" t="inlineStr">
+        <is>
+          <t>Enemy3D状态与真实进度单向采样</t>
+        </is>
+      </c>
+      <c r="H28" s="203" t="n"/>
+    </row>
+    <row r="29" ht="26" customHeight="1" s="135">
+      <c r="A29" s="195" t="inlineStr">
+        <is>
+          <t>attack</t>
+        </is>
+      </c>
+      <c r="B29" s="195" t="inlineStr">
+        <is>
+          <t>技能剪辑生效段 / special_channel</t>
+        </is>
+      </c>
+      <c r="C29" s="203" t="n"/>
+      <c r="D29" s="203" t="n"/>
+      <c r="E29" s="203" t="n"/>
+      <c r="F29" s="203" t="n"/>
+      <c r="G29" s="195" t="inlineStr">
+        <is>
+          <t>Enemy3D状态与真实进度单向采样</t>
+        </is>
+      </c>
+      <c r="H29" s="203" t="n"/>
+    </row>
+    <row r="30" ht="26" customHeight="1" s="135">
+      <c r="A30" s="195" t="inlineStr">
+        <is>
+          <t>recovery</t>
+        </is>
+      </c>
+      <c r="B30" s="195" t="inlineStr">
+        <is>
+          <t>技能剪辑恢复段 / special_recover</t>
+        </is>
+      </c>
+      <c r="C30" s="203" t="n"/>
+      <c r="D30" s="203" t="n"/>
+      <c r="E30" s="203" t="n"/>
+      <c r="F30" s="203" t="n"/>
+      <c r="G30" s="195" t="inlineStr">
+        <is>
+          <t>Enemy3D状态与真实进度单向采样</t>
+        </is>
+      </c>
+      <c r="H30" s="203" t="n"/>
+    </row>
+    <row r="31" ht="26" customHeight="1" s="135">
+      <c r="A31" s="195" t="inlineStr">
+        <is>
+          <t>stagger</t>
+        </is>
+      </c>
+      <c r="B31" s="195" t="inlineStr">
+        <is>
+          <t>hurt / stun_enter→stun_loop→stun_exit</t>
+        </is>
+      </c>
+      <c r="C31" s="203" t="n"/>
+      <c r="D31" s="203" t="n"/>
+      <c r="E31" s="203" t="n"/>
+      <c r="F31" s="203" t="n"/>
+      <c r="G31" s="195" t="inlineStr">
+        <is>
+          <t>韧性8%：坐下1.4s、坐地2.4s、起身1s</t>
+        </is>
+      </c>
+      <c r="H31" s="203" t="n"/>
+    </row>
+    <row r="32" ht="26" customHeight="1" s="135">
+      <c r="A32" s="195" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="B32" s="195" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="C32" s="203" t="n"/>
+      <c r="D32" s="203" t="n"/>
+      <c r="E32" s="203" t="n"/>
+      <c r="F32" s="203" t="n"/>
+      <c r="G32" s="195" t="inlineStr">
+        <is>
+          <t>死亡2s后回收；根不压扁</t>
+        </is>
+      </c>
+      <c r="H32" s="203" t="n"/>
+    </row>
+    <row r="33" ht="26" customHeight="1" s="135">
+      <c r="A33" s="195" t="n"/>
+      <c r="B33" s="195" t="n"/>
+      <c r="C33" s="195" t="n"/>
+      <c r="D33" s="195" t="n"/>
+      <c r="E33" s="195" t="n"/>
+      <c r="F33" s="195" t="n"/>
+      <c r="G33" s="195" t="n"/>
+      <c r="H33" s="195" t="n"/>
+    </row>
+    <row r="34" ht="40" customHeight="1" s="135">
+      <c r="A34" s="195" t="inlineStr">
+        <is>
+          <t>规则</t>
+        </is>
+      </c>
+      <c r="B34" s="195" t="inlineStr">
+        <is>
+          <t>10米外黑屏静止；触发后离开范围继续播完；started/进度/完成标记随实例保存；休眠暂停，旧档兼容。</t>
+        </is>
+      </c>
+      <c r="C34" s="203" t="n"/>
+      <c r="D34" s="203" t="n"/>
+      <c r="E34" s="203" t="n"/>
+      <c r="F34" s="203" t="n"/>
+      <c r="G34" s="203" t="n"/>
+      <c r="H34" s="203" t="n"/>
+    </row>
+    <row r="35" ht="26" customHeight="1" s="135">
+      <c r="A35" s="195" t="n"/>
+      <c r="B35" s="195" t="n"/>
+      <c r="C35" s="195" t="n"/>
+      <c r="D35" s="195" t="n"/>
+      <c r="E35" s="195" t="n"/>
+      <c r="F35" s="195" t="n"/>
+      <c r="G35" s="195" t="n"/>
+      <c r="H35" s="195" t="n"/>
+    </row>
+    <row r="36" ht="40" customHeight="1" s="135">
+      <c r="A36" s="195" t="inlineStr">
+        <is>
+          <t>设计主源</t>
+        </is>
+      </c>
+      <c r="B36" s="195" t="inlineStr">
+        <is>
+          <t>docs/v0.1/design/Boss002显示器技能设计.md（r4）；动画设计r28</t>
+        </is>
+      </c>
+      <c r="C36" s="203" t="n"/>
+      <c r="D36" s="203" t="n"/>
+      <c r="E36" s="203" t="n"/>
+      <c r="F36" s="203" t="n"/>
+      <c r="G36" s="203" t="n"/>
+      <c r="H36" s="203" t="n"/>
+    </row>
+    <row r="37" ht="40" customHeight="1" s="135">
+      <c r="A37" s="195" t="inlineStr">
+        <is>
+          <t>实现源</t>
+        </is>
+      </c>
+      <c r="B37" s="195" t="inlineStr">
+        <is>
+          <t>src/enemy3d/MonitorBossCombat.gd</t>
+        </is>
+      </c>
+      <c r="C37" s="203" t="n"/>
+      <c r="D37" s="203" t="n"/>
+      <c r="E37" s="203" t="n"/>
+      <c r="F37" s="203" t="n"/>
+      <c r="G37" s="203" t="n"/>
+      <c r="H37" s="203" t="n"/>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="34">
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="C16:H16"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B21:F21"/>
+    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="C17:H17"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="G30:H30"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="C15:H15"/>
-    <mergeCell ref="C16:H16"/>
-    <mergeCell ref="C17:H17"/>
+    <mergeCell ref="B28:F28"/>
     <mergeCell ref="C18:H18"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="B21:F21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="B22:F22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="B23:F23"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="B24:F24"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="G25:H25"/>
     <mergeCell ref="B26:F26"/>
     <mergeCell ref="G26:H26"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="C15:H15"/>
     <mergeCell ref="G29:H29"/>
     <mergeCell ref="B30:F30"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="B34:H34"/>
     <mergeCell ref="G31:H31"/>
+    <mergeCell ref="G22:H22"/>
     <mergeCell ref="B32:F32"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="B34:H34"/>
-    <mergeCell ref="B36:H36"/>
     <mergeCell ref="B37:H37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx
+++ b/docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet name="总览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="武器" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="命运卡" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="怪物与Boss" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="精英怪" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="掉落物品" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="字段字典" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="基地商店" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Boss002技能设计" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="武器" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命运卡" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物与Boss" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="精英怪" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掉落物品" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段字典" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="基地商店" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Boss002技能设计" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -1355,7 +1355,7 @@
     <row r="2" ht="30" customHeight="1" s="135">
       <c r="A2" s="204" t="inlineStr">
         <is>
-          <t>设计、内容与实现状态的中央索引｜最后校对：2026-08-27｜正式入口：TowerDescent3D.tscn</t>
+          <t>设计、内容与实现状态的中央索引｜最后校对：2026-10-14｜正式入口：TowerDescent3D.tscn</t>
         </is>
       </c>
       <c r="B2" s="203" t="n"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="B6" s="29" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" s="34" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D6" s="35" t="n">
         <v>0</v>
@@ -1447,12 +1447,12 @@
       </c>
       <c r="G6" s="29" t="inlineStr">
         <is>
-          <t>7远程枪身、3近战、8子弹、6配件、数值、价格和产出</t>
+          <t>9把运行枪身（本表已登记8行，花洒机枪缺行）、3近战、8子弹、6配件、数值、价格和产出</t>
         </is>
       </c>
       <c r="H6" s="29" t="inlineStr">
         <is>
-          <t>WeaponInstance统一承载远近战；六公共枪械配件位置固定、兼容子集禁用、单拆/整枪随行；棒球棍为基地初级近战</t>
+          <t>WeaponInstance统一承载远近战；六公共枪械配件位置固定、兼容子集禁用、单拆/整枪随行；棒球棍为基地初级近战；初始步枪(bp_starter_rifle)为出厂白送枪，命运槽 4</t>
         </is>
       </c>
     </row>
@@ -1569,10 +1569,10 @@
         </is>
       </c>
       <c r="B10" s="29" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C10" s="34" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D10" s="35" t="n">
         <v>7</v>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="H15" s="29" t="inlineStr">
         <is>
-          <t>构筑随具体武器实例；7远程+3近战；六公共配件位置固定，枪型开放兼容子集</t>
+          <t>构筑随具体武器实例；9远程+3近战；六公共配件位置固定，枪型开放兼容子集</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y28"/>
+  <dimension ref="A1:Y29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="135" min="1" max="1"/>
@@ -3754,7 +3754,7 @@
       </c>
       <c r="G19" s="177" t="inlineStr">
         <is>
-          <t>bullet_count=1；charge_time=1.2；damage=880；fire_rate=1.5；magazine_size=4；reload_time=3；spread=0.05；explosion_damage_scale=0.630631（中心范围伤害560）</t>
+          <t>bullet_count=1；charge_time=1.2；damage=880；fire_rate=1.5；magazine_size=4；reload_time=3；spread=0.05；explosion_damage_scale=0.630631（中心范围伤害560）；range=18</t>
         </is>
       </c>
       <c r="H19" s="177" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="G20" s="177" t="inlineStr">
         <is>
-          <t>bullet_count=1；damage=250；fire_rate=1；magazine_size=3；reload_time=4；spread=0.1；explosion_damage_scale=0.697675（中心范围伤害180）</t>
+          <t>bullet_count=1；damage=250；fire_rate=1；magazine_size=3；reload_time=4；spread=0.1；explosion_damage_scale=0.697675（中心范围伤害180）；range=18</t>
         </is>
       </c>
       <c r="H20" s="177" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="G21" s="177" t="inlineStr">
         <is>
-          <t>bullet_count=1；damage=15；fire_rate=12；magazine_size=60；reload_time=2.8；spread=0.15</t>
+          <t>bullet_count=1；damage=15；fire_rate=12；magazine_size=60；reload_time=2.8；spread=0.15；range=18</t>
         </is>
       </c>
       <c r="H21" s="177" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="G22" s="177" t="inlineStr">
         <is>
-          <t>bullet_count=1；damage=25；fire_rate=3.5；magazine_size=12；reload_time=1.5；spread=0.03</t>
+          <t>bullet_count=1；damage=25；fire_rate=3.5；magazine_size=12；reload_time=1.5；spread=0.03；range=15</t>
         </is>
       </c>
       <c r="H22" s="177" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="G23" s="177" t="inlineStr">
         <is>
-          <t>bullet_count=1；damage=60；fire_rate=6；magazine_size=30；reload_time=2.2；spread=0.07</t>
+          <t>bullet_count=1；damage=60；fire_rate=6；magazine_size=30；reload_time=2.2；spread=0.07；range=20</t>
         </is>
       </c>
       <c r="H23" s="177" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="G24" s="177" t="inlineStr">
         <is>
-          <t>bullet_count=5；damage=45；fire_rate=1.2；magazine_size=6；reload_time=3；spread=0.35</t>
+          <t>bullet_count=5；damage=45；fire_rate=1.2；magazine_size=6；reload_time=3；spread=0.35；range=7</t>
         </is>
       </c>
       <c r="H24" s="177" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="G25" s="177" t="inlineStr">
         <is>
-          <t>bullet_count=1；damage=380；fire_rate=1；magazine_size=5；reload_time=3.5；spread=0.01</t>
+          <t>bullet_count=1；damage=380；fire_rate=1；magazine_size=5；reload_time=3.5；spread=0.01；range=60</t>
         </is>
       </c>
       <c r="H25" s="177" t="inlineStr">
@@ -4862,6 +4862,122 @@
       </c>
       <c r="Y28" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="29" ht="54" customHeight="1" s="135">
+      <c r="A29" s="177" t="inlineStr">
+        <is>
+          <t>bp_starter_rifle</t>
+        </is>
+      </c>
+      <c r="B29" s="177" t="inlineStr">
+        <is>
+          <t>枪身</t>
+        </is>
+      </c>
+      <c r="C29" s="177" t="inlineStr">
+        <is>
+          <t>初始步枪</t>
+        </is>
+      </c>
+      <c r="D29" s="177" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="177" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F29" s="177" t="n">
+        <v>120</v>
+      </c>
+      <c r="G29" s="177" t="inlineStr">
+        <is>
+          <t>bullet_count=1；damage=50；fire_rate=5；magazine_size=30；reload_time=1.8；spread=0.07；range=20</t>
+        </is>
+      </c>
+      <c r="H29" s="177" t="inlineStr">
+        <is>
+          <t>出厂配发的突击步枪。高单发伤害与高射速，换弹快，是开局唯一可靠的武器。左键装备为当前主武器。</t>
+        </is>
+      </c>
+      <c r="I29" s="177" t="inlineStr">
+        <is>
+          <t>标签：rifle、automatic、assault、starter_rifle</t>
+        </is>
+      </c>
+      <c r="J29" s="177" t="inlineStr">
+        <is>
+          <t>成品：combat_floor_1×0.4；combat_floor_2×0.6；combat_floor_3×0.75；elite_floor_1×0.75；elite_floor_2×1.25；loot_abyss×1.25；loot_floor_1_2×0.5；loot_floor_3_4×0.75；loot_floor_5×1；scavenge_floor_1×0.25；scavenge_floor_2×0.5；scavenge_floor_3×0.6；scavenge_floor_4×0.75；scavenge_floor_5×1.25
+蓝图：combat_floor_1×0.75；combat_floor_2×0.5；loot_abyss×0.75；loot_common×1；loot_floor_1_2×2；loot_floor_3_4×1.5；loot_floor_5×1；scavenge_floor_1×1.5；scavenge_floor_2×1；spawn_starter×2</t>
+        </is>
+      </c>
+      <c r="K29" s="180" t="inlineStr">
+        <is>
+          <t>[已实装]</t>
+        </is>
+      </c>
+      <c r="L29" s="177" t="inlineStr">
+        <is>
+          <t>正式注册；出厂枪数值与表现仍需逐项QA</t>
+        </is>
+      </c>
+      <c r="M29" s="177" t="inlineStr">
+        <is>
+          <t>src/base/BlueprintRegistry.gd；src/base/ItemRegistry.gd</t>
+        </is>
+      </c>
+      <c r="N29" s="177" t="inlineStr">
+        <is>
+          <t>装配ID=bp_starter_rifle；成品物品ID=weapon_starter_rifle；蓝图物品ID=bp_starter_rifle</t>
+        </is>
+      </c>
+      <c r="O29" s="46" t="n">
+        <v>4</v>
+      </c>
+      <c r="P29" s="45" t="inlineStr">
+        <is>
+          <t>生成永久weapon_instance_id；六个公共配件位置固定，枪型仅开放兼容子集；单拆配件，整枪移动时完整装配树随实例转移</t>
+        </is>
+      </c>
+      <c r="Q29" s="47" t="inlineStr">
+        <is>
+          <t>[已实装并验收] WeaponInstance schema v2、主副武器独立配件、兼容禁用、替换回滚与旧快照迁移</t>
+        </is>
+      </c>
+      <c r="R29" s="45" t="inlineStr">
+        <is>
+          <t>显示高射速连发节奏、弹量、换弹速度与出厂枪定位</t>
+        </is>
+      </c>
+      <c r="S29" s="45" t="inlineStr">
+        <is>
+          <t>高射速连发、枪口焰与后坐累积持续可读；作为出厂基线枪比较</t>
+        </is>
+      </c>
+      <c r="T29" s="47" t="inlineStr">
+        <is>
+          <t>[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA</t>
+        </is>
+      </c>
+      <c r="U29" s="163">
+        <f>IF(F29&gt;0,F29,0)</f>
+        <v/>
+      </c>
+      <c r="V29" s="163">
+        <f>IF(F29&gt;0,ROUND(F29*0.5,0),0)</f>
+        <v/>
+      </c>
+      <c r="W29" s="151" t="b">
+        <v>0</v>
+      </c>
+      <c r="X29" s="151" t="inlineStr">
+        <is>
+          <t>not_listed</t>
+        </is>
+      </c>
+      <c r="Y29" s="163" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -17687,7 +17803,8 @@
     <row r="2" ht="30" customHeight="1" s="135">
       <c r="A2" s="209" t="inlineStr">
         <is>
-          <t>数值采用Enemy3D.PROFILES正式3D基线；MonsterInjector旧2D基线仅换算楼层/主题倍率，不再作为玩家可见生命值。</t>
+          <t>数值采用Enemy3D.PROFILES正式3D基线；MonsterInjector旧2D基线仅换算楼层/主题倍率，不再作为玩家可见生命值。
+【货币独立通道 2026-10-14】货币（魂 `extraction_points`）自 2026-10-14 起走**独立掉落通道**、**不再属于物品掉落**：① 所有被击败的怪 **100% 必掉**，不受关卡空掉落率影响；② **不占物品件数**；③ 数量按**怪种 + 楼层**分档，写在该关 `monster_rules.currency`（`per_tier` &gt; `per_kind` &gt; `default`，值 = round(base + per_floor × floor)）；④ 地面货币模型尺寸随数量分档放大。关卡空掉落率（`monster_drop_table.empty_chance`）**只作用于装备类**（武器/模块/配件）；带 tag `ammo` 的备弹**豁免**空掉落 —— 否则作者指定的弹药命中率会被二次打折（实测 80% → 47%）。</t>
         </is>
       </c>
       <c r="B2" s="203" t="n"/>
@@ -18067,7 +18184,8 @@
       </c>
       <c r="O8" s="177" t="inlineStr">
         <is>
-          <t>正式数值以Enemy3D.PROFILES为基线；旧2D基线仅用于倍率换算</t>
+          <t>正式数值以Enemy3D.PROFILES为基线；旧2D基线仅用于倍率换算
+【远征01·monster_rules 覆盖 2026-10-14】本关以关卡级 `monster_rules.stats.per_kind` 做**绝对覆盖**：生命 350 / 伤害 18 / 速度 3.5 m/s（写的是最终值，不再乘楼层与主题倍率）。PROFILES 基线 58/12/3.7 **未改**，仍是其它关卡取值。口径见 docs/v0.1/design/远征关卡01设计.md §4.5.3。</t>
         </is>
       </c>
     </row>
@@ -18134,7 +18252,8 @@
       </c>
       <c r="O9" s="177" t="inlineStr">
         <is>
-          <t>正式数值以Enemy3D.PROFILES为基线；旧2D基线仅用于倍率换算</t>
+          <t>正式数值以Enemy3D.PROFILES为基线；旧2D基线仅用于倍率换算
+【远征01·monster_rules 覆盖 2026-10-14】本关以关卡级 `monster_rules.stats.per_kind` 做**绝对覆盖**：生命 250 / 伤害 30（写的是最终值，不再乘楼层与主题倍率）；速度未改。另有 **80% 概率掉 1 包通用弹药**（`item_ammo_pack`，30-50 发）——该条目**豁免关卡空掉落**，故实测命中率 0.7920 而非 0.4703。PROFILES 基线 46/2.25/10 **未改**，仍是其它关卡取值。口径见 docs/v0.1/design/远征关卡01设计.md §4.5.3。</t>
         </is>
       </c>
     </row>
@@ -18583,7 +18702,9 @@
       </c>
       <c r="I16" s="177" t="inlineStr">
         <is>
-          <t>厚血慢速；张臂抱扑拍合；1.2秒前摇/1.3秒收势；轻击上半身反应</t>
+          <t>厚血慢速；张臂抱扑拍合；1.2秒前摇/1.3秒收势；轻击上半身反应
+；**被打死后自爆**（远征01 专属）：半径 5 m 内**敌我通吃**固定 **180** 伤害，可级联引爆隔壁残血胖子；同房过滤、不转移仇恨
+【地面持续伤害场 2026-10-14】自爆后在地上留一片持续 **3 秒**的伤害区：半径 = 爆炸半径（5 m），每 **0.5 s** 结算一次、每跳 **24**；同样**敌我通吃**（相邻敌对怪 ＋ 玩家）且**同房过滤**。首跳排在 0.5 s —— 死亡当帧已结算过一次 180 的爆炸伤害，故不在 t=0 重复命中。不写该段或 `enabled=false` ⇒ 不生成场地。表现见备注里的两个特效资产。</t>
         </is>
       </c>
       <c r="J16" s="177" t="inlineStr">
@@ -18613,7 +18734,9 @@
       </c>
       <c r="O16" s="177" t="inlineStr">
         <is>
-          <t>D/E为PROFILES源基线；实际第一层生命696、追击0.60m/s、巡逻0.30m/s；内容调用ID=fat_zombie03；资产编号03；已接替壳甲卫兵投放</t>
+          <t>D/E为PROFILES源基线；实际第一层生命696、追击0.60m/s、巡逻0.30m/s；内容调用ID=fat_zombie03；资产编号03；已接替壳甲卫兵投放
+【远征01·monster_rules 覆盖 2026-10-14】本关以关卡级 `monster_rules` 做**绝对覆盖**：生命 800 / 伤害 35 / 速度 1.5 m/s；并新增**死亡自爆** `death_explosion.fat_zombie03 = {damage:180, radius_m:5.0, sfx_radius_m:20.0}`。伤情为固定值、不走 contact_damage、不受楼层与主题倍率影响；敌我通吃（相邻敌对怪＋玩家）；**刻意不复用** exploder 的主动贴近自爆（那只伤玩家、用 contact_damage、半径硬编码 3.0 m）。PROFILES 基线 232/19/0.857 **未改**。见 远征关卡01设计.md §4.5.3 与 design/胖子僵尸03运行配置.md。
+【远征01·死亡自爆表现 2026-10-14】自爆与地面场**各占一个独立特效 Prefab**：① 爆炸 **FX01-17 `VFX-DEATH-BLAST-3D`**（`assets/art/vfx/combat_3d/vfx_death_blast_root_top3d.tscn` ＋ `src/vfx/VfxDeathBlast3D.gd`，lifetime 0.62s、带 `BlastLight`、**全向对称**）经 `VfxPool3D` 路由；② 地面残留伤害场 **FX01-18 `VFX-BLAST-ZONE-3D`**（`.../vfx_blast_zone_root_top3d.tscn` ＋ `src/vfx/VfxBlastZone3D.gd`，**纯视觉**无碰撞体、不结算伤害）由玩法节点 `src/enemy3d/DeathBlastZone3D.gd` **宿主自持、刻意不进池**（同 FX01-16／FX03-03 口径）。场地规格 `death_explosion.fat_zombie03.zone = {enabled:true, duration_sec:3.0, damage_per_tick:24, tick_interval_sec:0.5}`（`damage_per_tick` / `tick_interval_sec` 为 2026-10-14 定的默认值）。爆炸尺寸由调用方按 `radius × 0.6` 传入（5.0m ⇒ size 3.0 ⇒ 冲击环外缘 ≈ 4.75–5.29 m，视觉顶到伤害半径）。验收 `verify_death_blast_vfx`；特效账本登记见 `ShellStorm2_特效账本_v001.xlsx`《资产主表》r36/r37 与《3D-特效》FX01-17/FX01-18。</t>
         </is>
       </c>
     </row>
@@ -18680,7 +18803,8 @@
       </c>
       <c r="O17" s="177" t="inlineStr">
         <is>
-          <t>17 Blender剪辑；首次activate6.4s（非伤害技能），四技能/十二态；伤害8%韧性击晕4.8s；通电暴击可打断；独立资产ENM-BOSS-MONITOR002-3D；首次10米触发，出场播完后战斗；显示器Boss由正式触发盒生成于房间中心（局部X/Z=0），初始面向南方（世界+Z）。移动速度由1.204提高至3.612米/秒（3倍；内容speed=123.84）。10米激活及6.4秒出场规则保持。</t>
+          <t>17 Blender剪辑；首次activate6.4s（非伤害技能），四技能/十二态；伤害8%韧性击晕4.8s；通电暴击可打断；独立资产ENM-BOSS-MONITOR002-3D；首次10米触发，出场播完后战斗；显示器Boss由正式触发盒生成于房间中心（局部X/Z=0），初始面向南方（世界+Z）。移动速度由1.204提高至3.612米/秒（3倍；内容speed=123.84）。10米激活及6.4秒出场规则保持。
+【远征01·monster_rules 覆盖 2026-10-14】本关以关卡级 `monster_rules.stats.per_kind` 覆盖生命为 **32000**（覆盖排在身份基线 merge 之后，否则被 hp=200 盖掉）；速度 3.612 m/s 未动。PROFILES / BossContentCatalog 基线未改。见 远征关卡01设计.md §4.5.3。</t>
         </is>
       </c>
     </row>
@@ -19813,7 +19937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T49"/>
+  <dimension ref="A1:T50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" style="135" min="1" max="1"/>
@@ -19862,7 +19986,7 @@
     <row r="2" ht="31.5" customHeight="1" s="135">
       <c r="A2" s="209" t="inlineStr">
         <is>
-          <t>导入ItemRegistry当前44条正式记录与1条设计契约条目（Boss下行专用钥匙），共45条；大型电池、电芯包和三档手电模块均使用正式运行ID。价格0不自动代表免费，进度物不进入普通商店。</t>
+          <t>导入ItemRegistry当前45条正式记录与1条设计契约条目（Boss下行专用钥匙），共46条；大型电池、电芯包和三档手电模块均使用正式运行ID。价格0不自动代表免费，进度物不进入普通商店。花洒机枪（weapon_sprinkler）仅有运行注册，本表未登记。</t>
         </is>
       </c>
       <c r="B2" s="203" t="n"/>
@@ -23832,6 +23956,88 @@
       </c>
       <c r="T49" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="50" ht="54" customHeight="1" s="135">
+      <c r="A50" s="177" t="inlineStr">
+        <is>
+          <t>weapon_starter_rifle</t>
+        </is>
+      </c>
+      <c r="B50" s="177" t="inlineStr">
+        <is>
+          <t>初始步枪</t>
+        </is>
+      </c>
+      <c r="C50" s="177" t="inlineStr">
+        <is>
+          <t>weapon</t>
+        </is>
+      </c>
+      <c r="D50" s="177" t="inlineStr">
+        <is>
+          <t>gun_body</t>
+        </is>
+      </c>
+      <c r="E50" s="177" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F50" s="177" t="n">
+        <v>120</v>
+      </c>
+      <c r="G50" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" s="177" t="inlineStr">
+        <is>
+          <t>出厂配发的突击步枪。高单发伤害与高射速，换弹快，是开局唯一可靠的武器。左键装备为当前主武器。</t>
+        </is>
+      </c>
+      <c r="J50" s="177" t="inlineStr">
+        <is>
+          <t>combat_floor_1×0.4；combat_floor_2×0.6；combat_floor_3×0.75；elite_floor_1×0.75；elite_floor_2×1.25；loot_abyss×1.25；loot_floor_1_2×0.5；loot_floor_3_4×0.75；loot_floor_5×1；scavenge_floor_1×0.25；scavenge_floor_2×0.5；scavenge_floor_3×0.6；scavenge_floor_4×0.75；scavenge_floor_5×1.25</t>
+        </is>
+      </c>
+      <c r="L50" s="180" t="inlineStr">
+        <is>
+          <t>[已实装]</t>
+        </is>
+      </c>
+      <c r="M50" s="177" t="inlineStr">
+        <is>
+          <t>基础成品已注册；作为出厂枪白送，命运槽刻意只有 4 格</t>
+        </is>
+      </c>
+      <c r="N50" s="177" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd</t>
+        </is>
+      </c>
+      <c r="O50" s="177" t="inlineStr">
+        <is>
+          <t>新设计：stack_max=1；生成永久weapon_instance_id，并保存命运槽、子弹模块与配件快照</t>
+        </is>
+      </c>
+      <c r="P50" s="163">
+        <f>IF(F50&gt;0,F50,0)</f>
+        <v/>
+      </c>
+      <c r="Q50" s="163">
+        <f>IF(F50&gt;0,ROUND(F50*0.5,0),0)</f>
+        <v/>
+      </c>
+      <c r="R50" s="151" t="b">
+        <v>0</v>
+      </c>
+      <c r="S50" s="151" t="inlineStr">
+        <is>
+          <t>not_listed</t>
+        </is>
+      </c>
+      <c r="T50" s="163" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx
+++ b/docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E6" s="91" t="inlineStr">
         <is>
-          <t>副枪跟随主枪一起开火</t>
+          <t>副武器挂枪口旁，可叠加横排</t>
         </is>
       </c>
       <c r="F6" s="91" t="inlineStr">
         <is>
-          <t>选择一个枪身，将其挂到当前枪身上，副枪跟随射击</t>
+          <t>选择随身武器的完整装配副本；挂点闲置/背负缩小，开火放大，副武器从自身枪口攻击。</t>
         </is>
       </c>
       <c r="G6" s="91" t="inlineStr">
@@ -5530,7 +5530,7 @@
       <c r="I6" s="91" t="n"/>
       <c r="J6" s="91" t="inlineStr">
         <is>
-          <t>action=ATTACH_GUN_TO_GUN；damage_scale=0.5；fire_rate_scale=0.6；follow_probability=1</t>
+          <t>action=ATTACH_GUN_TO_GUN; damage_scale=0.5; fire_rate_scale=0.6; follow_probability=1</t>
         </is>
       </c>
       <c r="K6" s="91" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="L6" s="91" t="inlineStr">
         <is>
-          <t>[已实装]</t>
+          <t>[用户设计 2026-10-16]</t>
         </is>
       </c>
       <c r="M6" s="91" t="inlineStr">
         <is>
-          <t>[部分实装] 塔罗名称、正/逆位效果快照与通用执行已接入；复杂逆位专属行为继续逐卡QA</t>
+          <t>[已实装] 实体挂点/攻击/读档专项通过；FATE-RULES r3</t>
         </is>
       </c>
       <c r="N6" s="91" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="O6" s="91" t="inlineStr">
         <is>
-          <t>迁移前名称：枪上加枪；稳定ID不变，旧存档迁移为正位，不重投方位</t>
+          <t>迁移前名称：枪上加枪；稳定ID不变，旧存档迁移为正位，不重投方位；2026-10-16实体构筑修订；旧快照不重放。力量射速0.5、击退3m/6m·s为可调工程初值。</t>
         </is>
       </c>
       <c r="P6" s="112" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="T6" s="91" t="inlineStr">
         <is>
-          <t>卡背绕Y轴翻面；逆位整张正面卡牌（含边框、图案、文字与布局）收束180°，并显示逆位效果描述；主枪上出现副枪实体/能量轮廓；同步或派生开火用不同声层区分</t>
+          <t>选择随身武器的完整装配副本；挂点闲置/背负缩小，开火放大，副武器从自身枪口攻击。逆位：挂点移到角色身后，同样可叠加横排、开火放大。</t>
         </is>
       </c>
       <c r="U6" s="91" t="inlineStr">
         <is>
-          <t>[部分实装] 通用卡背/翻牌/逆位倒置已验收；逐卡逆位专属VFX与音效继续QA</t>
+          <t>实体与挂点已接入；独立真实渲染已验证，仍待业主实机手感调优</t>
         </is>
       </c>
       <c r="V6" s="91" t="inlineStr">
@@ -5616,22 +5616,22 @@
       </c>
       <c r="AB6" s="118" t="inlineStr">
         <is>
-          <t>选择一个枪身，将其挂到当前枪身上，副枪跟随射击</t>
+          <t>选择随身武器的完整装配副本；挂点闲置/背负缩小，开火放大，副武器从自身枪口攻击。</t>
         </is>
       </c>
       <c r="AC6" s="118" t="inlineStr">
         <is>
-          <t>action=ATTACH_GUN_TO_GUN；damage_scale=0.5；fire_rate_scale=0.6；follow_probability=1</t>
+          <t>action=ATTACH_GUN_TO_GUN; damage_scale=0.5; fire_rate_scale=0.6; follow_probability=1</t>
         </is>
       </c>
       <c r="AD6" s="115" t="inlineStr">
         <is>
-          <t>主副枪交替开火，单发更强但主枪变慢</t>
+          <t>挂点移到角色身后，同样可叠加横排、开火放大。</t>
         </is>
       </c>
       <c r="AE6" s="115" t="inlineStr">
         <is>
-          <t>action=ATTACH_GUN_TO_GUN; alternate_fire=true; damage_scale=0.85; main_fire_rate_scale=0.85</t>
+          <t>action=ATTACH_GUN_TO_GUN; damage_scale=0.5; fire_rate_scale=0.6; follow_probability=1; mount_reversed=true</t>
         </is>
       </c>
       <c r="AF6" s="122" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="AG6" s="123" t="inlineStr">
         <is>
-          <t>[设计完成/数据已入表/运行时待施工]</t>
+          <t>[FATE-RULES r3；effect_version=3]</t>
         </is>
       </c>
     </row>
@@ -6463,12 +6463,12 @@
       </c>
       <c r="E12" s="91" t="inlineStr">
         <is>
-          <t>子弹飞出去时自动开枪</t>
+          <t>子弹携带所选武器，飞行中自动攻击</t>
         </is>
       </c>
       <c r="F12" s="91" t="inlineStr">
         <is>
-          <t>选择一个子弹和一个枪身，该子弹将携带枪身并自动射击</t>
+          <t>选择随身武器的完整装配副本；每发子弹挂实体模型，远程持续向前开火，近战循环挥击。</t>
         </is>
       </c>
       <c r="G12" s="91" t="inlineStr">
@@ -6484,7 +6484,7 @@
       <c r="I12" s="91" t="n"/>
       <c r="J12" s="91" t="inlineStr">
         <is>
-          <t>action=ATTACH_GUN_TO_BULLET；damage_scale=0.45；fire_rate_scale=0.6；max_attached_gun=1</t>
+          <t>action=ATTACH_GUN_TO_BULLET; damage_scale=0.45; fire_rate_scale=0.6; max_attached_gun=1</t>
         </is>
       </c>
       <c r="K12" s="91" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L12" s="91" t="inlineStr">
         <is>
-          <t>[已实装]</t>
+          <t>[用户设计 2026-10-16]</t>
         </is>
       </c>
       <c r="M12" s="91" t="inlineStr">
         <is>
-          <t>[部分实装] 塔罗名称、正/逆位效果快照与通用执行已接入；复杂逆位专属行为继续逐卡QA</t>
+          <t>[已实装] 实体挂点/攻击/读档专项通过；FATE-RULES r3</t>
         </is>
       </c>
       <c r="N12" s="91" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="O12" s="91" t="inlineStr">
         <is>
-          <t>迁移前名称：子弹背枪；稳定ID不变，旧存档迁移为正位，不重投方位</t>
+          <t>迁移前名称：子弹背枪；稳定ID不变，旧存档迁移为正位，不重投方位；2026-10-16实体构筑修订；旧快照不重放。力量射速0.5、击退3m/6m·s为可调工程初值。</t>
         </is>
       </c>
       <c r="P12" s="112" t="inlineStr">
@@ -6534,12 +6534,12 @@
       </c>
       <c r="T12" s="91" t="inlineStr">
         <is>
-          <t>卡背绕Y轴翻面；逆位整张正面卡牌（含边框、图案、文字与布局）收束180°，并显示逆位效果描述；投射物上可见微型枪械或等价轮廓；派生开火有独立枪口焰且来源可追溯</t>
+          <t>选择随身武器的完整装配副本；每发子弹挂实体模型，远程持续向前开火，近战循环挥击。逆位：携枪枪口朝弹体后方，远程持续反向开火，近战朝后挥击。</t>
         </is>
       </c>
       <c r="U12" s="91" t="inlineStr">
         <is>
-          <t>[部分实装] 通用卡背/翻牌/逆位倒置已验收；逐卡逆位专属VFX与音效继续QA</t>
+          <t>实体与挂点已接入；独立真实渲染已验证，仍待业主实机手感调优</t>
         </is>
       </c>
       <c r="V12" s="91" t="inlineStr">
@@ -6570,22 +6570,22 @@
       </c>
       <c r="AB12" s="118" t="inlineStr">
         <is>
-          <t>选择一个子弹和一个枪身，该子弹将携带枪身并自动射击</t>
+          <t>选择随身武器的完整装配副本；每发子弹挂实体模型，远程持续向前开火，近战循环挥击。</t>
         </is>
       </c>
       <c r="AC12" s="118" t="inlineStr">
         <is>
-          <t>action=ATTACH_GUN_TO_BULLET；damage_scale=0.45；fire_rate_scale=0.6；max_attached_gun=1</t>
+          <t>action=ATTACH_GUN_TO_BULLET; damage_scale=0.45; fire_rate_scale=0.6; max_attached_gun=1</t>
         </is>
       </c>
       <c r="AD12" s="115" t="inlineStr">
         <is>
-          <t>携枪子弹只在命中时开一次高伤射击</t>
+          <t>携枪枪口朝弹体后方，远程持续反向开火，近战朝后挥击。</t>
         </is>
       </c>
       <c r="AE12" s="115" t="inlineStr">
         <is>
-          <t>action=ATTACH_GUN_TO_BULLET; trigger=ON_HIT; shots=1; damage_scale=0.75</t>
+          <t>action=ATTACH_GUN_TO_BULLET; damage_scale=0.45; fire_rate_scale=0.6; max_attached_gun=1; mount_reversed=true</t>
         </is>
       </c>
       <c r="AF12" s="122" t="inlineStr">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="AG12" s="123" t="inlineStr">
         <is>
-          <t>[设计完成/数据已入表/运行时待施工]</t>
+          <t>[FATE-RULES r3；effect_version=3]</t>
         </is>
       </c>
     </row>
@@ -6622,12 +6622,12 @@
       </c>
       <c r="E13" s="91" t="inlineStr">
         <is>
-          <t>伤害提升 50%，无视护盾</t>
+          <t>滚石弹：弹速与射速减半</t>
         </is>
       </c>
       <c r="F13" s="91" t="inlineStr">
         <is>
-          <t>选择一个节点，伤害提升 50%，无视护盾减伤效果</t>
+          <t>子弹变为石头，弹速乘0.5，射速乘0.5，重力落地后沿实际地面滚动。</t>
         </is>
       </c>
       <c r="G13" s="91" t="inlineStr">
@@ -6643,7 +6643,7 @@
       <c r="I13" s="91" t="n"/>
       <c r="J13" s="91" t="inlineStr">
         <is>
-          <t>action=ADD_DAMAGE；damage_scale=1.5；pierce_shield=true</t>
+          <t>action=ADD_DAMAGE; rock_projectile=true; rock_shatter=false; fire_rate_scale=0.5</t>
         </is>
       </c>
       <c r="K13" s="91" t="inlineStr">
@@ -6653,12 +6653,12 @@
       </c>
       <c r="L13" s="91" t="inlineStr">
         <is>
-          <t>[已实装]</t>
+          <t>[用户设计 2026-10-16]</t>
         </is>
       </c>
       <c r="M13" s="91" t="inlineStr">
         <is>
-          <t>[部分实装] 塔罗名称、正/逆位效果快照与通用执行已接入；复杂逆位专属行为继续逐卡QA</t>
+          <t>[已实装] 实体挂点/攻击/读档专项通过；FATE-RULES r3</t>
         </is>
       </c>
       <c r="N13" s="91" t="inlineStr">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="O13" s="91" t="inlineStr">
         <is>
-          <t>迁移前名称：穿甲强化；稳定ID不变，旧存档迁移为正位，不重投方位</t>
+          <t>迁移前名称：穿甲强化；稳定ID不变，旧存档迁移为正位，不重投方位；2026-10-16实体构筑修订；旧快照不重放。力量射速0.5、击退3m/6m·s为可调工程初值。</t>
         </is>
       </c>
       <c r="P13" s="112" t="inlineStr">
@@ -6693,12 +6693,12 @@
       </c>
       <c r="T13" s="91" t="inlineStr">
         <is>
-          <t>卡背绕Y轴翻面；逆位整张正面卡牌（含边框、图案、文字与布局）收束180°，并显示逆位效果描述；弹体使用贯穿线；护甲命中出现破盾裂纹与剩余穿透提示</t>
+          <t>子弹变为石头，弹速乘0.5，射速乘0.5，重力落地后沿实际地面滚动。逆位：同样变为滚石；命中怪物或障碍后碎裂，击退3米内怪物，无额外范围伤害。</t>
         </is>
       </c>
       <c r="U13" s="91" t="inlineStr">
         <is>
-          <t>[部分实装] 通用卡背/翻牌/逆位倒置已验收；逐卡逆位专属VFX与音效继续QA</t>
+          <t>实体与挂点已接入；独立真实渲染已验证，仍待业主实机手感调优</t>
         </is>
       </c>
       <c r="V13" s="91" t="inlineStr">
@@ -6729,22 +6729,22 @@
       </c>
       <c r="AB13" s="118" t="inlineStr">
         <is>
-          <t>选择一个节点，伤害提升 50%，无视护盾减伤效果</t>
+          <t>子弹变为石头，弹速乘0.5，射速乘0.5，重力落地后沿实际地面滚动。</t>
         </is>
       </c>
       <c r="AC13" s="118" t="inlineStr">
         <is>
-          <t>action=ADD_DAMAGE；damage_scale=1.5；pierce_shield=true</t>
+          <t>action=ADD_DAMAGE; rock_projectile=true; rock_shatter=false; fire_rate_scale=0.5</t>
         </is>
       </c>
       <c r="AD13" s="115" t="inlineStr">
         <is>
-          <t>伤害+15%，不穿盾但对护盾×2</t>
+          <t>同样变为滚石；命中怪物或障碍后碎裂，击退3米内怪物，无额外范围伤害。</t>
         </is>
       </c>
       <c r="AE13" s="115" t="inlineStr">
         <is>
-          <t>action=ADD_DAMAGE; damage_scale=1.15; pierce_shield=false; shield_damage_scale=2</t>
+          <t>action=ADD_DAMAGE; rock_projectile=true; rock_shatter=true; fire_rate_scale=0.5</t>
         </is>
       </c>
       <c r="AF13" s="122" t="inlineStr">
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AG13" s="123" t="inlineStr">
         <is>
-          <t>[设计完成/数据已入表/运行时待施工]</t>
+          <t>[FATE-RULES r3；effect_version=3]</t>
         </is>
       </c>
     </row>

--- a/docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx
+++ b/docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx
@@ -4571,7 +4571,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>左横斩→右回斩→过顶重劈；每段前摇/命中/后摇；无弹药与换弹</t>
+          <t>点按松开左右横扫三连；按住0.35秒旋风；每0.25秒伤害×0.55，松开0.3秒收势</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -4614,22 +4614,22 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>[已实装并验收] 四态动作机、三段缓存、扇区/墙体/去重、伤害/击退/中断与反馈闭环</t>
+          <t>[已实装并专项验收] 六态近战动作机；含充能/持续旋转与打断</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>HUD显示近战·三段；动作快照显示阶段、进度、攻击ID；挥空有弧光/切风声，命中有爆点/冲击声</t>
+          <t>点按/按住由攻击键决定；快照提供charge_ratio/spin_progress</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>双手重型持握；青色能量断刃；三段弧光方向可辨，第三段尺寸与冲击最强</t>
+          <t>点按松开左右横扫三连；按住0.35秒旋风；每0.25秒伤害×0.55，松开0.3秒收势；Blender v041角色动作；五种专属VFX</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>[核心已验收] 程序模型/三段动作/参数化VFX/专属音频完成；最终模型与低特效模式待替换/复验</t>
+          <t>[专项通过] 源37动作、运行/真实渲染；完整游戏与移动端未验；docs/v0.1/development/2026-10-16_melee_styles_v041.md</t>
         </is>
       </c>
       <c r="W26" t="n">
@@ -4673,12 +4673,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>damage=46；reach=2.85m；arc=100°；knockback=7.2；combo=3</t>
+          <t>damage=46；reach=2.85m；arc=100°；knockback=7.2；combo=3；普通预备0.48/0.52/0.65s，有效0.14/0.16/0.20s，收势0.40/0.46/0.65s；蓄力伤害1.2→2/击退1.4→2.6</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>上挑斩→交叉斩→砸地裂斩；高伤高击退；无弹药与换弹</t>
+          <t>慢速下劈；按住蓄力1秒上限，松开强击退；普通2帧/蓄力4帧停顿</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -4721,22 +4721,22 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>[已实装并验收] 四态动作机、三段缓存、扇区/墙体/去重、伤害/击退/中断与反馈闭环</t>
+          <t>[已实装并专项验收] 六态近战动作机；含充能/持续旋转与打断</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>HUD显示近战·三段；动作快照显示阶段、进度、攻击ID；挥空有弧光/切风声，命中有爆点/冲击声</t>
+          <t>点按/按住由攻击键决定；快照提供charge_ratio/spin_progress</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>双手长柄持握；橙色冲击核心；第三段最大过顶弧光，音高更低、冲击更重</t>
+          <t>慢速下劈；按住蓄力1秒上限，松开强击退；普通2帧/蓄力4帧停顿；Blender v041角色动作；五种专属VFX</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>[核心已验收] 程序模型/三段动作/参数化VFX/专属音频完成；最终模型与低特效模式待替换/复验</t>
+          <t>[专项通过] 源37动作、运行/真实渲染；完整游戏与移动端未验；docs/v0.1/development/2026-10-16_melee_styles_v041.md</t>
         </is>
       </c>
       <c r="W27" t="n">
@@ -4785,7 +4785,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>左横扫→右回扫→蓄力重挥；初级快速近战；无弹药与换弹</t>
+          <t>普通三连挥棒；按下立即攻击；1帧停顿</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -4828,22 +4828,22 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>[已实装并验收] 复用ready/windup/active/recovery四态、三段缓存、扇区/遮挡/去重、伤害/击退/中断与反馈闭环</t>
+          <t>[已实装并专项验收] 六态近战动作机；含充能/持续旋转与打断</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>HUD显示近战·三段；第三段反馈增强；基地货架明确初级定位</t>
+          <t>点按/按住由攻击键决定；快照提供charge_ratio/spin_progress</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>双手挥击；木质粗大轮廓、金属加固环；沿local -Z延伸，背负/手持轮廓清晰</t>
+          <t>普通三连挥棒；按下立即攻击；1帧停顿；Blender v041角色动作；五种专属VFX</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>[核心已验收] 程序模型/三段动作/VFX/音频完成；最终模型待替换</t>
+          <t>[专项通过] 源37动作、运行/真实渲染；完整游戏与移动端未验；docs/v0.1/development/2026-10-16_melee_styles_v041.md</t>
         </is>
       </c>
       <c r="U28" t="n">
@@ -23743,7 +23743,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>宽扇区三段重型挥砍；第三段过顶重劈强化伤害与击退；无弹药/换弹。</t>
+          <t>点按松开左右横扫三连；按住0.35秒旋风；每0.25秒伤害×0.55，松开0.3秒收势</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -23826,7 +23826,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>高伤高击退三段攻城斧；第三段砸地前后摇较长；无弹药/换弹。</t>
+          <t>慢速下劈；按住蓄力1秒上限，松开强击退；普通2帧/蓄力4帧停顿</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -23909,7 +23909,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>基地贩卖机初级近战；三段快速挥击，第三段强化伤害与击退</t>
+          <t>普通三连挥棒；按下立即攻击；1帧停顿</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">

--- a/docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx
+++ b/docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="武器" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命运卡" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物与Boss" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="精英怪" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掉落物品" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段字典" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="基地商店" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Boss002技能设计" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="总览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="武器" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="命运卡" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="怪物与Boss" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="精英怪" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="掉落物品" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="字段字典" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="基地商店" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Boss002技能设计" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -2023,7 +2023,7 @@
     <row r="2" ht="30" customHeight="1" s="135">
       <c r="A2" s="209" t="inlineStr">
         <is>
-          <t>正式注册：7远程枪身、2大型近战武器、8子弹、6配件。独立WeaponInstance与普通武器8命运槽已实装；近战四态/三段/命中闭环已验收，逐条最终美术与专属音频继续QA。</t>
+          <t>正式注册：7远程枪身、2大型近战武器、8子弹、6配件。独立WeaponInstance与普通武器8命运槽已实装；近战四态/三段/命中闭环已验收，逐条最终美术与专属音频继续QA。 掉落品质（2026-10-18）：掉落的枪械逐把随机蓝/紫/金，蓝=基础、紫=伤害+10% 且命运槽+2、金=伤害+15% 且命运槽+4；本表「基础命运槽」是蓝枪基线，紫/金在其上叠加。规则见 04 §22.13。 绑定弹药（2026-10-18）：掉落的远程枪械在掉落那一刻按权重掷定一个弹药模块并锁定，不可拆卸/替换；近战无弹药槽；非掉落来源不锁。规则见 04 §22.14。</t>
         </is>
       </c>
       <c r="B2" s="203" t="n"/>
@@ -17963,7 +17963,7 @@
       </c>
       <c r="K5" s="177" t="inlineStr">
         <is>
-          <t>由房间/楼层掉落表决定</t>
+          <t>由房间/楼层掉落表决定（远程枪械 0%，近战保留）</t>
         </is>
       </c>
       <c r="L5" s="180" t="inlineStr">
@@ -18030,7 +18030,7 @@
       </c>
       <c r="K6" s="177" t="inlineStr">
         <is>
-          <t>boss_floor_*</t>
+          <t>boss_weapon_floor_* ×1-2 把 + boss_floor_* ×3 件 + 弹药 ×1（合计 5-6 件）</t>
         </is>
       </c>
       <c r="L6" s="180" t="inlineStr">
@@ -18097,7 +18097,7 @@
       </c>
       <c r="K7" s="177" t="inlineStr">
         <is>
-          <t>由房间/楼层掉落表决定</t>
+          <t>由房间/楼层掉落表决定（远程枪械 0%，近战保留）</t>
         </is>
       </c>
       <c r="L7" s="180" t="inlineStr">
@@ -18164,7 +18164,7 @@
       </c>
       <c r="K8" s="177" t="inlineStr">
         <is>
-          <t>由房间/楼层掉落表决定</t>
+          <t>由房间/楼层掉落表决定（远程枪械 0%，近战保留）</t>
         </is>
       </c>
       <c r="L8" s="180" t="inlineStr">
@@ -18232,7 +18232,7 @@
       </c>
       <c r="K9" s="177" t="inlineStr">
         <is>
-          <t>由房间/楼层掉落表决定</t>
+          <t>由房间/楼层掉落表决定（远程枪械 0%，近战保留）</t>
         </is>
       </c>
       <c r="L9" s="180" t="inlineStr">
@@ -18300,7 +18300,7 @@
       </c>
       <c r="K10" s="177" t="inlineStr">
         <is>
-          <t>由房间/楼层掉落表决定</t>
+          <t>由房间/楼层掉落表决定（远程枪械 0%，近战保留）</t>
         </is>
       </c>
       <c r="L10" s="180" t="inlineStr">
@@ -18367,7 +18367,7 @@
       </c>
       <c r="K11" s="177" t="inlineStr">
         <is>
-          <t>由房间/楼层掉落表决定</t>
+          <t>由房间/楼层掉落表决定（远程枪械 0%，近战保留）</t>
         </is>
       </c>
       <c r="L11" s="180" t="inlineStr">
@@ -18434,7 +18434,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>boss_floor_5；专用下行权限</t>
+          <t>boss_weapon_floor_N ×1-2 把 + boss_floor_N ×3 件 + 弹药 ×1（合计 5-6 件）；专用下行权限</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -18501,7 +18501,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>boss_floor_10；专用下行权限</t>
+          <t>boss_weapon_floor_N ×1-2 把 + boss_floor_N ×3 件 + 弹药 ×1（合计 5-6 件）；专用下行权限</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -18568,7 +18568,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>boss_floor_15；专用下行权限</t>
+          <t>boss_weapon_floor_N ×1-2 把 + boss_floor_N ×3 件 + 弹药 ×1（合计 5-6 件）；专用下行权限</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -18645,7 +18645,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>待定</t>
+          <t>由房间/楼层掉落表决定（远程枪械 0%，近战保留）</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -18714,7 +18714,7 @@
       </c>
       <c r="K16" s="177" t="inlineStr">
         <is>
-          <t>通用楼层掉落表；killed一次结算</t>
+          <t>由房间/楼层掉落表决定（远程枪械 0%，近战保留）</t>
         </is>
       </c>
       <c r="L16" s="180" t="inlineStr">
@@ -18783,7 +18783,7 @@
       </c>
       <c r="K17" s="177" t="inlineStr">
         <is>
-          <t>Enemy3D Boss结算与既有房间奖励</t>
+          <t>boss_weapon_floor_N ×1-2 把 + boss_floor_N ×3 件 + 弹药 ×1（合计 5-6 件）；专用下行权限</t>
         </is>
       </c>
       <c r="L17" s="180" t="inlineStr">
@@ -22275,7 +22275,7 @@
       </c>
       <c r="J30" s="177" t="inlineStr">
         <is>
-          <t>boss_floor_2×4；combat_floor_4×0.5；combat_floor_5×1；elite_floor_2×3；loot_abyss×2；loot_floor_5×0.8；scavenge_floor_4×0.4；scavenge_floor_5×1</t>
+          <t>boss_weapon_floor_2×1；combat_floor_4×0.5；combat_floor_5×1；elite_floor_2×3；scavenge_floor_4×0.4；scavenge_floor_5×0.7；strong_weapon_floor_2×0.5</t>
         </is>
       </c>
       <c r="K30" s="177" t="str"/>
@@ -22359,7 +22359,7 @@
       </c>
       <c r="J31" s="177" t="inlineStr">
         <is>
-          <t>boss_floor_1×2.5；boss_floor_2×4；combat_floor_3×0.8；combat_floor_4×0.5；combat_floor_5×1；elite_floor_2×3；loot_abyss×2.5；loot_floor_3_4×1；loot_floor_5×1.5；scavenge_floor_3×0.5；scavenge_floor_4×1；scavenge_floor_5×2</t>
+          <t>boss_weapon_floor_1×1；boss_weapon_floor_2×1；combat_floor_3×0.8；combat_floor_4×0.5；combat_floor_5×1；elite_floor_2×3；scavenge_floor_3×0.5；scavenge_floor_4×1；scavenge_floor_5×1.4；strong_weapon_floor_2×0.8</t>
         </is>
       </c>
       <c r="K31" s="177" t="str"/>
@@ -22443,7 +22443,7 @@
       </c>
       <c r="J32" s="177" t="inlineStr">
         <is>
-          <t>combat_floor_1×0.8；combat_floor_2×1.2；combat_floor_3×1.5；elite_floor_1×1.5；elite_floor_2×2.5；loot_abyss×2.5；loot_floor_1_2×1；loot_floor_3_4×1.5；loot_floor_5×2；scavenge_floor_1×0.5；scavenge_floor_2×1；scavenge_floor_3×1.2；scavenge_floor_4×1.5；scavenge_floor_5×2.5</t>
+          <t>boss_weapon_floor_1×0.8；boss_weapon_floor_2×0.8；combat_floor_1×0.8；combat_floor_2×1.2；combat_floor_3×1.5；elite_floor_1×1.5；elite_floor_2×2.5；scavenge_floor_1×0.5；scavenge_floor_2×1；scavenge_floor_3×1.2；scavenge_floor_4×1.5；scavenge_floor_5×1.75；strong_weapon_floor_1×0.6；strong_weapon_floor_2×1</t>
         </is>
       </c>
       <c r="K32" s="177" t="str"/>
@@ -22527,7 +22527,7 @@
       </c>
       <c r="J33" s="177" t="inlineStr">
         <is>
-          <t>combat_floor_1×0.5；combat_floor_2×0.8；loot_floor_1_2×0.8；scavenge_floor_1×0.8；scavenge_floor_2×1.4</t>
+          <t>combat_floor_1×0.5；combat_floor_2×0.8；scavenge_floor_1×0.8；scavenge_floor_2×1.4；strong_weapon_floor_1×1</t>
         </is>
       </c>
       <c r="K33" s="177" t="str"/>
@@ -22609,7 +22609,7 @@
       </c>
       <c r="J34" s="177" t="inlineStr">
         <is>
-          <t>boss_floor_1×2；boss_floor_2×3；combat_floor_1×0.5；combat_floor_2×1；combat_floor_3×1.5；elite_floor_1×1.5；elite_floor_2×2；loot_abyss×2.5；loot_floor_1_2×0.3；loot_floor_3_4×1.5；loot_floor_5×2；scavenge_floor_3×1；scavenge_floor_4×1.5；scavenge_floor_5×2</t>
+          <t>boss_weapon_floor_1×1；boss_weapon_floor_2×1；combat_floor_1×0.5；combat_floor_2×1；combat_floor_3×1.5；elite_floor_1×1.5；elite_floor_2×2；scavenge_floor_3×1；scavenge_floor_4×1.5；scavenge_floor_5×1.4；strong_weapon_floor_1×0.4；strong_weapon_floor_2×1</t>
         </is>
       </c>
       <c r="K34" s="177" t="str"/>
@@ -22691,7 +22691,7 @@
       </c>
       <c r="J35" s="177" t="inlineStr">
         <is>
-          <t>combat_floor_1×0.8；combat_floor_2×1.2；loot_floor_1_2×1；scavenge_floor_1×1.4；scavenge_floor_2×2；spawn_starter×3</t>
+          <t>boss_weapon_floor_1×0.8；combat_floor_1×0.8；combat_floor_2×1.2；scavenge_floor_1×1.4；scavenge_floor_2×2；spawn_starter×3；strong_weapon_floor_1×1；strong_weapon_floor_2×0.6</t>
         </is>
       </c>
       <c r="K35" s="177" t="str"/>
@@ -22773,7 +22773,7 @@
       </c>
       <c r="J36" s="177" t="inlineStr">
         <is>
-          <t>boss_floor_1×2；boss_floor_2×4；combat_floor_2×0.3；combat_floor_3×0.8；elite_floor_1×1.5；elite_floor_2×2；loot_abyss×2.5；loot_floor_3_4×0.5；loot_floor_5×1.5；scavenge_floor_3×0.5；scavenge_floor_4×1；scavenge_floor_5×2</t>
+          <t>boss_weapon_floor_1×1；boss_weapon_floor_2×1；combat_floor_2×0.3；combat_floor_3×0.8；elite_floor_1×1.5；elite_floor_2×2；scavenge_floor_3×0.5；scavenge_floor_4×1；scavenge_floor_5×1.4；strong_weapon_floor_2×0.8</t>
         </is>
       </c>
       <c r="K36" s="177" t="str"/>
@@ -23221,7 +23221,7 @@
       </c>
       <c r="J41" s="167" t="inlineStr">
         <is>
-          <t>loot_common×2；loot_floor_1_2×2.5；spawn_starter×2；combat_floor_1-5×1.5；base_vending unlimited</t>
+          <t>combat_floor_1×1.5；combat_floor_2×1.5；combat_floor_3×1.5；combat_floor_4×1.5；combat_floor_5×1.5；loot_common×2；loot_floor_1_2×2.5；spawn_starter×2；combat_floor_1-5×1.5；base_vending unlimited</t>
         </is>
       </c>
       <c r="K41" s="167" t="n">
@@ -23309,7 +23309,7 @@
       </c>
       <c r="J42" s="167" t="inlineStr">
         <is>
-          <t>loot_floor_3_4×1.2；scavenge_floor_3×1；scavenge_floor_4×1；scavenge_floor_5×1；elite_floor_1×0.8；elite_floor_2×0.8；boss_floor_1×1.5</t>
+          <t>boss_floor_1×1.5；elite_floor_1×0.8；elite_floor_2×0.8；loot_floor_3_4×1.2；scavenge_floor_3×1；scavenge_floor_4×1；scavenge_floor_5×1</t>
         </is>
       </c>
       <c r="K42" s="167" t="n">
@@ -23399,7 +23399,7 @@
       </c>
       <c r="J43" s="167" t="inlineStr">
         <is>
-          <t>loot_floor_5×0.6；loot_abyss×1；boss_floor_2×1.5</t>
+          <t>boss_floor_2×1.5；loot_abyss×1；loot_floor_5×0.6</t>
         </is>
       </c>
       <c r="K43" s="167" t="n">
@@ -23665,7 +23665,7 @@
       </c>
       <c r="J46" s="167" t="inlineStr">
         <is>
-          <t>elite_floor_1×0.6；elite_floor_2×0.8；boss_floor_2×1</t>
+          <t>boss_floor_2×1；elite_floor_1×0.6；elite_floor_2×0.8</t>
         </is>
       </c>
       <c r="K46" s="167" t="n"/>
@@ -23748,7 +23748,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>spawn_starter×1.2；loot_floor_1_2×0.75；loot_floor_3_4×1.2；scavenge_floor_1×0.65；scavenge_floor_2×1.1；combat_floor_1×0.5；combat_floor_2×0.9</t>
+          <t>combat_floor_1×0.5；combat_floor_2×0.9；loot_floor_1_2×0.75；loot_floor_3_4×1.2；scavenge_floor_1×0.65；scavenge_floor_2×1.1；spawn_starter×1.2</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -23831,7 +23831,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>loot_floor_1_2×0.18；loot_floor_3_4×0.95；loot_floor_5×1.45；loot_abyss×1.8；scavenge_floor_3×0.8；combat_floor_3×0.72；elite_floor_1×1.2；elite_floor_2×1.8</t>
+          <t>combat_floor_3×0.72；elite_floor_1×1.2；elite_floor_2×1.8；loot_abyss×1.8；loot_floor_1_2×0.18；loot_floor_3_4×0.95；loot_floor_5×1.45；scavenge_floor_3×0.8</t>
         </is>
       </c>
       <c r="K48" t="n">
@@ -23914,7 +23914,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>spawn_starter×2.2；loot_floor_1_2×1.6；scavenge_floor_1×1.8；scavenge_floor_2×1.2；combat_floor_1×1.0；base_vending unlimited</t>
+          <t>combat_floor_1×1；loot_floor_1_2×1.6；scavenge_floor_1×1.8；scavenge_floor_2×1.2；spawn_starter×2.2；base_vending unlimited</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -23997,7 +23997,7 @@
       </c>
       <c r="J50" s="177" t="inlineStr">
         <is>
-          <t>combat_floor_1×0.4；combat_floor_2×0.6；combat_floor_3×0.75；elite_floor_1×0.75；elite_floor_2×1.25；loot_abyss×1.25；loot_floor_1_2×0.5；loot_floor_3_4×0.75；loot_floor_5×1；scavenge_floor_1×0.25；scavenge_floor_2×0.5；scavenge_floor_3×0.6；scavenge_floor_4×0.75；scavenge_floor_5×1.25</t>
+          <t>boss_weapon_floor_2×0.4；combat_floor_1×0.4；combat_floor_2×0.6；combat_floor_3×0.75；elite_floor_1×0.75；elite_floor_2×1.25；scavenge_floor_1×0.25；scavenge_floor_2×0.5；scavenge_floor_3×0.6；scavenge_floor_4×0.75；scavenge_floor_5×0.88；strong_weapon_floor_1×0.8；strong_weapon_floor_2×0.5</t>
         </is>
       </c>
       <c r="L50" s="180" t="inlineStr">
@@ -24061,7 +24061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="135" min="1" max="1"/>
@@ -26591,6 +26591,154 @@
       <c r="H62" t="inlineStr">
         <is>
           <t>[已实装并验收]</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="192" t="inlineStr">
+        <is>
+          <t>武器</t>
+        </is>
+      </c>
+      <c r="B63" s="192" t="inlineStr">
+        <is>
+          <t>drop_grade</t>
+        </is>
+      </c>
+      <c r="C63" s="192" t="inlineStr">
+        <is>
+          <t>掉落品质：blue=基础 / purple=伤害+10%、命运槽+2 / gold=伤害+15%、命运槽+4</t>
+        </is>
+      </c>
+      <c r="D63" s="192" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="E63" s="192" t="inlineStr">
+        <is>
+          <t>掉落枪械必填</t>
+        </is>
+      </c>
+      <c r="F63" s="192" t="inlineStr">
+        <is>
+          <t>武器实例/奖励服务</t>
+        </is>
+      </c>
+      <c r="G63" s="192" t="inlineStr">
+        <is>
+          <t>三值枚举；非掉落来源（出厂枪/蓝图合成/商人）固定 blue；逐把掷骰，同箱可不同</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="192" t="inlineStr">
+        <is>
+          <t>武器</t>
+        </is>
+      </c>
+      <c r="B64" s="192" t="inlineStr">
+        <is>
+          <t>grade_damage_multiplier</t>
+        </is>
+      </c>
+      <c r="C64" s="192" t="inlineStr">
+        <is>
+          <t>品质伤害倍率，运行时由装配树出口折算（1.00/1.10/1.15）</t>
+        </is>
+      </c>
+      <c r="D64" s="192" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="E64" s="192" t="inlineStr">
+        <is>
+          <t>运行时派生</t>
+        </is>
+      </c>
+      <c r="F64" s="192" t="inlineStr">
+        <is>
+          <t>装配树</t>
+        </is>
+      </c>
+      <c r="G64" s="192" t="inlineStr">
+        <is>
+          <t>不入 assembly_snapshot；读档不得复利；damage 与 bullet_damage 同步乘</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="192" t="inlineStr">
+        <is>
+          <t>武器</t>
+        </is>
+      </c>
+      <c r="B65" s="192" t="inlineStr">
+        <is>
+          <t>bullet_module_locked</t>
+        </is>
+      </c>
+      <c r="C65" s="192" t="inlineStr">
+        <is>
+          <t>弹药模块是否绑定锁定：掉落枪为 true（不可拆卸/替换）；出厂、蓝图合成、商人购入为 false</t>
+        </is>
+      </c>
+      <c r="D65" s="192" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="E65" s="192" t="inlineStr">
+        <is>
+          <t>掉落远程枪必填</t>
+        </is>
+      </c>
+      <c r="F65" s="192" t="inlineStr">
+        <is>
+          <t>武器实例/奖励服务</t>
+        </is>
+      </c>
+      <c r="G65" s="192" t="inlineStr">
+        <is>
+          <t>随实例持久化；三条换弹入口（Player3D / Dungeon3D / WorkbenchPanel）一律拒绝；近战恒 false</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="192" t="inlineStr">
+        <is>
+          <t>武器</t>
+        </is>
+      </c>
+      <c r="B66" s="192" t="inlineStr">
+        <is>
+          <t>bullet_module_id</t>
+        </is>
+      </c>
+      <c r="C66" s="192" t="inlineStr">
+        <is>
+          <t>掉落时掷定的弹药模块内容ID（装配快照的输入，非运行时派生值）</t>
+        </is>
+      </c>
+      <c r="D66" s="192" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E66" s="192" t="inlineStr">
+        <is>
+          <t>掉落远程枪必填</t>
+        </is>
+      </c>
+      <c r="F66" s="192" t="inlineStr">
+        <is>
+          <t>奖励服务</t>
+        </is>
+      </c>
+      <c r="G66" s="192" t="inlineStr">
+        <is>
+          <t>必须存在于 ItemRegistry 且 subtype=bullet；未知值回落 mod_bullet_standard</t>
         </is>
       </c>
     </row>

--- a/docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx
+++ b/docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx
@@ -24061,7 +24061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H66"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="135" min="1" max="1"/>
@@ -25095,7 +25095,7 @@
       </c>
       <c r="C27" s="45" t="inlineStr">
         <is>
-          <t>可拆卸配件与子弹模块槽位快照</t>
+          <t>配件槽位与子弹模块只读快照</t>
         </is>
       </c>
       <c r="D27" s="45" t="inlineStr">
@@ -25115,7 +25115,7 @@
       </c>
       <c r="G27" s="45" t="inlineStr">
         <is>
-          <t>不占命运槽；卸装与交换必须事务化</t>
+          <t>配件不占命运槽，卸装与交换必须事务化；子弹模块不提供手动更换（2026-10-19），仅随实例保存</t>
         </is>
       </c>
       <c r="H27" s="47" t="inlineStr">
@@ -26681,7 +26681,7 @@
       </c>
       <c r="C65" s="192" t="inlineStr">
         <is>
-          <t>弹药模块是否绑定锁定：掉落枪为 true（不可拆卸/替换）；出厂、蓝图合成、商人购入为 false</t>
+          <t>弹药模块是否绑定锁定：掉落枪为 true（弹种是这把枪的身份）；出厂、蓝图合成、商人购入为非掉落来源，保持 false</t>
         </is>
       </c>
       <c r="D65" s="192" t="inlineStr">
@@ -26701,11 +26701,11 @@
       </c>
       <c r="G65" s="192" t="inlineStr">
         <is>
-          <t>随实例持久化；三条换弹入口（Player3D / Dungeon3D / WorkbenchPanel）一律拒绝；近战恒 false</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
+          <t>随实例持久化；身份锁只决定拒绝原因，不决定渠道；2026-10-19 起手动更换总闸关闭，Player3D / Dungeon3D / InventoryUI / ItemSlot 一律拒绝；近战恒 false</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" s="135">
       <c r="A66" s="192" t="inlineStr">
         <is>
           <t>武器</t>
@@ -26739,6 +26739,48 @@
       <c r="G66" s="192" t="inlineStr">
         <is>
           <t>必须存在于 ItemRegistry 且 subtype=bullet；未知值回落 mod_bullet_standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="192" t="inlineStr">
+        <is>
+          <t>武器</t>
+        </is>
+      </c>
+      <c r="B67" s="192" t="inlineStr">
+        <is>
+          <t>bullet_module_swap_channel</t>
+        </is>
+      </c>
+      <c r="C67" s="192" t="inlineStr">
+        <is>
+          <t>弹药模块更换渠道：manual_locked = 玩家不能从背包/装备界面/局内快捷装配手动更换；workshop = 仅枪械工坊特殊流程</t>
+        </is>
+      </c>
+      <c r="D67" s="192" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="E67" s="192" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F67" s="192" t="inlineStr">
+        <is>
+          <t>武器实例/UI/基地设施</t>
+        </is>
+      </c>
+      <c r="G67" s="192" t="inlineStr">
+        <is>
+          <t>当前恒为 manual_locked；背包左键、拖武器格、局内快捷装配、改造台均拒绝；枪械工坊流程未实现，不得以任何旁路恢复手动换弹</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>[用户设计]</t>
         </is>
       </c>
     </row>

--- a/docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx
+++ b/docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx
@@ -4102,7 +4102,7 @@
       </c>
       <c r="G22" s="177" t="inlineStr">
         <is>
-          <t>bullet_count=1；damage=25；fire_rate=3.5；magazine_size=12；reload_time=1.5；spread=0.03；range=15</t>
+          <t>bullet_count=1；damage=25；fire_rate=3.5；magazine_size=10；reload_time=1.5；spread=0.03；range=15；bullet_speed=25/23（≈1.087，弹速 25 m/s）</t>
         </is>
       </c>
       <c r="H22" s="177" t="inlineStr">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="N22" s="177" t="inlineStr">
         <is>
-          <t>装配ID=bp_pistol；成品物品ID=weapon_pistol；蓝图物品ID=bp_pistol</t>
+          <t>装配ID=bp_pistol；成品物品ID=weapon_pistol；蓝图物品ID=bp_pistol；2026-10-30 弹匣 12→10、弹速 23→25 m/s，对标《挺进地牢》陆战队员 Marine Sidearm（Magazine 10 / Shot Speed 25）；伤害/射速/换弹/扩散/射程未动</t>
         </is>
       </c>
       <c r="O22" s="46" t="n">

--- a/docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx
+++ b/docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx
@@ -343,7 +343,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="22">
     <border/>
     <border>
       <left style="thin">
@@ -539,11 +539,25 @@
     </border>
     <border/>
     <border/>
+    <border>
+      <left style="thin">
+        <color rgb="FFB8C4D4"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB8C4D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB8C4D4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB8C4D4"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="32" fillId="22" borderId="20"/>
   </cellStyleXfs>
-  <cellXfs count="215">
+  <cellXfs count="216">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1053,6 +1067,9 @@
     <xf numFmtId="165" fontId="33" fillId="25" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -1355,7 +1372,7 @@
     <row r="2" ht="30" customHeight="1" s="135">
       <c r="A2" s="204" t="inlineStr">
         <is>
-          <t>设计、内容与实现状态的中央索引｜最后校对：2026-10-14｜正式入口：TowerDescent3D.tscn</t>
+          <t>设计、内容与实现状态的中央索引｜最后校对：2026-10-30｜正式入口：TowerDescent3D.tscn</t>
         </is>
       </c>
       <c r="B2" s="203" t="n"/>
@@ -4102,7 +4119,7 @@
       </c>
       <c r="G22" s="177" t="inlineStr">
         <is>
-          <t>bullet_count=1；damage=25；fire_rate=3.5；magazine_size=10；reload_time=1.5；spread=0.03；range=15；bullet_speed=25/23（≈1.087，弹速 25 m/s）</t>
+          <t>bullet_count=1；damage=25；fire_rate=3.5；magazine_size=10；reload_time=1.5；spread=0.03；range=15；bullet_speed=0.7525（=25×0.6923÷23，弹速 17.31 m/s）</t>
         </is>
       </c>
       <c r="H22" s="177" t="inlineStr">
@@ -4138,7 +4155,7 @@
       </c>
       <c r="N22" s="177" t="inlineStr">
         <is>
-          <t>装配ID=bp_pistol；成品物品ID=weapon_pistol；蓝图物品ID=bp_pistol；2026-10-30 弹匣 12→10、弹速 23→25 m/s，对标《挺进地牢》陆战队员 Marine Sidearm（Magazine 10 / Shot Speed 25）；伤害/射速/换弹/扩散/射程未动</t>
+          <t>装配ID=bp_pistol；成品物品ID=weapon_pistol；蓝图物品ID=bp_pistol；**【2026-10-30 起是出厂枪（新档/死亡返城白送）】**，剧本 nar_tower_opening_01_wake 的地面枪同步改为 weapon_pistol。2026-10-30 两轮改动：①上午 弹匣 12→10、弹速 23→25 m/s（对标 Marine Sidearm Magazine 10 / Shot Speed 25）；②晚上 弹速改 17.31 m/s —— 原作「单位」不是米（原作玩家 6.5 单位/秒 vs 本作 4.5 m/s ⇒ ×0.6923），直接抄 25 会快 44%；同时弹体视觉 ×2（命中判定不变）。伤害 25 / 射速 3.5 / 换弹 1.5 / 扩散 0.03 / 射程 15 未动。命运槽沿用默认 8（未随前任出厂枪砍到 4，理由见 04 §6.1）。</t>
         </is>
       </c>
       <c r="O22" s="46" t="n">
@@ -4929,7 +4946,7 @@
       </c>
       <c r="N29" s="177" t="inlineStr">
         <is>
-          <t>装配ID=bp_starter_rifle；成品物品ID=weapon_starter_rifle；蓝图物品ID=bp_starter_rifle</t>
+          <t>装配ID=bp_starter_rifle；成品物品ID=weapon_starter_rifle；**2026-10-30 起不再是出厂枪**（出厂枪换回豌豆手枪 bp_pistol）；本枪仍是正式内容（tier0、掉落表保留），数值 50 伤 / 30 发 / 20 m 不变，回归哨兵见 verify_starting_weapon_contract._check_retired_factory_guns()。</t>
         </is>
       </c>
       <c r="O29" s="46" t="n">
@@ -17759,7 +17776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" style="135" min="1" max="1"/>
@@ -18805,6 +18822,2158 @@
         <is>
           <t>17 Blender剪辑；首次activate6.4s（非伤害技能），四技能/十二态；伤害8%韧性击晕4.8s；通电暴击可打断；独立资产ENM-BOSS-MONITOR002-3D；首次10米触发，出场播完后战斗；显示器Boss由正式触发盒生成于房间中心（局部X/Z=0），初始面向南方（世界+Z）。移动速度由1.204提高至3.612米/秒（3倍；内容speed=123.84）。10米激活及6.4秒出场规则保持。
 【远征01·monster_rules 覆盖 2026-10-14】本关以关卡级 `monster_rules.stats.per_kind` 覆盖生命为 **32000**（覆盖排在身份基线 merge 之后，否则被 hp=200 盖掉）；速度 3.612 m/s 未动。PROFILES / BossContentCatalog 基线未改。见 远征关卡01设计.md §4.5.3。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="64" customHeight="1" s="135">
+      <c r="A18" s="215" t="inlineStr">
+        <is>
+          <t>monster_egt_bullet_kin</t>
+        </is>
+      </c>
+      <c r="B18" s="215" t="inlineStr">
+        <is>
+          <t>子弹小子</t>
+        </is>
+      </c>
+      <c r="C18" s="215" t="inlineStr">
+        <is>
+          <t>egt_bullet_kin</t>
+        </is>
+      </c>
+      <c r="D18" s="215" t="n">
+        <v>150</v>
+      </c>
+      <c r="E18" s="215" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" s="215" t="n">
+        <v>17</v>
+      </c>
+      <c r="G18" s="215" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H18" s="215" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I18" s="215" t="inlineStr">
+        <is>
+          <t>1 发</t>
+        </is>
+      </c>
+      <c r="J18" s="215" t="inlineStr">
+        <is>
+          <t>n01、n02、hub_01、n08、兜底·NORMAL、兜底·HUB</t>
+        </is>
+      </c>
+      <c r="K18" s="215" t="inlineStr">
+        <is>
+          <t>铸币 1~2 枚</t>
+        </is>
+      </c>
+      <c r="L18" s="215" t="inlineStr">
+        <is>
+          <t>[已实装]</t>
+        </is>
+      </c>
+      <c r="M18" s="215" t="inlineStr">
+        <is>
+          <t>占位美术（借 保安僵尸）</t>
+        </is>
+      </c>
+      <c r="N18" s="215" t="inlineStr">
+        <is>
+          <t>src/enemy3d/Enemy3D.gd → PROFILES</t>
+        </is>
+      </c>
+      <c r="O18" s="215" t="inlineStr">
+        <is>
+          <t>原作 Bullet Kin（血 15×10）；冷却带 ±20% 抖动；受房间节拍器 470ms 约束；开火需视线</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="64" customHeight="1" s="135">
+      <c r="A19" s="215" t="inlineStr">
+        <is>
+          <t>monster_egt_bandana_kin</t>
+        </is>
+      </c>
+      <c r="B19" s="215" t="inlineStr">
+        <is>
+          <t>头巾小子</t>
+        </is>
+      </c>
+      <c r="C19" s="215" t="inlineStr">
+        <is>
+          <t>egt_bandana_kin</t>
+        </is>
+      </c>
+      <c r="D19" s="215" t="n">
+        <v>150</v>
+      </c>
+      <c r="E19" s="215" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" s="215" t="n">
+        <v>17</v>
+      </c>
+      <c r="G19" s="215" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H19" s="215" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="I19" s="215" t="inlineStr">
+        <is>
+          <t>3 发 间隔 0.12s</t>
+        </is>
+      </c>
+      <c r="J19" s="215" t="inlineStr">
+        <is>
+          <t>n02、hub_01、hub_02、n07、n08、兜底·HUB</t>
+        </is>
+      </c>
+      <c r="K19" s="215" t="inlineStr">
+        <is>
+          <t>铸币 1~2 枚</t>
+        </is>
+      </c>
+      <c r="L19" s="215" t="inlineStr">
+        <is>
+          <t>[已实装]</t>
+        </is>
+      </c>
+      <c r="M19" s="215" t="inlineStr">
+        <is>
+          <t>占位美术（借 保安僵尸）</t>
+        </is>
+      </c>
+      <c r="N19" s="215" t="inlineStr">
+        <is>
+          <t>src/enemy3d/Enemy3D.gd → PROFILES</t>
+        </is>
+      </c>
+      <c r="O19" s="215" t="inlineStr">
+        <is>
+          <t>原作 Bandana Bullet Kin（血 15×10）；冷却带 ±20% 抖动；受房间节拍器 470ms 约束；开火需视线</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="64" customHeight="1" s="135">
+      <c r="A20" s="215" t="inlineStr">
+        <is>
+          <t>monster_egt_veteran_kin</t>
+        </is>
+      </c>
+      <c r="B20" s="215" t="inlineStr">
+        <is>
+          <t>老兵小子</t>
+        </is>
+      </c>
+      <c r="C20" s="215" t="inlineStr">
+        <is>
+          <t>egt_veteran_kin</t>
+        </is>
+      </c>
+      <c r="D20" s="215" t="n">
+        <v>150</v>
+      </c>
+      <c r="E20" s="215" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F20" s="215" t="n">
+        <v>17</v>
+      </c>
+      <c r="G20" s="215" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="H20" s="215" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I20" s="215" t="inlineStr">
+        <is>
+          <t>4 发 ±1.5° 间隔 0.12s 预判 62%</t>
+        </is>
+      </c>
+      <c r="J20" s="215" t="inlineStr">
+        <is>
+          <t>n02、hub_01、n03、n06、n08、兜底·HUB</t>
+        </is>
+      </c>
+      <c r="K20" s="215" t="inlineStr">
+        <is>
+          <t>铸币 1~2 枚</t>
+        </is>
+      </c>
+      <c r="L20" s="215" t="inlineStr">
+        <is>
+          <t>[已实装]</t>
+        </is>
+      </c>
+      <c r="M20" s="215" t="inlineStr">
+        <is>
+          <t>占位美术（借 保安僵尸）</t>
+        </is>
+      </c>
+      <c r="N20" s="215" t="inlineStr">
+        <is>
+          <t>src/enemy3d/Enemy3D.gd → PROFILES</t>
+        </is>
+      </c>
+      <c r="O20" s="215" t="inlineStr">
+        <is>
+          <t>原作 Veteran Bullet Kin（血 15×10）；冷却带 ±20% 抖动；受房间节拍器 470ms 约束；开火需视线</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="64" customHeight="1" s="135">
+      <c r="A21" s="215" t="inlineStr">
+        <is>
+          <t>monster_egt_cardinal</t>
+        </is>
+      </c>
+      <c r="B21" s="215" t="inlineStr">
+        <is>
+          <t>红衣主教</t>
+        </is>
+      </c>
+      <c r="C21" s="215" t="inlineStr">
+        <is>
+          <t>egt_cardinal</t>
+        </is>
+      </c>
+      <c r="D21" s="215" t="n">
+        <v>225</v>
+      </c>
+      <c r="E21" s="215" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" s="215" t="n">
+        <v>17</v>
+      </c>
+      <c r="G21" s="215" t="n">
+        <v>9</v>
+      </c>
+      <c r="H21" s="215" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I21" s="215" t="inlineStr">
+        <is>
+          <t>1 发；每 3 次换招</t>
+        </is>
+      </c>
+      <c r="J21" s="215" t="inlineStr">
+        <is>
+          <t>hub_01</t>
+        </is>
+      </c>
+      <c r="K21" s="215" t="inlineStr">
+        <is>
+          <t>铸币 1~2 枚</t>
+        </is>
+      </c>
+      <c r="L21" s="215" t="inlineStr">
+        <is>
+          <t>[已实装]</t>
+        </is>
+      </c>
+      <c r="M21" s="215" t="inlineStr">
+        <is>
+          <t>占位美术（借 保安僵尸）</t>
+        </is>
+      </c>
+      <c r="N21" s="215" t="inlineStr">
+        <is>
+          <t>src/enemy3d/Enemy3D.gd → PROFILES</t>
+        </is>
+      </c>
+      <c r="O21" s="215" t="inlineStr">
+        <is>
+          <t>原作 Cardinal（血 22.5×10）；冷却带 ±20% 抖动；受房间节拍器 470ms 约束；开火需视线</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="64" customHeight="1" s="135">
+      <c r="A22" s="215" t="inlineStr">
+        <is>
+          <t>monster_egt_hollowpoint</t>
+        </is>
+      </c>
+      <c r="B22" s="215" t="inlineStr">
+        <is>
+          <t>空尖弹</t>
+        </is>
+      </c>
+      <c r="C22" s="215" t="inlineStr">
+        <is>
+          <t>egt_hollowpoint</t>
+        </is>
+      </c>
+      <c r="D22" s="215" t="n">
+        <v>250</v>
+      </c>
+      <c r="E22" s="215" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F22" s="215" t="n">
+        <v>17</v>
+      </c>
+      <c r="G22" s="215" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="H22" s="215" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="I22" s="215" t="inlineStr">
+        <is>
+          <t>4 发 ±3° 间隔 0.09s 预判 20%；每 5.0s 瞬移</t>
+        </is>
+      </c>
+      <c r="J22" s="215" t="inlineStr">
+        <is>
+          <t>n02</t>
+        </is>
+      </c>
+      <c r="K22" s="215" t="inlineStr">
+        <is>
+          <t>铸币 1~2 枚</t>
+        </is>
+      </c>
+      <c r="L22" s="215" t="inlineStr">
+        <is>
+          <t>[已实装]</t>
+        </is>
+      </c>
+      <c r="M22" s="215" t="inlineStr">
+        <is>
+          <t>占位美术（借 保安僵尸）</t>
+        </is>
+      </c>
+      <c r="N22" s="215" t="inlineStr">
+        <is>
+          <t>src/enemy3d/Enemy3D.gd → PROFILES</t>
+        </is>
+      </c>
+      <c r="O22" s="215" t="inlineStr">
+        <is>
+          <t>原作 Hollowpoint（血 25×10）；冷却带 ±20% 抖动；受房间节拍器 470ms 约束；开火需视线</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="64" customHeight="1" s="135">
+      <c r="A23" s="215" t="inlineStr">
+        <is>
+          <t>monster_egt_red_shotgun</t>
+        </is>
+      </c>
+      <c r="B23" s="215" t="inlineStr">
+        <is>
+          <t>红霰弹枪小子</t>
+        </is>
+      </c>
+      <c r="C23" s="215" t="inlineStr">
+        <is>
+          <t>egt_red_shotgun</t>
+        </is>
+      </c>
+      <c r="D23" s="215" t="n">
+        <v>300</v>
+      </c>
+      <c r="E23" s="215" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" s="215" t="n">
+        <v>17</v>
+      </c>
+      <c r="G23" s="215" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H23" s="215" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I23" s="215" t="inlineStr">
+        <is>
+          <t>5 发 ±14°；死亡35%喷 6 发</t>
+        </is>
+      </c>
+      <c r="J23" s="215" t="inlineStr">
+        <is>
+          <t>hub_01、n03、hub_02、n07、兜底·HUB</t>
+        </is>
+      </c>
+      <c r="K23" s="215" t="inlineStr">
+        <is>
+          <t>铸币 1~2 枚</t>
+        </is>
+      </c>
+      <c r="L23" s="215" t="inlineStr">
+        <is>
+          <t>[已实装]</t>
+        </is>
+      </c>
+      <c r="M23" s="215" t="inlineStr">
+        <is>
+          <t>占位美术（借 保安僵尸）</t>
+        </is>
+      </c>
+      <c r="N23" s="215" t="inlineStr">
+        <is>
+          <t>src/enemy3d/Enemy3D.gd → PROFILES</t>
+        </is>
+      </c>
+      <c r="O23" s="215" t="inlineStr">
+        <is>
+          <t>原作 Red Shotgun Kin（血 30×10）；冷却带 ±20% 抖动；受房间节拍器 470ms 约束；开火需视线</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="64" customHeight="1" s="135">
+      <c r="A24" s="215" t="inlineStr">
+        <is>
+          <t>monster_egt_blue_shotgun</t>
+        </is>
+      </c>
+      <c r="B24" s="215" t="inlineStr">
+        <is>
+          <t>蓝霰弹枪小子</t>
+        </is>
+      </c>
+      <c r="C24" s="215" t="inlineStr">
+        <is>
+          <t>egt_blue_shotgun</t>
+        </is>
+      </c>
+      <c r="D24" s="215" t="n">
+        <v>400</v>
+      </c>
+      <c r="E24" s="215" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" s="215" t="n">
+        <v>17</v>
+      </c>
+      <c r="G24" s="215" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H24" s="215" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I24" s="215" t="inlineStr">
+        <is>
+          <t>5 发 ±26° 间隔 0.16s；死亡35%喷 6 发</t>
+        </is>
+      </c>
+      <c r="J24" s="215" t="inlineStr">
+        <is>
+          <t>hub_02、n07</t>
+        </is>
+      </c>
+      <c r="K24" s="215" t="inlineStr">
+        <is>
+          <t>铸币 1~2 枚</t>
+        </is>
+      </c>
+      <c r="L24" s="215" t="inlineStr">
+        <is>
+          <t>[已实装]</t>
+        </is>
+      </c>
+      <c r="M24" s="215" t="inlineStr">
+        <is>
+          <t>占位美术（借 保安僵尸）</t>
+        </is>
+      </c>
+      <c r="N24" s="215" t="inlineStr">
+        <is>
+          <t>src/enemy3d/Enemy3D.gd → PROFILES</t>
+        </is>
+      </c>
+      <c r="O24" s="215" t="inlineStr">
+        <is>
+          <t>原作 Blue Shotgun Kin（血 40×10）；冷却带 ±20% 抖动；受房间节拍器 470ms 约束；开火需视线</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="64" customHeight="1" s="135">
+      <c r="A25" s="215" t="inlineStr">
+        <is>
+          <t>monster_egt_veteran_shotgun</t>
+        </is>
+      </c>
+      <c r="B25" s="215" t="inlineStr">
+        <is>
+          <t>老兵霰弹枪小子</t>
+        </is>
+      </c>
+      <c r="C25" s="215" t="inlineStr">
+        <is>
+          <t>egt_veteran_shotgun</t>
+        </is>
+      </c>
+      <c r="D25" s="215" t="n">
+        <v>338</v>
+      </c>
+      <c r="E25" s="215" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" s="215" t="n">
+        <v>17</v>
+      </c>
+      <c r="G25" s="215" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H25" s="215" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I25" s="215" t="inlineStr">
+        <is>
+          <t>v 5 发 ±22° 预判 100%；死亡必喷 12 发</t>
+        </is>
+      </c>
+      <c r="J25" s="215" t="inlineStr">
+        <is>
+          <t>n03</t>
+        </is>
+      </c>
+      <c r="K25" s="215" t="inlineStr">
+        <is>
+          <t>铸币 1~2 枚</t>
+        </is>
+      </c>
+      <c r="L25" s="215" t="inlineStr">
+        <is>
+          <t>[已实装]</t>
+        </is>
+      </c>
+      <c r="M25" s="215" t="inlineStr">
+        <is>
+          <t>占位美术（借 保安僵尸）</t>
+        </is>
+      </c>
+      <c r="N25" s="215" t="inlineStr">
+        <is>
+          <t>src/enemy3d/Enemy3D.gd → PROFILES</t>
+        </is>
+      </c>
+      <c r="O25" s="215" t="inlineStr">
+        <is>
+          <t>原作 Veteran Shotgun Kin（血 33.8×10）；冷却带 ±20% 抖动；受房间节拍器 470ms 约束；开火需视线</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="64" customHeight="1" s="135">
+      <c r="A26" s="215" t="inlineStr">
+        <is>
+          <t>monster_egt_pinhead</t>
+        </is>
+      </c>
+      <c r="B26" s="215" t="inlineStr">
+        <is>
+          <t>保险销头</t>
+        </is>
+      </c>
+      <c r="C26" s="215" t="inlineStr">
+        <is>
+          <t>egt_pinhead</t>
+        </is>
+      </c>
+      <c r="D26" s="215" t="n">
+        <v>130</v>
+      </c>
+      <c r="E26" s="215" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F26" s="215" t="n">
+        <v>17</v>
+      </c>
+      <c r="G26" s="215" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="H26" s="215" t="n">
+        <v>3</v>
+      </c>
+      <c r="I26" s="215" t="inlineStr">
+        <is>
+          <t>接触自爆；玩家靠近时主动扑击再爆</t>
+        </is>
+      </c>
+      <c r="J26" s="215" t="inlineStr">
+        <is>
+          <t>n04、n05</t>
+        </is>
+      </c>
+      <c r="K26" s="215" t="inlineStr">
+        <is>
+          <t>0（原作自爆怪不掉铸币）</t>
+        </is>
+      </c>
+      <c r="L26" s="215" t="inlineStr">
+        <is>
+          <t>[已实装]</t>
+        </is>
+      </c>
+      <c r="M26" s="215" t="inlineStr">
+        <is>
+          <t>占位美术（借 炸弹果）</t>
+        </is>
+      </c>
+      <c r="N26" s="215" t="inlineStr">
+        <is>
+          <t>src/enemy3d/Enemy3D.gd → PROFILES</t>
+        </is>
+      </c>
+      <c r="O26" s="215" t="inlineStr">
+        <is>
+          <t>原作 Pinhead（血 13×10）；冷却带 ±20% 抖动；受房间节拍器 470ms 约束；开火需视线</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="64" customHeight="1" s="135">
+      <c r="A27" s="215" t="inlineStr">
+        <is>
+          <t>monster_egt_nitra</t>
+        </is>
+      </c>
+      <c r="B27" s="215" t="inlineStr">
+        <is>
+          <t>硝酸怪</t>
+        </is>
+      </c>
+      <c r="C27" s="215" t="inlineStr">
+        <is>
+          <t>egt_nitra</t>
+        </is>
+      </c>
+      <c r="D27" s="215" t="n">
+        <v>100</v>
+      </c>
+      <c r="E27" s="215" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F27" s="215" t="n">
+        <v>17</v>
+      </c>
+      <c r="G27" s="215" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H27" s="215" t="n">
+        <v>3</v>
+      </c>
+      <c r="I27" s="215" t="inlineStr">
+        <is>
+          <t>死亡炸成一条线，线朝远离玩家方向延伸；玩家太近则提前自爆且爆线转向玩家</t>
+        </is>
+      </c>
+      <c r="J27" s="215" t="inlineStr">
+        <is>
+          <t>n04、n05</t>
+        </is>
+      </c>
+      <c r="K27" s="215" t="inlineStr">
+        <is>
+          <t>0（原作自爆怪不掉铸币）</t>
+        </is>
+      </c>
+      <c r="L27" s="215" t="inlineStr">
+        <is>
+          <t>[已实装]</t>
+        </is>
+      </c>
+      <c r="M27" s="215" t="inlineStr">
+        <is>
+          <t>占位美术（借 炸弹果）</t>
+        </is>
+      </c>
+      <c r="N27" s="215" t="inlineStr">
+        <is>
+          <t>src/enemy3d/Enemy3D.gd → PROFILES</t>
+        </is>
+      </c>
+      <c r="O27" s="215" t="inlineStr">
+        <is>
+          <t>原作 Nitra（血 10×10）；冷却带 ±20% 抖动；受房间节拍器 470ms 约束；开火需视线</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="64" customHeight="1" s="135">
+      <c r="A28" s="215" t="inlineStr">
+        <is>
+          <t>monster_egt_king_bullat</t>
+        </is>
+      </c>
+      <c r="B28" s="215" t="inlineStr">
+        <is>
+          <t>子弹榴弹王</t>
+        </is>
+      </c>
+      <c r="C28" s="215" t="inlineStr">
+        <is>
+          <t>egt_king_bullat</t>
+        </is>
+      </c>
+      <c r="D28" s="215" t="n">
+        <v>260</v>
+      </c>
+      <c r="E28" s="215" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F28" s="215" t="n">
+        <v>17</v>
+      </c>
+      <c r="G28" s="215" t="n">
+        <v>9</v>
+      </c>
+      <c r="H28" s="215" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I28" s="215" t="inlineStr">
+        <is>
+          <t>ring 8 发 间隔 0.05s；死后产 2×bullat+2×shotgat；原地不动</t>
+        </is>
+      </c>
+      <c r="J28" s="215" t="inlineStr">
+        <is>
+          <t>hub_02</t>
+        </is>
+      </c>
+      <c r="K28" s="215" t="inlineStr">
+        <is>
+          <t>铸币 1~2 枚</t>
+        </is>
+      </c>
+      <c r="L28" s="215" t="inlineStr">
+        <is>
+          <t>[已实装]</t>
+        </is>
+      </c>
+      <c r="M28" s="215" t="inlineStr">
+        <is>
+          <t>占位美术（借 炸弹果）</t>
+        </is>
+      </c>
+      <c r="N28" s="215" t="inlineStr">
+        <is>
+          <t>src/enemy3d/Enemy3D.gd → PROFILES</t>
+        </is>
+      </c>
+      <c r="O28" s="215" t="inlineStr">
+        <is>
+          <t>原作 King Bullat（血 26×10）；冷却带 ±20% 抖动；受房间节拍器 470ms 约束；开火需视线</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="64" customHeight="1" s="135">
+      <c r="A29" s="215" t="inlineStr">
+        <is>
+          <t>monster_egt_blobulon</t>
+        </is>
+      </c>
+      <c r="B29" s="215" t="inlineStr">
+        <is>
+          <t>布洛布</t>
+        </is>
+      </c>
+      <c r="C29" s="215" t="inlineStr">
+        <is>
+          <t>egt_blobulon</t>
+        </is>
+      </c>
+      <c r="D29" s="215" t="n">
+        <v>200</v>
+      </c>
+      <c r="E29" s="215" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F29" s="215" t="n">
+        <v>17</v>
+      </c>
+      <c r="G29" s="215" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="H29" s="215" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I29" s="215" t="inlineStr">
+        <is>
+          <t>死后裂 2×blobuloid</t>
+        </is>
+      </c>
+      <c r="J29" s="215" t="inlineStr">
+        <is>
+          <t>n01、n04、兜底·NORMAL</t>
+        </is>
+      </c>
+      <c r="K29" s="215" t="inlineStr">
+        <is>
+          <t>铸币 1~2 枚</t>
+        </is>
+      </c>
+      <c r="L29" s="215" t="inlineStr">
+        <is>
+          <t>[已实装]</t>
+        </is>
+      </c>
+      <c r="M29" s="215" t="inlineStr">
+        <is>
+          <t>占位美术（借 小僵尸）</t>
+        </is>
+      </c>
+      <c r="N29" s="215" t="inlineStr">
+        <is>
+          <t>src/enemy3d/Enemy3D.gd → PROFILES</t>
+        </is>
+      </c>
+      <c r="O29" s="215" t="inlineStr">
+        <is>
+          <t>原作 Blobulon（血 20×10）；冷却带 ±20% 抖动；受房间节拍器 470ms 约束；开火需视线</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="64" customHeight="1" s="135">
+      <c r="A30" s="215" t="inlineStr">
+        <is>
+          <t>monster_egt_blobuloid</t>
+        </is>
+      </c>
+      <c r="B30" s="215" t="inlineStr">
+        <is>
+          <t>布洛布幼体</t>
+        </is>
+      </c>
+      <c r="C30" s="215" t="inlineStr">
+        <is>
+          <t>egt_blobuloid</t>
+        </is>
+      </c>
+      <c r="D30" s="215" t="n">
+        <v>100</v>
+      </c>
+      <c r="E30" s="215" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F30" s="215" t="n">
+        <v>17</v>
+      </c>
+      <c r="G30" s="215" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H30" s="215" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I30" s="215" t="inlineStr">
+        <is>
+          <t>死后裂 2×blobulin</t>
+        </is>
+      </c>
+      <c r="J30" s="215" t="inlineStr">
+        <is>
+          <t>n01、兜底·NORMAL</t>
+        </is>
+      </c>
+      <c r="K30" s="215" t="inlineStr">
+        <is>
+          <t>铸币 1~2 枚</t>
+        </is>
+      </c>
+      <c r="L30" s="215" t="inlineStr">
+        <is>
+          <t>[已实装]</t>
+        </is>
+      </c>
+      <c r="M30" s="215" t="inlineStr">
+        <is>
+          <t>占位美术（借 小僵尸）</t>
+        </is>
+      </c>
+      <c r="N30" s="215" t="inlineStr">
+        <is>
+          <t>src/enemy3d/Enemy3D.gd → PROFILES</t>
+        </is>
+      </c>
+      <c r="O30" s="215" t="inlineStr">
+        <is>
+          <t>原作 Blobuloid（血 10×10）；冷却带 ±20% 抖动；受房间节拍器 470ms 约束；开火需视线</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="64" customHeight="1" s="135">
+      <c r="A31" s="215" t="inlineStr">
+        <is>
+          <t>monster_egt_blobulin</t>
+        </is>
+      </c>
+      <c r="B31" s="215" t="inlineStr">
+        <is>
+          <t>布洛布微体</t>
+        </is>
+      </c>
+      <c r="C31" s="215" t="inlineStr">
+        <is>
+          <t>egt_blobulin</t>
+        </is>
+      </c>
+      <c r="D31" s="215" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" s="215" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F31" s="215" t="n">
+        <v>17</v>
+      </c>
+      <c r="G31" s="215" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H31" s="215" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I31" s="215" t="inlineStr">
+        <is>
+          <t>纯接触伤害；快速移向玩家；不再裂</t>
+        </is>
+      </c>
+      <c r="J31" s="215" t="inlineStr">
+        <is>
+          <t>分裂产物（blobuloid 死后）</t>
+        </is>
+      </c>
+      <c r="K31" s="215" t="inlineStr">
+        <is>
+          <t>铸币 1~2 枚</t>
+        </is>
+      </c>
+      <c r="L31" s="215" t="inlineStr">
+        <is>
+          <t>[已实装]</t>
+        </is>
+      </c>
+      <c r="M31" s="215" t="inlineStr">
+        <is>
+          <t>占位美术（借 小僵尸）</t>
+        </is>
+      </c>
+      <c r="N31" s="215" t="inlineStr">
+        <is>
+          <t>src/enemy3d/Enemy3D.gd → PROFILES</t>
+        </is>
+      </c>
+      <c r="O31" s="215" t="inlineStr">
+        <is>
+          <t>原作 Blobulin（血 1×10）；冷却带 ±20% 抖动；受房间节拍器 470ms 约束；开火需视线</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="64" customHeight="1" s="135">
+      <c r="A32" s="215" t="inlineStr">
+        <is>
+          <t>monster_egt_chancebulon</t>
+        </is>
+      </c>
+      <c r="B32" s="215" t="inlineStr">
+        <is>
+          <t>骰子布洛布</t>
+        </is>
+      </c>
+      <c r="C32" s="215" t="inlineStr">
+        <is>
+          <t>egt_chancebulon</t>
+        </is>
+      </c>
+      <c r="D32" s="215" t="n">
+        <v>500</v>
+      </c>
+      <c r="E32" s="215" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F32" s="215" t="n">
+        <v>17</v>
+      </c>
+      <c r="G32" s="215" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H32" s="215" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I32" s="215" t="inlineStr">
+        <is>
+          <t>20% 不攻击直接死</t>
+        </is>
+      </c>
+      <c r="J32" s="215" t="inlineStr">
+        <is>
+          <t>n04</t>
+        </is>
+      </c>
+      <c r="K32" s="215" t="inlineStr">
+        <is>
+          <t>铸币 1~2 枚</t>
+        </is>
+      </c>
+      <c r="L32" s="215" t="inlineStr">
+        <is>
+          <t>[已实装]</t>
+        </is>
+      </c>
+      <c r="M32" s="215" t="inlineStr">
+        <is>
+          <t>占位美术（借 小僵尸）</t>
+        </is>
+      </c>
+      <c r="N32" s="215" t="inlineStr">
+        <is>
+          <t>src/enemy3d/Enemy3D.gd → PROFILES</t>
+        </is>
+      </c>
+      <c r="O32" s="215" t="inlineStr">
+        <is>
+          <t>原作 Chancebulon（血 50×10）；冷却带 ±20% 抖动；受房间节拍器 470ms 约束；开火需视线</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="64" customHeight="1" s="135">
+      <c r="A33" s="215" t="inlineStr">
+        <is>
+          <t>monster_egt_bookllet</t>
+        </is>
+      </c>
+      <c r="B33" s="215" t="inlineStr">
+        <is>
+          <t>书怪</t>
+        </is>
+      </c>
+      <c r="C33" s="215" t="inlineStr">
+        <is>
+          <t>egt_bookllet</t>
+        </is>
+      </c>
+      <c r="D33" s="215" t="n">
+        <v>250</v>
+      </c>
+      <c r="E33" s="215" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F33" s="215" t="n">
+        <v>17</v>
+      </c>
+      <c r="G33" s="215" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H33" s="215" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I33" s="215" t="inlineStr">
+        <is>
+          <t>letter 10 发 间隔 0.06s</t>
+        </is>
+      </c>
+      <c r="J33" s="215" t="inlineStr">
+        <is>
+          <t>n08</t>
+        </is>
+      </c>
+      <c r="K33" s="215" t="inlineStr">
+        <is>
+          <t>铸币 1~2 枚</t>
+        </is>
+      </c>
+      <c r="L33" s="215" t="inlineStr">
+        <is>
+          <t>[已实装]</t>
+        </is>
+      </c>
+      <c r="M33" s="215" t="inlineStr">
+        <is>
+          <t>占位美术（借 蜂巢怪）</t>
+        </is>
+      </c>
+      <c r="N33" s="215" t="inlineStr">
+        <is>
+          <t>src/enemy3d/Enemy3D.gd → PROFILES</t>
+        </is>
+      </c>
+      <c r="O33" s="215" t="inlineStr">
+        <is>
+          <t>原作 Bookllet（三色同）（血 25×10）；冷却带 ±20% 抖动；受房间节拍器 470ms 约束；开火需视线</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="64" customHeight="1" s="135">
+      <c r="A34" s="215" t="inlineStr">
+        <is>
+          <t>monster_egt_blue_bookllet</t>
+        </is>
+      </c>
+      <c r="B34" s="215" t="inlineStr">
+        <is>
+          <t>蓝书怪</t>
+        </is>
+      </c>
+      <c r="C34" s="215" t="inlineStr">
+        <is>
+          <t>egt_blue_bookllet</t>
+        </is>
+      </c>
+      <c r="D34" s="215" t="n">
+        <v>250</v>
+      </c>
+      <c r="E34" s="215" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F34" s="215" t="n">
+        <v>17</v>
+      </c>
+      <c r="G34" s="215" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H34" s="215" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I34" s="215" t="inlineStr">
+        <is>
+          <t>ring 8 发 间隔 0.12s；每 3 次换招</t>
+        </is>
+      </c>
+      <c r="J34" s="215" t="inlineStr">
+        <is>
+          <t>n08</t>
+        </is>
+      </c>
+      <c r="K34" s="215" t="inlineStr">
+        <is>
+          <t>铸币 1~2 枚</t>
+        </is>
+      </c>
+      <c r="L34" s="215" t="inlineStr">
+        <is>
+          <t>[已实装]</t>
+        </is>
+      </c>
+      <c r="M34" s="215" t="inlineStr">
+        <is>
+          <t>占位美术（借 蜂巢怪）</t>
+        </is>
+      </c>
+      <c r="N34" s="215" t="inlineStr">
+        <is>
+          <t>src/enemy3d/Enemy3D.gd → PROFILES</t>
+        </is>
+      </c>
+      <c r="O34" s="215" t="inlineStr">
+        <is>
+          <t>原作 Bookllet（三色同）（血 25×10）；冷却带 ±20% 抖动；受房间节拍器 470ms 约束；开火需视线</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="64" customHeight="1" s="135">
+      <c r="A35" s="215" t="inlineStr">
+        <is>
+          <t>monster_egt_green_bookllet</t>
+        </is>
+      </c>
+      <c r="B35" s="215" t="inlineStr">
+        <is>
+          <t>绿书怪</t>
+        </is>
+      </c>
+      <c r="C35" s="215" t="inlineStr">
+        <is>
+          <t>egt_green_bookllet</t>
+        </is>
+      </c>
+      <c r="D35" s="215" t="n">
+        <v>250</v>
+      </c>
+      <c r="E35" s="215" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F35" s="215" t="n">
+        <v>17</v>
+      </c>
+      <c r="G35" s="215" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H35" s="215" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I35" s="215" t="inlineStr">
+        <is>
+          <t>clover 4 发 ±12° 间隔 0.07s</t>
+        </is>
+      </c>
+      <c r="J35" s="215" t="inlineStr">
+        <is>
+          <t>n08</t>
+        </is>
+      </c>
+      <c r="K35" s="215" t="inlineStr">
+        <is>
+          <t>铸币 1~2 枚</t>
+        </is>
+      </c>
+      <c r="L35" s="215" t="inlineStr">
+        <is>
+          <t>[已实装]</t>
+        </is>
+      </c>
+      <c r="M35" s="215" t="inlineStr">
+        <is>
+          <t>占位美术（借 蜂巢怪）</t>
+        </is>
+      </c>
+      <c r="N35" s="215" t="inlineStr">
+        <is>
+          <t>src/enemy3d/Enemy3D.gd → PROFILES</t>
+        </is>
+      </c>
+      <c r="O35" s="215" t="inlineStr">
+        <is>
+          <t>原作 Bookllet（三色同）（血 25×10）；冷却带 ±20% 抖动；受房间节拍器 470ms 约束；开火需视线</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="64" customHeight="1" s="135">
+      <c r="A36" s="215" t="inlineStr">
+        <is>
+          <t>monster_egt_gunjurer</t>
+        </is>
+      </c>
+      <c r="B36" s="215" t="inlineStr">
+        <is>
+          <t>学徒枪法师</t>
+        </is>
+      </c>
+      <c r="C36" s="215" t="inlineStr">
+        <is>
+          <t>egt_gunjurer</t>
+        </is>
+      </c>
+      <c r="D36" s="215" t="n">
+        <v>188</v>
+      </c>
+      <c r="E36" s="215" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F36" s="215" t="n">
+        <v>17</v>
+      </c>
+      <c r="G36" s="215" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H36" s="215" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I36" s="215" t="inlineStr">
+        <is>
+          <t>spiral 9 发 间隔 0.1s；出手后瞬移</t>
+        </is>
+      </c>
+      <c r="J36" s="215" t="inlineStr">
+        <is>
+          <t>n05</t>
+        </is>
+      </c>
+      <c r="K36" s="215" t="inlineStr">
+        <is>
+          <t>铸币 1~2 枚</t>
+        </is>
+      </c>
+      <c r="L36" s="215" t="inlineStr">
+        <is>
+          <t>[已实装]</t>
+        </is>
+      </c>
+      <c r="M36" s="215" t="inlineStr">
+        <is>
+          <t>占位美术（借 蜂巢怪）</t>
+        </is>
+      </c>
+      <c r="N36" s="215" t="inlineStr">
+        <is>
+          <t>src/enemy3d/Enemy3D.gd → PROFILES</t>
+        </is>
+      </c>
+      <c r="O36" s="215" t="inlineStr">
+        <is>
+          <t>原作 Apprentice Gunjurer（血 18.8×10）；冷却带 ±20% 抖动；受房间节拍器 470ms 约束；开火需视线</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="64" customHeight="1" s="135">
+      <c r="A37" s="215" t="inlineStr">
+        <is>
+          <t>monster_egt_gunsinger</t>
+        </is>
+      </c>
+      <c r="B37" s="215" t="inlineStr">
+        <is>
+          <t>枪歌者</t>
+        </is>
+      </c>
+      <c r="C37" s="215" t="inlineStr">
+        <is>
+          <t>egt_gunsinger</t>
+        </is>
+      </c>
+      <c r="D37" s="215" t="n">
+        <v>150</v>
+      </c>
+      <c r="E37" s="215" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="215" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="215" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H37" s="215" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I37" s="215" t="inlineStr">
+        <is>
+          <t>给同伴 +35%血 / 1.35×速；原地不动</t>
+        </is>
+      </c>
+      <c r="J37" s="215" t="inlineStr">
+        <is>
+          <t>hub_02、n07</t>
+        </is>
+      </c>
+      <c r="K37" s="215" t="inlineStr">
+        <is>
+          <t>铸币 1~2 枚</t>
+        </is>
+      </c>
+      <c r="L37" s="215" t="inlineStr">
+        <is>
+          <t>[已实装]</t>
+        </is>
+      </c>
+      <c r="M37" s="215" t="inlineStr">
+        <is>
+          <t>占位美术（借 蜂巢怪）</t>
+        </is>
+      </c>
+      <c r="N37" s="215" t="inlineStr">
+        <is>
+          <t>src/enemy3d/Enemy3D.gd → PROFILES</t>
+        </is>
+      </c>
+      <c r="O37" s="215" t="inlineStr">
+        <is>
+          <t>原作 Gunsinger（血 15×10）；冷却带 ±20% 抖动；受房间节拍器 470ms 约束；开火需视线</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="64" customHeight="1" s="135">
+      <c r="A38" s="215" t="inlineStr">
+        <is>
+          <t>monster_egt_gigi</t>
+        </is>
+      </c>
+      <c r="B38" s="215" t="inlineStr">
+        <is>
+          <t>吉吉</t>
+        </is>
+      </c>
+      <c r="C38" s="215" t="inlineStr">
+        <is>
+          <t>egt_gigi</t>
+        </is>
+      </c>
+      <c r="D38" s="215" t="n">
+        <v>120</v>
+      </c>
+      <c r="E38" s="215" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F38" s="215" t="n">
+        <v>17</v>
+      </c>
+      <c r="G38" s="215" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H38" s="215" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I38" s="215" t="inlineStr">
+        <is>
+          <t>1 发 预判 25%；蛋炸 8 发</t>
+        </is>
+      </c>
+      <c r="J38" s="215" t="inlineStr">
+        <is>
+          <t>n05</t>
+        </is>
+      </c>
+      <c r="K38" s="215" t="inlineStr">
+        <is>
+          <t>铸币 1~2 枚</t>
+        </is>
+      </c>
+      <c r="L38" s="215" t="inlineStr">
+        <is>
+          <t>[已实装]</t>
+        </is>
+      </c>
+      <c r="M38" s="215" t="inlineStr">
+        <is>
+          <t>占位美术（借 蜂巢怪）</t>
+        </is>
+      </c>
+      <c r="N38" s="215" t="inlineStr">
+        <is>
+          <t>src/enemy3d/Enemy3D.gd → PROFILES</t>
+        </is>
+      </c>
+      <c r="O38" s="215" t="inlineStr">
+        <is>
+          <t>原作 Gigi（血 12×10）；冷却带 ±20% 抖动；受房间节拍器 470ms 约束；开火需视线</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="64" customHeight="1" s="135">
+      <c r="A39" s="215" t="inlineStr">
+        <is>
+          <t>monster_egt_bullat</t>
+        </is>
+      </c>
+      <c r="B39" s="215" t="inlineStr">
+        <is>
+          <t>子弹榴弹</t>
+        </is>
+      </c>
+      <c r="C39" s="215" t="inlineStr">
+        <is>
+          <t>egt_bullat</t>
+        </is>
+      </c>
+      <c r="D39" s="215" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" s="215" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F39" s="215" t="n">
+        <v>17</v>
+      </c>
+      <c r="G39" s="215" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H39" s="215" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I39" s="215" t="inlineStr">
+        <is>
+          <t>冲撞 11.0m/s 命中自毁</t>
+        </is>
+      </c>
+      <c r="J39" s="215" t="inlineStr">
+        <is>
+          <t>n03、n06</t>
+        </is>
+      </c>
+      <c r="K39" s="215" t="inlineStr">
+        <is>
+          <t>0（原作自爆怪不掉铸币）</t>
+        </is>
+      </c>
+      <c r="L39" s="215" t="inlineStr">
+        <is>
+          <t>[已实装]</t>
+        </is>
+      </c>
+      <c r="M39" s="215" t="inlineStr">
+        <is>
+          <t>占位美术（借 炸弹果）</t>
+        </is>
+      </c>
+      <c r="N39" s="215" t="inlineStr">
+        <is>
+          <t>src/enemy3d/Enemy3D.gd → PROFILES</t>
+        </is>
+      </c>
+      <c r="O39" s="215" t="inlineStr">
+        <is>
+          <t>原作 Bullat（血 1×10）；冷却带 ±20% 抖动；受房间节拍器 470ms 约束；开火需视线</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="64" customHeight="1" s="135">
+      <c r="A40" s="215" t="inlineStr">
+        <is>
+          <t>monster_egt_shotgat</t>
+        </is>
+      </c>
+      <c r="B40" s="215" t="inlineStr">
+        <is>
+          <t>霰弹榴弹</t>
+        </is>
+      </c>
+      <c r="C40" s="215" t="inlineStr">
+        <is>
+          <t>egt_shotgat</t>
+        </is>
+      </c>
+      <c r="D40" s="215" t="n">
+        <v>20</v>
+      </c>
+      <c r="E40" s="215" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F40" s="215" t="n">
+        <v>17</v>
+      </c>
+      <c r="G40" s="215" t="n">
+        <v>8</v>
+      </c>
+      <c r="H40" s="215" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I40" s="215" t="inlineStr">
+        <is>
+          <t>冲撞 10.5m/s 命中自毁</t>
+        </is>
+      </c>
+      <c r="J40" s="215" t="inlineStr">
+        <is>
+          <t>hub_02、n06</t>
+        </is>
+      </c>
+      <c r="K40" s="215" t="inlineStr">
+        <is>
+          <t>0（原作自爆怪不掉铸币）</t>
+        </is>
+      </c>
+      <c r="L40" s="215" t="inlineStr">
+        <is>
+          <t>[已实装]</t>
+        </is>
+      </c>
+      <c r="M40" s="215" t="inlineStr">
+        <is>
+          <t>占位美术（借 炸弹果）</t>
+        </is>
+      </c>
+      <c r="N40" s="215" t="inlineStr">
+        <is>
+          <t>src/enemy3d/Enemy3D.gd → PROFILES</t>
+        </is>
+      </c>
+      <c r="O40" s="215" t="inlineStr">
+        <is>
+          <t>原作 Shotgat（血 2×10）；冷却带 ±20% 抖动；受房间节拍器 470ms 约束；开火需视线</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="64" customHeight="1" s="135">
+      <c r="A41" s="215" t="inlineStr">
+        <is>
+          <t>monster_egt_grenat</t>
+        </is>
+      </c>
+      <c r="B41" s="215" t="inlineStr">
+        <is>
+          <t>榴弹子</t>
+        </is>
+      </c>
+      <c r="C41" s="215" t="inlineStr">
+        <is>
+          <t>egt_grenat</t>
+        </is>
+      </c>
+      <c r="D41" s="215" t="n">
+        <v>30</v>
+      </c>
+      <c r="E41" s="215" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F41" s="215" t="n">
+        <v>17</v>
+      </c>
+      <c r="G41" s="215" t="n">
+        <v>8</v>
+      </c>
+      <c r="H41" s="215" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I41" s="215" t="inlineStr">
+        <is>
+          <t>冲撞 10.0m/s 命中自毁</t>
+        </is>
+      </c>
+      <c r="J41" s="215" t="inlineStr">
+        <is>
+          <t>n06</t>
+        </is>
+      </c>
+      <c r="K41" s="215" t="inlineStr">
+        <is>
+          <t>0（原作自爆怪不掉铸币）</t>
+        </is>
+      </c>
+      <c r="L41" s="215" t="inlineStr">
+        <is>
+          <t>[已实装]</t>
+        </is>
+      </c>
+      <c r="M41" s="215" t="inlineStr">
+        <is>
+          <t>占位美术（借 炸弹果）</t>
+        </is>
+      </c>
+      <c r="N41" s="215" t="inlineStr">
+        <is>
+          <t>src/enemy3d/Enemy3D.gd → PROFILES</t>
+        </is>
+      </c>
+      <c r="O41" s="215" t="inlineStr">
+        <is>
+          <t>原作 Grenat（血 3×10）；冷却带 ±20% 抖动；受房间节拍器 470ms 约束；开火需视线</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="64" customHeight="1" s="135">
+      <c r="A42" s="215" t="inlineStr">
+        <is>
+          <t>monster_egt_spirat</t>
+        </is>
+      </c>
+      <c r="B42" s="215" t="inlineStr">
+        <is>
+          <t>螺旋转弹</t>
+        </is>
+      </c>
+      <c r="C42" s="215" t="inlineStr">
+        <is>
+          <t>egt_spirat</t>
+        </is>
+      </c>
+      <c r="D42" s="215" t="n">
+        <v>50</v>
+      </c>
+      <c r="E42" s="215" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F42" s="215" t="n">
+        <v>17</v>
+      </c>
+      <c r="G42" s="215" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H42" s="215" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I42" s="215" t="inlineStr">
+        <is>
+          <t>冲撞 9.5m/s 命中自毁</t>
+        </is>
+      </c>
+      <c r="J42" s="215" t="inlineStr">
+        <is>
+          <t>n06</t>
+        </is>
+      </c>
+      <c r="K42" s="215" t="inlineStr">
+        <is>
+          <t>0（原作自爆怪不掉铸币）</t>
+        </is>
+      </c>
+      <c r="L42" s="215" t="inlineStr">
+        <is>
+          <t>[已实装]</t>
+        </is>
+      </c>
+      <c r="M42" s="215" t="inlineStr">
+        <is>
+          <t>占位美术（借 炸弹果）</t>
+        </is>
+      </c>
+      <c r="N42" s="215" t="inlineStr">
+        <is>
+          <t>src/enemy3d/Enemy3D.gd → PROFILES</t>
+        </is>
+      </c>
+      <c r="O42" s="215" t="inlineStr">
+        <is>
+          <t>原作 Spirat（血 5×10）；冷却带 ±20% 抖动；受房间节拍器 470ms 约束；开火需视线</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="64" customHeight="1" s="135">
+      <c r="A43" s="215" t="inlineStr">
+        <is>
+          <t>monster_egt_keybullet_kin</t>
+        </is>
+      </c>
+      <c r="B43" s="215" t="inlineStr">
+        <is>
+          <t>钥匙小子</t>
+        </is>
+      </c>
+      <c r="C43" s="215" t="inlineStr">
+        <is>
+          <t>egt_keybullet_kin</t>
+        </is>
+      </c>
+      <c r="D43" s="215" t="n">
+        <v>150</v>
+      </c>
+      <c r="E43" s="215" t="n">
+        <v>3</v>
+      </c>
+      <c r="F43" s="215" t="n">
+        <v>17</v>
+      </c>
+      <c r="G43" s="215" t="n">
+        <v>2</v>
+      </c>
+      <c r="H43" s="215" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I43" s="215" t="inlineStr">
+        <is>
+          <t>11.0s 未击杀消失</t>
+        </is>
+      </c>
+      <c r="J43" s="215" t="inlineStr">
+        <is>
+          <t>n06</t>
+        </is>
+      </c>
+      <c r="K43" s="215" t="inlineStr">
+        <is>
+          <t>铸币 1~2 枚</t>
+        </is>
+      </c>
+      <c r="L43" s="215" t="inlineStr">
+        <is>
+          <t>[已实装]</t>
+        </is>
+      </c>
+      <c r="M43" s="215" t="inlineStr">
+        <is>
+          <t>占位美术（借 小僵尸）</t>
+        </is>
+      </c>
+      <c r="N43" s="215" t="inlineStr">
+        <is>
+          <t>src/enemy3d/Enemy3D.gd → PROFILES</t>
+        </is>
+      </c>
+      <c r="O43" s="215" t="inlineStr">
+        <is>
+          <t>原作 Keybullet Kin（血 15×10）；冷却带 ±20% 抖动；受房间节拍器 470ms 约束；开火需视线</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="64" customHeight="1" s="135">
+      <c r="A44" s="215" t="inlineStr">
+        <is>
+          <t>monster_egt_chance_kin</t>
+        </is>
+      </c>
+      <c r="B44" s="215" t="inlineStr">
+        <is>
+          <t>运气小子</t>
+        </is>
+      </c>
+      <c r="C44" s="215" t="inlineStr">
+        <is>
+          <t>egt_chance_kin</t>
+        </is>
+      </c>
+      <c r="D44" s="215" t="n">
+        <v>150</v>
+      </c>
+      <c r="E44" s="215" t="n">
+        <v>3</v>
+      </c>
+      <c r="F44" s="215" t="n">
+        <v>17</v>
+      </c>
+      <c r="G44" s="215" t="n">
+        <v>2</v>
+      </c>
+      <c r="H44" s="215" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I44" s="215" t="inlineStr">
+        <is>
+          <t>11.0s 未击杀消失</t>
+        </is>
+      </c>
+      <c r="J44" s="215" t="inlineStr">
+        <is>
+          <t>n06</t>
+        </is>
+      </c>
+      <c r="K44" s="215" t="inlineStr">
+        <is>
+          <t>铸币 1~2 枚</t>
+        </is>
+      </c>
+      <c r="L44" s="215" t="inlineStr">
+        <is>
+          <t>[已实装]</t>
+        </is>
+      </c>
+      <c r="M44" s="215" t="inlineStr">
+        <is>
+          <t>占位美术（借 小僵尸）</t>
+        </is>
+      </c>
+      <c r="N44" s="215" t="inlineStr">
+        <is>
+          <t>src/enemy3d/Enemy3D.gd → PROFILES</t>
+        </is>
+      </c>
+      <c r="O44" s="215" t="inlineStr">
+        <is>
+          <t>原作 Chance Kin（血 15×10）；冷却带 ±20% 抖动；受房间节拍器 470ms 约束；开火需视线</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="64" customHeight="1" s="135">
+      <c r="A45" s="215" t="inlineStr">
+        <is>
+          <t>monster_egt_confirmed</t>
+        </is>
+      </c>
+      <c r="B45" s="215" t="inlineStr">
+        <is>
+          <t>已确认者</t>
+        </is>
+      </c>
+      <c r="C45" s="215" t="inlineStr">
+        <is>
+          <t>egt_confirmed</t>
+        </is>
+      </c>
+      <c r="D45" s="215" t="n">
+        <v>450</v>
+      </c>
+      <c r="E45" s="215" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F45" s="215" t="n">
+        <v>17</v>
+      </c>
+      <c r="G45" s="215" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H45" s="215" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I45" s="215" t="inlineStr">
+        <is>
+          <t>serpentine 4 发 间隔 0.16s 预判 30%</t>
+        </is>
+      </c>
+      <c r="J45" s="215" t="inlineStr">
+        <is>
+          <t>n08</t>
+        </is>
+      </c>
+      <c r="K45" s="215" t="inlineStr">
+        <is>
+          <t>铸币 1~2 枚</t>
+        </is>
+      </c>
+      <c r="L45" s="215" t="inlineStr">
+        <is>
+          <t>[已实装]</t>
+        </is>
+      </c>
+      <c r="M45" s="215" t="inlineStr">
+        <is>
+          <t>占位美术（借 保安僵尸）</t>
+        </is>
+      </c>
+      <c r="N45" s="215" t="inlineStr">
+        <is>
+          <t>src/enemy3d/Enemy3D.gd → PROFILES</t>
+        </is>
+      </c>
+      <c r="O45" s="215" t="inlineStr">
+        <is>
+          <t>原作 Confirmed（血 45×10）；冷却带 ±20% 抖动；受房间节拍器 470ms 约束；开火需视线</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="64" customHeight="1" s="135">
+      <c r="A46" s="215" t="inlineStr">
+        <is>
+          <t>monster_egt_gun_fairy</t>
+        </is>
+      </c>
+      <c r="B46" s="215" t="inlineStr">
+        <is>
+          <t>枪精灵</t>
+        </is>
+      </c>
+      <c r="C46" s="215" t="inlineStr">
+        <is>
+          <t>egt_gun_fairy</t>
+        </is>
+      </c>
+      <c r="D46" s="215" t="n">
+        <v>150</v>
+      </c>
+      <c r="E46" s="215" t="n">
+        <v>3</v>
+      </c>
+      <c r="F46" s="215" t="n">
+        <v>17</v>
+      </c>
+      <c r="G46" s="215" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H46" s="215" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="I46" s="215" t="inlineStr">
+        <is>
+          <t>3 发 ±6° 间隔 0.08s</t>
+        </is>
+      </c>
+      <c r="J46" s="215" t="inlineStr">
+        <is>
+          <t>n08</t>
+        </is>
+      </c>
+      <c r="K46" s="215" t="inlineStr">
+        <is>
+          <t>铸币 1~2 枚</t>
+        </is>
+      </c>
+      <c r="L46" s="215" t="inlineStr">
+        <is>
+          <t>[已实装]</t>
+        </is>
+      </c>
+      <c r="M46" s="215" t="inlineStr">
+        <is>
+          <t>占位美术（借 保安僵尸）</t>
+        </is>
+      </c>
+      <c r="N46" s="215" t="inlineStr">
+        <is>
+          <t>src/enemy3d/Enemy3D.gd → PROFILES</t>
+        </is>
+      </c>
+      <c r="O46" s="215" t="inlineStr">
+        <is>
+          <t>原作 Gun Fairy（血 15×10）；冷却带 ±20% 抖动；受房间节拍器 470ms 约束；开火需视线</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="64" customHeight="1" s="135">
+      <c r="A47" s="215" t="inlineStr">
+        <is>
+          <t>monster_egt_gripmaster</t>
+        </is>
+      </c>
+      <c r="B47" s="215" t="inlineStr">
+        <is>
+          <t>抓握大师</t>
+        </is>
+      </c>
+      <c r="C47" s="215" t="inlineStr">
+        <is>
+          <t>egt_gripmaster</t>
+        </is>
+      </c>
+      <c r="D47" s="215" t="n">
+        <v>300</v>
+      </c>
+      <c r="E47" s="215" t="n">
+        <v>2</v>
+      </c>
+      <c r="F47" s="215" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="215" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H47" s="215" t="n">
+        <v>6</v>
+      </c>
+      <c r="I47" s="215" t="inlineStr">
+        <is>
+          <t>悬停下压抓人（不改血）</t>
+        </is>
+      </c>
+      <c r="J47" s="215" t="inlineStr">
+        <is>
+          <t>兜底·HUB</t>
+        </is>
+      </c>
+      <c r="K47" s="215" t="inlineStr">
+        <is>
+          <t>铸币 1~2 枚</t>
+        </is>
+      </c>
+      <c r="L47" s="215" t="inlineStr">
+        <is>
+          <t>[已实装]</t>
+        </is>
+      </c>
+      <c r="M47" s="215" t="inlineStr">
+        <is>
+          <t>占位美术（借 蜂巢怪）</t>
+        </is>
+      </c>
+      <c r="N47" s="215" t="inlineStr">
+        <is>
+          <t>src/enemy3d/Enemy3D.gd → PROFILES</t>
+        </is>
+      </c>
+      <c r="O47" s="215" t="inlineStr">
+        <is>
+          <t>原作 Gripmaster（血 30×10）；冷却带 ±20% 抖动；受房间节拍器 470ms 约束；开火需视线</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="64" customHeight="1" s="135">
+      <c r="A48" s="215" t="inlineStr">
+        <is>
+          <t>monster_egt_gun_nut</t>
+        </is>
+      </c>
+      <c r="B48" s="215" t="inlineStr">
+        <is>
+          <t>枪坚果</t>
+        </is>
+      </c>
+      <c r="C48" s="215" t="inlineStr">
+        <is>
+          <t>egt_gun_nut</t>
+        </is>
+      </c>
+      <c r="D48" s="215" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E48" s="215" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F48" s="215" t="n">
+        <v>17</v>
+      </c>
+      <c r="G48" s="215" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H48" s="215" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="I48" s="215" t="inlineStr">
+        <is>
+          <t>compass 7 发 ±45°；每 2 次换招</t>
+        </is>
+      </c>
+      <c r="J48" s="215" t="inlineStr">
+        <is>
+          <t>hub_01、hub_02</t>
+        </is>
+      </c>
+      <c r="K48" s="215" t="inlineStr">
+        <is>
+          <t>铸币 1~2 枚</t>
+        </is>
+      </c>
+      <c r="L48" s="215" t="inlineStr">
+        <is>
+          <t>[已实装]</t>
+        </is>
+      </c>
+      <c r="M48" s="215" t="inlineStr">
+        <is>
+          <t>占位美术（借 胖子僵尸）</t>
+        </is>
+      </c>
+      <c r="N48" s="215" t="inlineStr">
+        <is>
+          <t>src/enemy3d/Enemy3D.gd → PROFILES</t>
+        </is>
+      </c>
+      <c r="O48" s="215" t="inlineStr">
+        <is>
+          <t>原作 Gun Nut（血 100×10）；冷却带 ±20% 抖动；受房间节拍器 470ms 约束；开火需视线</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="64" customHeight="1" s="135">
+      <c r="A49" s="215" t="inlineStr">
+        <is>
+          <t>monster_egt_chain_gunner</t>
+        </is>
+      </c>
+      <c r="B49" s="215" t="inlineStr">
+        <is>
+          <t>链枪手</t>
+        </is>
+      </c>
+      <c r="C49" s="215" t="inlineStr">
+        <is>
+          <t>egt_chain_gunner</t>
+        </is>
+      </c>
+      <c r="D49" s="215" t="n">
+        <v>900</v>
+      </c>
+      <c r="E49" s="215" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F49" s="215" t="n">
+        <v>17</v>
+      </c>
+      <c r="G49" s="215" t="n">
+        <v>8</v>
+      </c>
+      <c r="H49" s="215" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I49" s="215" t="inlineStr">
+        <is>
+          <t>子弹链 3.0 圈/s×2.0s</t>
+        </is>
+      </c>
+      <c r="J49" s="215" t="inlineStr">
+        <is>
+          <t>hub_02</t>
+        </is>
+      </c>
+      <c r="K49" s="215" t="inlineStr">
+        <is>
+          <t>铸币 1~2 枚</t>
+        </is>
+      </c>
+      <c r="L49" s="215" t="inlineStr">
+        <is>
+          <t>[已实装]</t>
+        </is>
+      </c>
+      <c r="M49" s="215" t="inlineStr">
+        <is>
+          <t>占位美术（借 胖子僵尸）</t>
+        </is>
+      </c>
+      <c r="N49" s="215" t="inlineStr">
+        <is>
+          <t>src/enemy3d/Enemy3D.gd → PROFILES</t>
+        </is>
+      </c>
+      <c r="O49" s="215" t="inlineStr">
+        <is>
+          <t>原作 Chain Gunner（血 90×10）；冷却带 ±20% 抖动；受房间节拍器 470ms 约束；开火需视线</t>
         </is>
       </c>
     </row>
@@ -24061,7 +26230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="135" min="1" max="1"/>
@@ -26781,6 +28950,132 @@
       <c r="H67" t="inlineStr">
         <is>
           <t>[用户设计]</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="44" customHeight="1" s="135">
+      <c r="A68" s="215" t="inlineStr">
+        <is>
+          <t>怪物与Boss</t>
+        </is>
+      </c>
+      <c r="B68" s="215" t="inlineStr">
+        <is>
+          <t>cooldown_jitter</t>
+        </is>
+      </c>
+      <c r="C68" s="215" t="inlineStr">
+        <is>
+          <t>出手冷却的随机浮动比例（±x）。原作措辞是 occasionally / periodically，不是恒定节拍</t>
+        </is>
+      </c>
+      <c r="D68" s="215" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="E68" s="215" t="inlineStr">
+        <is>
+          <t>复刻怪必填（缺省0.20）</t>
+        </is>
+      </c>
+      <c r="F68" s="215" t="inlineStr">
+        <is>
+          <t>怪物AI</t>
+        </is>
+      </c>
+      <c r="G68" s="215" t="inlineStr">
+        <is>
+          <t>0~0.35；超出按上限截断；非复刻怪不生效</t>
+        </is>
+      </c>
+      <c r="H68" s="215" t="inlineStr">
+        <is>
+          <t>[Codex补充]</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="44" customHeight="1" s="135">
+      <c r="A69" s="215" t="inlineStr">
+        <is>
+          <t>怪物与Boss</t>
+        </is>
+      </c>
+      <c r="B69" s="215" t="inlineStr">
+        <is>
+          <t>room_attack_gap_sec</t>
+        </is>
+      </c>
+      <c r="C69" s="215" t="inlineStr">
+        <is>
+          <t>同一房间内两次出手之间的最小间隔（房间级节拍器），实现原作『错开攻击时机、给喘息』</t>
+        </is>
+      </c>
+      <c r="D69" s="215" t="inlineStr">
+        <is>
+          <t>float (秒)</t>
+        </is>
+      </c>
+      <c r="E69" s="215" t="inlineStr">
+        <is>
+          <t>关卡级可选</t>
+        </is>
+      </c>
+      <c r="F69" s="215" t="inlineStr">
+        <is>
+          <t>怪物AI</t>
+        </is>
+      </c>
+      <c r="G69" s="215" t="inlineStr">
+        <is>
+          <t>默认0.47s；room_id为空的怪不节流；未配置关卡回退默认</t>
+        </is>
+      </c>
+      <c r="H69" s="215" t="inlineStr">
+        <is>
+          <t>[Codex补充]</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="44" customHeight="1" s="135">
+      <c r="A70" s="215" t="inlineStr">
+        <is>
+          <t>怪物与Boss</t>
+        </is>
+      </c>
+      <c r="B70" s="215" t="inlineStr">
+        <is>
+          <t>requires_line_of_sight</t>
+        </is>
+      </c>
+      <c r="C70" s="215" t="inlineStr">
+        <is>
+          <t>开火前是否需要视线。缺省开启：隔墙不得开火</t>
+        </is>
+      </c>
+      <c r="D70" s="215" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="E70" s="215" t="inlineStr">
+        <is>
+          <t>全局默认 true</t>
+        </is>
+      </c>
+      <c r="F70" s="215" t="inlineStr">
+        <is>
+          <t>怪物AI</t>
+        </is>
+      </c>
+      <c r="G70" s="215" t="inlineStr">
+        <is>
+          <t>_tick_chase 内短路到最后一条；仅『已进射程且冷却已好』才投射</t>
+        </is>
+      </c>
+      <c r="H70" s="215" t="inlineStr">
+        <is>
+          <t>[Codex补充]</t>
         </is>
       </c>
     </row>
